--- a/results/job_matches_2026-07-21.xlsx
+++ b/results/job_matches_2026-07-21.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G91"/>
+  <dimension ref="A1:G113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,17 +573,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Data Engineer - Databricks</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Rippling</t>
+          <t>Steampunk</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Event Hubs, Spark, PySpark</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, Step Functions, S3, RDS, Azure, Databricks</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07c6726c35ad8fa5</t>
+          <t>https://www.indeed.com/viewjob?jk=d8b9759a865fb48a</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AWS Cloud</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Rippling</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, ECS, IAM, RDS, Scala</t>
+          <t>IAM, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Event Hubs, Spark, PySpark</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,14 +636,14 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42e3c5912b49c237</t>
+          <t>https://www.indeed.com/viewjob?jk=07c6726c35ad8fa5</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AWS Solutions Architect</t>
+          <t>AWS Cloud</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf903a5bb459577f</t>
+          <t>https://www.indeed.com/viewjob?jk=42e3c5912b49c237</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AWS Solutions Architect</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>CrossCountry Mortgage, LLC</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, RDS, Azure, GCP, Spark, PySpark</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=704b1f0ab6bff192</t>
+          <t>https://www.indeed.com/viewjob?jk=cf903a5bb459577f</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Architect (Azure + Databricks)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Nine Core Technologies</t>
+          <t>CrossCountry Mortgage, LLC</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Milpitas, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Medallion Architecture, GCP</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, RDS, Azure, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=118ef7e12d0743d7</t>
+          <t>https://www.indeed.com/viewjob?jk=704b1f0ab6bff192</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Software Engineer III - Data/Payments Technology</t>
+          <t>Senior Data Engineer - Digital Pathology (Hybrid)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Mayo Clinic</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Scala, Kafka, Snowflake, Oracle</t>
+          <t>Google Cloud Platform, GCP, Hive, Spark, Kafka, Snowflake, ELT, Power BI, Tableau, DataOps</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8366ecb2495ecb5</t>
+          <t>https://www.indeed.com/viewjob?jk=761b34bda9b68b66</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Hunt Military Communities</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Bridgewater, NJ, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Azure, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Hadoop, Hive, Spark, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29325c8c8e335924</t>
+          <t>https://www.indeed.com/viewjob?jk=177a0dfa7a7c2758</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Cybersecurity Engineer</t>
+          <t>Senior Technical Architect</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Workday</t>
+          <t>REI Systems</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Sterling, VA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, ECS, IAM, RDS, Hive, Spark</t>
+          <t>AWS, Lambda, API Gateway, ECS, IAM, RDS, Scala, Oracle, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=278c7726eee6f36f</t>
+          <t>https://www.indeed.com/viewjob?jk=175f2d223e3312d6</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer II - (Remote)</t>
+          <t>Data Architect (Azure + Databricks)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Fanatics Betting &amp; Gaming</t>
+          <t>Nine Core Technologies</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Milpitas, CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>15.3</v>
+        <v>16.7</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Databricks, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
+          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Medallion Architecture, GCP</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54fa68f69cf2083f</t>
+          <t>https://www.indeed.com/viewjob?jk=118ef7e12d0743d7</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer III - Data/Payments Technology</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CrossCountry Mortgage, LLC</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, RDS, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26d0c8a6b975fef0</t>
+          <t>https://www.indeed.com/viewjob?jk=c8366ecb2495ecb5</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Java Application Architect</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Hunt Military Communities</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Azure, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06adce66e837b3b3</t>
+          <t>https://www.indeed.com/viewjob?jk=29325c8c8e335924</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Reporting Engineer</t>
+          <t>Data Engineer II - (Remote)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Hitachi Rail</t>
+          <t>Fanatics Betting &amp; Gaming</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MySQL, Star Schema, Fact Tables, Dimension Tables</t>
+          <t>AWS, S3, RDS, Databricks, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7504d94e8707d02b</t>
+          <t>https://www.indeed.com/viewjob?jk=54fa68f69cf2083f</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Solutions Engineer - HYBRID/NC RESIDENTS ONLY</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>PowerSecure Inc.</t>
+          <t>CrossCountry Mortgage, LLC</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, RDS, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc9b66f689cbeefb</t>
+          <t>https://www.indeed.com/viewjob?jk=26d0c8a6b975fef0</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Reporting Engineer</t>
+          <t>Java Application Architect</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Hitachi Energy</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MySQL, Star Schema, Fact Tables, Dimension Tables</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59ef3d85179316f9</t>
+          <t>https://www.indeed.com/viewjob?jk=06adce66e837b3b3</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Reporting Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Bloomerang</t>
+          <t>Hitachi Rail</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, Google Cloud Platform, BigQuery, Scala, Snowflake, PostgreSQL, MySQL</t>
+          <t>AWS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MySQL, Star Schema, Fact Tables, Dimension Tables</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0eff179e948461c2</t>
+          <t>https://www.indeed.com/viewjob?jk=7504d94e8707d02b</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Databricks Architect</t>
+          <t>Data Solutions Engineer - HYBRID/NC RESIDENTS ONLY</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Confiz</t>
+          <t>PowerSecure Inc.</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Bentonville, AR, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Google Cloud Platform, Cloud Storage, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18be742c481fa20b</t>
+          <t>https://www.indeed.com/viewjob?jk=dc9b66f689cbeefb</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer (HYBRID)</t>
+          <t>Reporting Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Equinox</t>
+          <t>Hitachi Energy</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, Scala, DynamoDB, Dimensional Modeling</t>
+          <t>AWS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MySQL, Star Schema, Fact Tables, Dimension Tables</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22216c34e7397891</t>
+          <t>https://www.indeed.com/viewjob?jk=59ef3d85179316f9</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Software Engineer III : AI/ML Solutions</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Bloomerang</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, Redshift, RDS, Databricks, Google Cloud Platform, BigQuery, Scala, Snowflake, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7bc806520585d5fd</t>
+          <t>https://www.indeed.com/viewjob?jk=0eff179e948461c2</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Cloud Solutions Engineer – Azure</t>
+          <t>Software Engineering LMTS</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc23fc3c19075d7c</t>
+          <t>https://www.indeed.com/viewjob?jk=572e8633b0661a80</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Software Engineering Intern</t>
+          <t>Databricks Architect</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Copart, Inc</t>
+          <t>Confiz</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Bentonville, AR, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Google Cloud Platform, Cloud Storage, Spark, PySpark</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7bf2ebcfa4a5f5e</t>
+          <t>https://www.indeed.com/viewjob?jk=18be742c481fa20b</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Sr. SW Engineer</t>
+          <t>Sr. Data Engineer (HYBRID)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Equinox</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Foster City, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, Data Modeling, ETL, Splunk, CI/CD, Terraform</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, Scala, DynamoDB, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f774d387b35a5b8</t>
+          <t>https://www.indeed.com/viewjob?jk=22216c34e7397891</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Salesforce Business Systems Analyst</t>
+          <t>Software Engineer III : AI/ML Solutions</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb817b0533864176</t>
+          <t>https://www.indeed.com/viewjob?jk=7bc806520585d5fd</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Salesforce Business Systems Analyst</t>
+          <t>Cloud Solutions Engineer – Azure</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b799aca0d95f271</t>
+          <t>https://www.indeed.com/viewjob?jk=dc23fc3c19075d7c</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Big Data Engineer</t>
+          <t>Software Engineering Intern</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Highmark Health</t>
+          <t>Copart, Inc</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Hive, Spark, Scala, Kafka, Oracle</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d94c95081afe04c8</t>
+          <t>https://www.indeed.com/viewjob?jk=c7bf2ebcfa4a5f5e</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer with Sales Incentive Compensation (SIC)</t>
+          <t>Sr. SW Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>UNIFY SOLUTIONS INC</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Foster City, CA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, GCP, Scala</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, Data Modeling, ETL, Splunk, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb057adb6c59f5ff</t>
+          <t>https://www.indeed.com/viewjob?jk=8f774d387b35a5b8</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Salesforce Business Systems Analyst</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>NetApp</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Morrisville, NC, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0844aea628b28dab</t>
+          <t>https://www.indeed.com/viewjob?jk=cb817b0533864176</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>SAP FICO Architect</t>
+          <t>Salesforce Business Systems Analyst</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>GeekSoft Consulting</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Carmel, IN, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7242710483aaa20</t>
+          <t>https://www.indeed.com/viewjob?jk=7b799aca0d95f271</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Specialist Software Engineer</t>
+          <t>Big Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Highmark Health</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, RDS, Azure, Databricks, Scala, Oracle, SQL Server</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Hive, Spark, Scala, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31c5d5f535a77ad9</t>
+          <t>https://www.indeed.com/viewjob?jk=d94c95081afe04c8</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>LoopNet - Software Engineer II</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>CoStar Group</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Bridgewater, NJ, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, Databricks, BigQuery, Scala, Kafka, Snowflake, MySQL, DynamoDB</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51f6585eaae3edd6</t>
+          <t>https://www.indeed.com/viewjob?jk=d193f030168c94d0</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Engineer - ITS4</t>
+          <t>Databricks Data Engineer with Sales Incentive Compensation (SIC)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>State of Minnesota - Minnesota IT Services</t>
+          <t>UNIFY SOLUTIONS INC</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, ECS, IAM, RDS, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, GCP, Scala</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb33eaf3683a2fd9</t>
+          <t>https://www.indeed.com/viewjob?jk=eb057adb6c59f5ff</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Databricks Platform Engineer</t>
+          <t>Software Engineering SMTS</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Confiz</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Bentonville, AR, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Google Cloud Platform, Spark, Scala, ELT, CI/CD</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b713352ad723441</t>
+          <t>https://www.indeed.com/viewjob?jk=98a642ee513df5f7</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Bricks Data Engineer</t>
+          <t>Powertrain Applications Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Bavel systems LLP</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, GCP, Scala, Kafka</t>
+          <t>AWS, S3, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, SQL Server, ELT</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d997e2a6aa4fbed</t>
+          <t>https://www.indeed.com/viewjob?jk=af00d281c82c2777</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Informatica Cloud Data Engineer (IDMC/IICS)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>NetApp</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Morrisville, NC, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Snowflake, Oracle, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,67 +1721,67 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2526f9ca235bb42c</t>
+          <t>https://www.indeed.com/viewjob?jk=0844aea628b28dab</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Informatica Cloud Data Engineer (IDMC/IICS)</t>
+          <t>Specialist Software Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Snowflake, Oracle, Data Modeling, ETL</t>
+          <t>AWS, Lambda, Redshift, S3, RDS, Azure, Databricks, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f156bc316e4a8e1e</t>
+          <t>https://www.indeed.com/viewjob?jk=31c5d5f535a77ad9</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>AWS DevOps Engineer Experience in Pega Platform EKS with Jenkins and Terraform DevOps OnlyUS Citizen</t>
+          <t>LoopNet - Software Engineer II</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>nProspect</t>
+          <t>CoStar Group</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, Kafka, Cassandra, Jenkins, Terraform</t>
+          <t>AWS, S3, SQS, Databricks, BigQuery, Scala, Kafka, Snowflake, MySQL, DynamoDB</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c8c651e8e033eb5</t>
+          <t>https://www.indeed.com/viewjob?jk=51f6585eaae3edd6</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Data Engineer - ITS4</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>FEED THE CHILDREN</t>
+          <t>State of Minnesota - Minnesota IT Services</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Spark, Scala, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, ECS, IAM, RDS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d4416990cb07c5b</t>
+          <t>https://www.indeed.com/viewjob?jk=fb33eaf3683a2fd9</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer</t>
+          <t>AI &amp; Data Engineer, Data Discovery Services</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>LogicMonitor</t>
+          <t>Bristol Myers Squibb</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Data Modeling, ETL, Terraform</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, ECS, RDS, Azure, Databricks, Vertex AI</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92a2dfe6bebcb2dc</t>
+          <t>https://www.indeed.com/viewjob?jk=9331d42b3835041a</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Windows Engineer (Expert)</t>
+          <t>Databricks Platform Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>BAE Systems USA</t>
+          <t>Confiz</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Bentonville, AR, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, Oracle, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Google Cloud Platform, Spark, Scala, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09ee1d1985ee70d9</t>
+          <t>https://www.indeed.com/viewjob?jk=5b713352ad723441</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Bricks Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Qureos</t>
+          <t>Bavel systems LLP</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, GCP, Scala, Kafka</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c91b09d863e5b13</t>
+          <t>https://www.indeed.com/viewjob?jk=2d997e2a6aa4fbed</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Software Engineer II - Streaming</t>
+          <t>Informatica Cloud Data Engineer (IDMC/IICS)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Rivian and Volkswagen Group Technologies</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Kafka Connect, ELT, CI/CD</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Snowflake, Oracle, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3871dec46927667b</t>
+          <t>https://www.indeed.com/viewjob?jk=2526f9ca235bb42c</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Python Software Architect</t>
+          <t>Informatica Cloud Data Engineer (IDMC/IICS)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Scala, Oracle, SQL Server, PostgreSQL, DynamoDB, CI/CD</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Snowflake, Oracle, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51db177a53e7ef14</t>
+          <t>https://www.indeed.com/viewjob?jk=f156bc316e4a8e1e</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Java Product Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>Diaconia, LLC.</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, PostgreSQL, MySQL, Splunk, Maven</t>
+          <t>AWS, Azure, Scala, Kafka, Oracle, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1d1f01448956ac8</t>
+          <t>https://www.indeed.com/viewjob?jk=ed19f7417f9c2e59</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, PostgreSQL, MySQL, Splunk, Maven</t>
+          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Azure, Snowflake, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c9d86fee622b07b</t>
+          <t>https://www.indeed.com/viewjob?jk=87d9611a04bffadf</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Analyst (Data Solutions)</t>
+          <t>Sr. Forward Deployed Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company</t>
+          <t>LogicMonitor</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI, Tableau, Git</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Data Modeling, ETL, Terraform</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60db44428bef76ed</t>
+          <t>https://www.indeed.com/viewjob?jk=92a2dfe6bebcb2dc</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Azure DevOps Architect</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>IPolarity LLC</t>
+          <t>FEED THE CHILDREN</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Whippany, NJ, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Glue, IAM, RDS, Azure, GCP, Scala, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Spark, Scala, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=198e8bee7c6735a3</t>
+          <t>https://www.indeed.com/viewjob?jk=3d4416990cb07c5b</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Full Stack .NET Developer – C#, React, Azure/AWS</t>
+          <t>Windows Engineer (Expert)</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>J2B GLOBAL LLC</t>
+          <t>BAE Systems USA</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MongoDB, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, Oracle, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ceec9a4f672d1616</t>
+          <t>https://www.indeed.com/viewjob?jk=09ee1d1985ee70d9</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Java Engineer</t>
+          <t>Cloud Systems Engineer III</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>Orange County's Credit Union</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Santa Ana, CA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, MongoDB</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Scala, ELT, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9eed61967883578e</t>
+          <t>https://www.indeed.com/viewjob?jk=37e9b523a42f1787</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Foley</t>
+          <t>Qureos</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Medallion Architecture, Scala, Data Modeling, ETL</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb528101e5b7e6f0</t>
+          <t>https://www.indeed.com/viewjob?jk=3c91b09d863e5b13</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>AI Solution Engineer</t>
+          <t>Software Engineer II - Streaming</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Agilify</t>
+          <t>Rivian and Volkswagen Group Technologies</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, Azure, Event Hubs, BigQuery, Scala, Kafka, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Kafka Connect, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=173deae55fc0fc11</t>
+          <t>https://www.indeed.com/viewjob?jk=3871dec46927667b</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Network Engineer</t>
+          <t>Senior Software Engineer (C#/Java/AI) - Underwriting Automation - Hybrid</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Citizens</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Johnston, RI, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, CI/CD, Jenkins, Maven, Terraform, Docker, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93cf7434fe21677c</t>
+          <t>https://www.indeed.com/viewjob?jk=6f1adc20d8ab8b4a</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Sr. Database Administrator</t>
+          <t>Senior Software Engineer (C#/Java/AI) - Underwriting Automation - Hybrid</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Vertafore</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, Terraform, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=652e6c19792a8b61</t>
+          <t>https://www.indeed.com/viewjob?jk=86fdcdffd7cae712</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Solution Architect – Data Migration &amp; Analytics</t>
+          <t>ML-GenAI Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Zensar Technologies</t>
+          <t>Prodapt Solutions</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, RDS, Data Lake Storage, Medallion Architecture, Scala, Snowflake, Data Modeling, dbt</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Vertex AI, Scala, NoSQL, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f7b9a9c0a9082ee</t>
+          <t>https://www.indeed.com/viewjob?jk=1b71a1261fd024f4</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Python Software Architect</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>SpyCloud</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Databricks, Spark, Scala, DynamoDB, ETL</t>
+          <t>AWS, Glue, S3, RDS, Scala, Oracle, SQL Server, PostgreSQL, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,32 +2421,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a2f212e69e1f862</t>
+          <t>https://www.indeed.com/viewjob?jk=51db177a53e7ef14</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>EagleView</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, PostgreSQL, MySQL, Splunk, Maven</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,32 +2456,32 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eee26a905ec914aa</t>
+          <t>https://www.indeed.com/viewjob?jk=b1d1f01448956ac8</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Database Reliability Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Frontline Education</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Wayne, PA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, ETL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, PostgreSQL, MySQL, Splunk, Maven</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,32 +2491,32 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ca664998e6fb6c3</t>
+          <t>https://www.indeed.com/viewjob?jk=5c9d86fee622b07b</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Database Reliability Engineer</t>
+          <t>Data Analyst (Data Solutions)</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Frontline Education</t>
+          <t>The Coca-Cola Company</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Naperville, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, ETL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI, Tableau, Git</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,32 +2526,32 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae22c1a528cec63a</t>
+          <t>https://www.indeed.com/viewjob?jk=60db44428bef76ed</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Database Reliability Engineer</t>
+          <t>Azure DevOps Architect</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Frontline Education</t>
+          <t>IPolarity LLC</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Whippany, NJ, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, ETL, CI/CD, Terraform</t>
+          <t>AWS, Glue, IAM, RDS, Azure, GCP, Scala, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97b21b525c894dd7</t>
+          <t>https://www.indeed.com/viewjob?jk=198e8bee7c6735a3</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Full Stack .NET Developer – C#, React, Azure/AWS</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>SpyCloud</t>
+          <t>J2B GLOBAL LLC</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Databricks, Spark, Scala, DynamoDB, ETL</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MongoDB, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,19 +2596,19 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b990fe917577735</t>
+          <t>https://www.indeed.com/viewjob?jk=ceec9a4f672d1616</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Security Data Analyst - Parsing</t>
+          <t>Java Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>SpyCloud</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2617,11 +2617,11 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, API Gateway, RDS, Databricks, NoSQL, ETL, CI/CD</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=171de003fe5563fb</t>
+          <t>https://www.indeed.com/viewjob?jk=9eed61967883578e</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>MDM Integration Engineer</t>
+          <t>Forward Deployed Data Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>McLane Company</t>
+          <t>CoorsTek</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Temple, TX, US USA</t>
+          <t>Golden, CO, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, CI/CD, Terraform</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,19 +2666,19 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3b598b8c3673649</t>
+          <t>https://www.indeed.com/viewjob?jk=01c677c253d655bb</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Scientist / Senior Data Scientist (Risk Modeling)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Berkshire Hathaway Specialty Insurance</t>
+          <t>Foley</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2687,81 +2687,81 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Docker, Git, Python</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Medallion Architecture, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c9e4130f1298022</t>
+          <t>https://www.indeed.com/viewjob?jk=fb528101e5b7e6f0</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Scientist / Senior Data Scientist (Risk Modeling)</t>
+          <t>AI Solution Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Berkshire Hathaway Specialty Insurance</t>
+          <t>Agilify</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Docker, Git, Python</t>
+          <t>AWS, S3, API Gateway, Azure, Event Hubs, BigQuery, Scala, Kafka, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7f7784d943297ed</t>
+          <t>https://www.indeed.com/viewjob?jk=173deae55fc0fc11</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Senior Network Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Northwest Federal Credit Union</t>
+          <t>Citizens</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Johnston, RI, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, MySQL, Azure DevOps, Terraform, Azure Monitor</t>
+          <t>AWS, S3, RDS, Scala, CI/CD, Jenkins, Maven, Terraform, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7291a950f8ec410d</t>
+          <t>https://www.indeed.com/viewjob?jk=93cf7434fe21677c</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Software Engineer II - Platform Engineer/Databricks</t>
+          <t>Senior Database Reliability Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Frontline Education</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Naperville, IL, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Jenkins, Maven, Terraform, Jenkins, Git</t>
+          <t>AWS, RDS, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, ETL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4448bee09655101c</t>
+          <t>https://www.indeed.com/viewjob?jk=03a470170ea48de6</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Senior Database Reliability Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>State Street</t>
+          <t>Frontline Education</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Quincy, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Splunk, CI/CD, Jenkins, Terraform, Jenkins</t>
+          <t>AWS, RDS, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, ETL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb61fc433cd2352b</t>
+          <t>https://www.indeed.com/viewjob?jk=22e28cc34091c701</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Architect</t>
+          <t>Senior Database Reliability Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Mass General Brigham</t>
+          <t>Frontline Education</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Somerville, MA, US USA</t>
+          <t>Wayne, PA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, ETL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,32 +2876,32 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dccbfd697359c720</t>
+          <t>https://www.indeed.com/viewjob?jk=406eb6619e461cdd</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Software Engineer IV / V (Java, React, AWS)</t>
+          <t>SR SOFTWARE ENGINEER</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Auto.Live</t>
+          <t>Dollar General</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Goodlettsville, TN, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, SQS, Scala, Kafka, MySQL, CI/CD, Terraform, Docker, Kubernetes, Git</t>
+          <t>S3, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, Cassandra, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,32 +2911,32 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42c2207352100be0</t>
+          <t>https://www.indeed.com/viewjob?jk=fbb1d7ed6fd57469</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Engineer, Corp Solutions</t>
+          <t>Software Engineer 3, Content Platforms</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Papa John's</t>
+          <t>Condé Nast</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, CI/CD, Jenkins, Maven, Kubernetes, Jenkins, Git, Bitbucket</t>
+          <t>AWS, Kafka, PostgreSQL, MongoDB, Data Modeling, Splunk, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,32 +2946,32 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ae25ca0f2bd81f6</t>
+          <t>https://www.indeed.com/viewjob?jk=1d59c1e871e80877</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Amazon Connect Application Architect</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>TELUS Digital</t>
+          <t>EagleView</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, RDS, Scala, DynamoDB, CI/CD, Terraform, AWS CloudFormation</t>
+          <t>AWS, Lambda, S3, SQS, SNS, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=feceaa7f623de4d6</t>
+          <t>https://www.indeed.com/viewjob?jk=eee26a905ec914aa</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Amazon Connect Application Architect</t>
+          <t>Sr. Database Administrator</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>TELUS Digital</t>
+          <t>Vertafore</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, RDS, Scala, DynamoDB, CI/CD, Terraform, AWS CloudFormation</t>
+          <t>AWS, Redshift, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, Terraform, Git</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,32 +3016,32 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef89c4f9800f8a90</t>
+          <t>https://www.indeed.com/viewjob?jk=652e6c19792a8b61</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Amazon Connect Application Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>TELUS Digital</t>
+          <t>SpyCloud</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, RDS, Scala, DynamoDB, CI/CD, Terraform, AWS CloudFormation</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Databricks, Spark, Scala, DynamoDB, ETL</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,32 +3051,32 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5fc58207e473b9f5</t>
+          <t>https://www.indeed.com/viewjob?jk=7a2f212e69e1f862</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Amazon Connect Application Architect</t>
+          <t>Senior Database Reliability Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>TELUS Digital</t>
+          <t>Frontline Education</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Wayne, PA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, RDS, Scala, DynamoDB, CI/CD, Terraform, AWS CloudFormation</t>
+          <t>AWS, RDS, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, ETL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,32 +3086,32 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f8bb981d509050f</t>
+          <t>https://www.indeed.com/viewjob?jk=1ca664998e6fb6c3</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Amazon Connect Application Architect</t>
+          <t>Senior Database Reliability Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>TELUS Digital</t>
+          <t>Frontline Education</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Charlottesville, VA, US USA</t>
+          <t>Naperville, IL, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, RDS, Scala, DynamoDB, CI/CD, Terraform, AWS CloudFormation</t>
+          <t>AWS, RDS, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, ETL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,32 +3121,32 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b3612752c893190</t>
+          <t>https://www.indeed.com/viewjob?jk=ae22c1a528cec63a</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Software Engineer ( Seattle/Provo)</t>
+          <t>Senior Database Reliability Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Press Ganey</t>
+          <t>Frontline Education</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Provo, UT, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, Data Modeling, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, ETL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,32 +3156,32 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b27efa8ed4a1f97</t>
+          <t>https://www.indeed.com/viewjob?jk=97b21b525c894dd7</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Sr Devops Engineer</t>
+          <t>Solution Architect – Data Migration &amp; Analytics</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>_coderio</t>
+          <t>Zensar Technologies</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, Kinesis, S3, RDS, Data Lake Storage, Medallion Architecture, Scala, Snowflake, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,32 +3191,32 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=541df4abc8320b5a</t>
+          <t>https://www.indeed.com/viewjob?jk=1f7b9a9c0a9082ee</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior R&amp;D Software Engineer, Fivetran AI</t>
+          <t>FCCM Senior Consultant</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Fivetran</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Iselin, NJ, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, BigQuery, Snowflake, ETL, ELT, dbt, Docker</t>
+          <t>Spark, PySpark, Scala, Oracle, Data Modeling, ETL, CI/CD, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,32 +3226,32 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55c8e7c6018043d4</t>
+          <t>https://www.indeed.com/viewjob?jk=a3f4310b4c00f608</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior R&amp;D Software Engineer, Fivetran AI</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Fivetran</t>
+          <t>SpyCloud</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, BigQuery, Snowflake, ETL, ELT, dbt, Docker</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Databricks, Spark, Scala, DynamoDB, ETL</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,32 +3261,32 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30bf0451dbc419d1</t>
+          <t>https://www.indeed.com/viewjob?jk=8b990fe917577735</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior R&amp;D Software Engineer, Fivetran AI</t>
+          <t>Security Data Analyst - Parsing</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Fivetran</t>
+          <t>SpyCloud</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, BigQuery, Snowflake, ETL, ELT, dbt, Docker</t>
+          <t>AWS, Lambda, S3, SQS, API Gateway, RDS, Databricks, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,32 +3296,32 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=501671e22555fe5c</t>
+          <t>https://www.indeed.com/viewjob?jk=171de003fe5563fb</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior R&amp;D Software Engineer, Fivetran AI</t>
+          <t>MDM Integration Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Fivetran</t>
+          <t>McLane Company</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Temple, TX, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, BigQuery, Snowflake, ETL, ELT, dbt, Docker</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8b8baa922f2b05a</t>
+          <t>https://www.indeed.com/viewjob?jk=c3b598b8c3673649</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>AI Software Engineer IV</t>
+          <t>Data Scientist / Senior Data Scientist (Risk Modeling)</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>The Standard Insurance</t>
+          <t>Berkshire Hathaway Specialty Insurance</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, MLflow, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Docker, Git, Python</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3c232645c82fc83</t>
+          <t>https://www.indeed.com/viewjob?jk=2c9e4130f1298022</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Systems Engineer I</t>
+          <t>Data Scientist / Senior Data Scientist (Risk Modeling)</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Texas A&amp;M AgriLife Extension</t>
+          <t>Berkshire Hathaway Specialty Insurance</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>College Station, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,34 +3391,34 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Cloud Storage, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Docker, Git, Python</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a99f136d94c9eab9</t>
+          <t>https://www.indeed.com/viewjob?jk=d7f7784d943297ed</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Systems Engineer I</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Texas A&amp;M AgriLife Extension</t>
+          <t>Northwest Federal Credit Union</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>College Station, TX, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Cloud Storage, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, MySQL, Azure DevOps, Terraform, Azure Monitor</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b951b068dc32695</t>
+          <t>https://www.indeed.com/viewjob?jk=7291a950f8ec410d</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Sr. Business Intelligence Engineer</t>
+          <t>Software Engineer II - Platform Engineer/Databricks</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Crane Worldwide Logistics</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Snowflake, Data Modeling, dbt, Power BI, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Jenkins, Maven, Terraform, Jenkins, Git</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53344a199a269470</t>
+          <t>https://www.indeed.com/viewjob?jk=4448bee09655101c</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Software Engineer- Greensboro, NC</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Stake Center Locating</t>
+          <t>State Street</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Greensboro, NC, US USA</t>
+          <t>Quincy, MA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, SQL Server, ETL, ELT, Power BI, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Splunk, CI/CD, Jenkins, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c8332d54e7fcd1c</t>
+          <t>https://www.indeed.com/viewjob?jk=eb61fc433cd2352b</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior MLOps Engineer I</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Qureos</t>
+          <t>Zeitview</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,34 +3531,34 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Docker, Git</t>
+          <t>AWS, RDS, Scala, PostgreSQL, MLOps, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad6582003e647074</t>
+          <t>https://www.indeed.com/viewjob?jk=5c8710a47a6c9b4e</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Database Developer</t>
+          <t>Senior MLOps Engineer I</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Hollstadt Consulting</t>
+          <t>Zeitview</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,34 +3566,34 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>RDS, Azure, Spark, PySpark, SQL Server, Data Modeling, ETL, Power BI, Jenkins, Azure DevOps</t>
+          <t>AWS, RDS, Scala, PostgreSQL, MLOps, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdef6e08804da8cc</t>
+          <t>https://www.indeed.com/viewjob?jk=84de7dc9a3088a08</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Database Developer (Contractor) - MNSITE-3762</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>RE/SPEC Inc</t>
+          <t>Karsun Solutions LLC</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,17 +3601,787 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2f81c0ec4956c9db</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Senior R&amp;D Software Engineer, Fivetran AI</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Fivetran</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, GCP, BigQuery, Snowflake, ETL, ELT, dbt, Docker</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=55c8e7c6018043d4</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Senior R&amp;D Software Engineer, Fivetran AI</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Fivetran</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, GCP, BigQuery, Snowflake, ETL, ELT, dbt, Docker</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=30bf0451dbc419d1</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Senior R&amp;D Software Engineer, Fivetran AI</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Fivetran</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, GCP, BigQuery, Snowflake, ETL, ELT, dbt, Docker</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=501671e22555fe5c</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Senior R&amp;D Software Engineer, Fivetran AI</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Fivetran</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Oakland, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, GCP, BigQuery, Snowflake, ETL, ELT, dbt, Docker</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f8b8baa922f2b05a</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Sr Devops Engineer</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>_coderio</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Miami, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=541df4abc8320b5a</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Senior .NET Developer</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Cognizant</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, ECS, Scala, Kafka, SQL Server, PostgreSQL, NoSQL, Data Modeling, CI/CD</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=35a2c65d6f2f7d06</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Senior Architect</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Mass General Brigham</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Somerville, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dccbfd697359c720</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer IV / V (Java, React, AWS)</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Auto.Live</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>AWS, SQS, Scala, Kafka, MySQL, CI/CD, Terraform, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=42c2207352100be0</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Senior Engineer, Corp Solutions</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Papa John's</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Louisville, KY, US USA</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>RDS, Google Cloud Platform, GCP, CI/CD, Jenkins, Maven, Kubernetes, Jenkins, Git, Bitbucket</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6ae25ca0f2bd81f6</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Senior Amazon Connect Application Architect</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>TELUS Digital</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Kinesis, S3, RDS, Scala, DynamoDB, CI/CD, Terraform, AWS CloudFormation</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=feceaa7f623de4d6</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Senior Amazon Connect Application Architect</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>TELUS Digital</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Kinesis, S3, RDS, Scala, DynamoDB, CI/CD, Terraform, AWS CloudFormation</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ef89c4f9800f8a90</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Senior Amazon Connect Application Architect</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>TELUS Digital</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Durham, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Kinesis, S3, RDS, Scala, DynamoDB, CI/CD, Terraform, AWS CloudFormation</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5fc58207e473b9f5</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Senior Amazon Connect Application Architect</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>TELUS Digital</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Kinesis, S3, RDS, Scala, DynamoDB, CI/CD, Terraform, AWS CloudFormation</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1f8bb981d509050f</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Senior Amazon Connect Application Architect</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>TELUS Digital</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Charlottesville, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Kinesis, S3, RDS, Scala, DynamoDB, CI/CD, Terraform, AWS CloudFormation</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4b3612752c893190</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer ( Seattle/Provo)</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Press Ganey</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Provo, UT, US USA</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, Data Modeling, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1b27efa8ed4a1f97</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>AI Software Engineer IV</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>The Standard Insurance</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Portland, OR, US USA</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Scala, MLflow, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b3c232645c82fc83</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Sr. Business Intelligence Engineer</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Crane Worldwide Logistics</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Snowflake, Data Modeling, dbt, Power BI, CI/CD, GitHub Actions, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=53344a199a269470</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Software Engineer- Greensboro, NC</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Stake Center Locating</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Greensboro, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, SQL Server, ETL, ELT, Power BI, Git</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2c8332d54e7fcd1c</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Qureos</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Louisville, KY, US USA</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Docker, Git</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ad6582003e647074</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Database Developer</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Hollstadt Consulting</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>MN, US USA</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
           <t>RDS, Azure, Spark, PySpark, SQL Server, Data Modeling, ETL, Power BI, Jenkins, Azure DevOps</t>
         </is>
       </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bdef6e08804da8cc</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Database Developer (Contractor) - MNSITE-3762</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>RE/SPEC Inc</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Saint Paul, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Spark, PySpark, SQL Server, Data Modeling, ETL, Power BI, Jenkins, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=bac2143c91f124e3</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>AI &amp; Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>OneBlood</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Saint Petersburg, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Medallion Architecture, ETL, ELT, CI/CD, Git, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9242f2d7ab83418a</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-07-21.xlsx
+++ b/results/job_matches_2026-07-21.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G113"/>
+  <dimension ref="A1:G118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,17 +608,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>AWS Cloud</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Rippling</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Event Hubs, Spark, PySpark</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07c6726c35ad8fa5</t>
+          <t>https://www.indeed.com/viewjob?jk=42e3c5912b49c237</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AWS Cloud</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Rippling</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, ECS, IAM, RDS, Scala</t>
+          <t>IAM, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Event Hubs, Spark, PySpark</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42e3c5912b49c237</t>
+          <t>https://www.indeed.com/viewjob?jk=07c6726c35ad8fa5</t>
         </is>
       </c>
     </row>
@@ -748,25 +748,25 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Digital Pathology (Hybrid)</t>
+          <t>Azure Databricks Architect Healthcare Payer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Mayo Clinic</t>
+          <t>VeeRteq Solutions Inc.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Rochester, MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, Hive, Spark, Kafka, Snowflake, ELT, Power BI, Tableau, DataOps</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Hadoop, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=761b34bda9b68b66</t>
+          <t>https://www.indeed.com/viewjob?jk=5652d49391bd82a2</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Data Engineer - Digital Pathology (Hybrid)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>Mayo Clinic</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Bridgewater, NJ, US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Hadoop, Hive, Spark, Scala</t>
+          <t>Google Cloud Platform, GCP, Hive, Spark, Kafka, Snowflake, ELT, Power BI, Tableau, DataOps</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=177a0dfa7a7c2758</t>
+          <t>https://www.indeed.com/viewjob?jk=761b34bda9b68b66</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Technical Architect</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>REI Systems</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sterling, VA, US USA</t>
+          <t>Bridgewater, NJ, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, ECS, IAM, RDS, Scala, Oracle, DynamoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Hadoop, Hive, Spark, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=175f2d223e3312d6</t>
+          <t>https://www.indeed.com/viewjob?jk=177a0dfa7a7c2758</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Architect (Azure + Databricks)</t>
+          <t>Senior Technical Architect</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Nine Core Technologies</t>
+          <t>REI Systems</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Milpitas, CA, US USA</t>
+          <t>Sterling, VA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Medallion Architecture, GCP</t>
+          <t>AWS, Lambda, API Gateway, ECS, IAM, RDS, Scala, Oracle, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=118ef7e12d0743d7</t>
+          <t>https://www.indeed.com/viewjob?jk=175f2d223e3312d6</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Software Engineer III - Data/Payments Technology</t>
+          <t>Data Architect (Azure + Databricks)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Nine Core Technologies</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Milpitas, CA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Scala, Kafka, Snowflake, Oracle</t>
+          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Medallion Architecture, GCP</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8366ecb2495ecb5</t>
+          <t>https://www.indeed.com/viewjob?jk=118ef7e12d0743d7</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Software Engineer III - Data/Payments Technology</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Hunt Military Communities</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Azure, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29325c8c8e335924</t>
+          <t>https://www.indeed.com/viewjob?jk=c8366ecb2495ecb5</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Engineer II - (Remote)</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Fanatics Betting &amp; Gaming</t>
+          <t>Hunt Military Communities</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Databricks, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Azure, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54fa68f69cf2083f</t>
+          <t>https://www.indeed.com/viewjob?jk=29325c8c8e335924</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer II - (Remote)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CrossCountry Mortgage, LLC</t>
+          <t>Fanatics Betting &amp; Gaming</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, RDS, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, S3, RDS, Databricks, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26d0c8a6b975fef0</t>
+          <t>https://www.indeed.com/viewjob?jk=54fa68f69cf2083f</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Java Application Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>CrossCountry Mortgage, LLC</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, RDS, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06adce66e837b3b3</t>
+          <t>https://www.indeed.com/viewjob?jk=26d0c8a6b975fef0</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Reporting Engineer</t>
+          <t>Java Application Architect</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Hitachi Rail</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MySQL, Star Schema, Fact Tables, Dimension Tables</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7504d94e8707d02b</t>
+          <t>https://www.indeed.com/viewjob?jk=06adce66e837b3b3</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Solutions Engineer - HYBRID/NC RESIDENTS ONLY</t>
+          <t>Data Modeler</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>PowerSecure Inc.</t>
+          <t>VeeRteq Solutions Inc.</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Hadoop, Scala, Snowflake, Databricks Lakehouse, Oracle</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc9b66f689cbeefb</t>
+          <t>https://www.indeed.com/viewjob?jk=99058f5a757f5431</t>
         </is>
       </c>
     </row>
@@ -1138,7 +1138,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Hitachi Energy</t>
+          <t>Hitachi Rail</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59ef3d85179316f9</t>
+          <t>https://www.indeed.com/viewjob?jk=7504d94e8707d02b</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Solutions Engineer - HYBRID/NC RESIDENTS ONLY</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Bloomerang</t>
+          <t>PowerSecure Inc.</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, Google Cloud Platform, BigQuery, Scala, Snowflake, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0eff179e948461c2</t>
+          <t>https://www.indeed.com/viewjob?jk=dc9b66f689cbeefb</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Software Engineering LMTS</t>
+          <t>Reporting Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Hitachi Energy</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, NoSQL</t>
+          <t>AWS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MySQL, Star Schema, Fact Tables, Dimension Tables</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=572e8633b0661a80</t>
+          <t>https://www.indeed.com/viewjob?jk=59ef3d85179316f9</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Databricks Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Confiz</t>
+          <t>Bloomerang</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Bentonville, AR, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Google Cloud Platform, Cloud Storage, Spark, PySpark</t>
+          <t>AWS, Redshift, RDS, Databricks, Google Cloud Platform, BigQuery, Scala, Snowflake, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18be742c481fa20b</t>
+          <t>https://www.indeed.com/viewjob?jk=0eff179e948461c2</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer (HYBRID)</t>
+          <t>Software Engineering LMTS</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Equinox</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, Scala, DynamoDB, Dimensional Modeling</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22216c34e7397891</t>
+          <t>https://www.indeed.com/viewjob?jk=572e8633b0661a80</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Software Engineer III : AI/ML Solutions</t>
+          <t>Databricks Architect</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Confiz</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Bentonville, AR, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Google Cloud Platform, Cloud Storage, Spark, PySpark</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7bc806520585d5fd</t>
+          <t>https://www.indeed.com/viewjob?jk=18be742c481fa20b</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Cloud Solutions Engineer – Azure</t>
+          <t>Software Engineer III : AI/ML Solutions</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc23fc3c19075d7c</t>
+          <t>https://www.indeed.com/viewjob?jk=7bc806520585d5fd</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Software Engineering Intern</t>
+          <t>Cloud Solutions Engineer – Azure</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Copart, Inc</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7bf2ebcfa4a5f5e</t>
+          <t>https://www.indeed.com/viewjob?jk=dc23fc3c19075d7c</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Sr. SW Engineer</t>
+          <t>Sr. Data Engineer (HYBRID)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Equinox</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Foster City, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, Data Modeling, ETL, Splunk, CI/CD, Terraform</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, Scala, DynamoDB, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f774d387b35a5b8</t>
+          <t>https://www.indeed.com/viewjob?jk=22216c34e7397891</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Salesforce Business Systems Analyst</t>
+          <t>Software Engineering Intern</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Copart, Inc</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb817b0533864176</t>
+          <t>https://www.indeed.com/viewjob?jk=c7bf2ebcfa4a5f5e</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Salesforce Business Systems Analyst</t>
+          <t>Senior AI Security Automation Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>State Street</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Quincy, MA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, ELT</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b799aca0d95f271</t>
+          <t>https://www.indeed.com/viewjob?jk=1063ffb870d53611</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Big Data Engineer</t>
+          <t>Sr. SW Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Highmark Health</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>Foster City, CA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Hive, Spark, Scala, Kafka, Oracle</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, Data Modeling, ETL, Splunk, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d94c95081afe04c8</t>
+          <t>https://www.indeed.com/viewjob?jk=8f774d387b35a5b8</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Salesforce Business Systems Analyst</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Bridgewater, NJ, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d193f030168c94d0</t>
+          <t>https://www.indeed.com/viewjob?jk=cb817b0533864176</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer with Sales Incentive Compensation (SIC)</t>
+          <t>Salesforce Business Systems Analyst</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>UNIFY SOLUTIONS INC</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, GCP, Scala</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb057adb6c59f5ff</t>
+          <t>https://www.indeed.com/viewjob?jk=7b799aca0d95f271</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Software Engineering SMTS</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Bridgewater, NJ, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98a642ee513df5f7</t>
+          <t>https://www.indeed.com/viewjob?jk=d193f030168c94d0</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Powertrain Applications Engineer</t>
+          <t>Big Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Highmark Health</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, SQL Server, ELT</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Hive, Spark, Scala, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af00d281c82c2777</t>
+          <t>https://www.indeed.com/viewjob?jk=d94c95081afe04c8</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Databricks Data Engineer with Sales Incentive Compensation (SIC)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>NetApp</t>
+          <t>UNIFY SOLUTIONS INC</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Morrisville, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, GCP, Scala</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0844aea628b28dab</t>
+          <t>https://www.indeed.com/viewjob?jk=eb057adb6c59f5ff</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Specialist Software Engineer</t>
+          <t>Senior Solution Architect - Java/J2EE</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>PNC Financial Services Group</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Farmers Branch, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, RDS, Azure, Databricks, Scala, Oracle, SQL Server</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31c5d5f535a77ad9</t>
+          <t>https://www.indeed.com/viewjob?jk=3a23b5c57a47b265</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>LoopNet - Software Engineer II</t>
+          <t>Software Architect - Java/Spring Boot/Kafka</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>CoStar Group</t>
+          <t>PNC Financial Services Group</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, Databricks, BigQuery, Scala, Kafka, Snowflake, MySQL, DynamoDB</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51f6585eaae3edd6</t>
+          <t>https://www.indeed.com/viewjob?jk=f929c4ac83ec17b7</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Engineer - ITS4</t>
+          <t>Software Engineering SMTS</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>State of Minnesota - Minnesota IT Services</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, ECS, IAM, RDS, Spark, PySpark</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb33eaf3683a2fd9</t>
+          <t>https://www.indeed.com/viewjob?jk=98a642ee513df5f7</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>AI &amp; Data Engineer, Data Discovery Services</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Bristol Myers Squibb</t>
+          <t>NetApp</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Morrisville, NC, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, ECS, RDS, Azure, Databricks, Vertex AI</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,67 +1861,67 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9331d42b3835041a</t>
+          <t>https://www.indeed.com/viewjob?jk=0844aea628b28dab</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Databricks Platform Engineer</t>
+          <t>Specialist Software Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Confiz</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Bentonville, AR, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Google Cloud Platform, Spark, Scala, ELT, CI/CD</t>
+          <t>AWS, Lambda, Redshift, S3, RDS, Azure, Databricks, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b713352ad723441</t>
+          <t>https://www.indeed.com/viewjob?jk=31c5d5f535a77ad9</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Data Bricks Data Engineer</t>
+          <t>LoopNet - Software Engineer II</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Bavel systems LLP</t>
+          <t>CoStar Group</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, GCP, Scala, Kafka</t>
+          <t>AWS, S3, SQS, Databricks, BigQuery, Scala, Kafka, Snowflake, MySQL, DynamoDB</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d997e2a6aa4fbed</t>
+          <t>https://www.indeed.com/viewjob?jk=51f6585eaae3edd6</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Informatica Cloud Data Engineer (IDMC/IICS)</t>
+          <t>AI &amp; Data Engineer, Data Discovery Services</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Bristol Myers Squibb</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Snowflake, Oracle, Data Modeling, ETL</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, ECS, RDS, Azure, Databricks, Vertex AI</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2526f9ca235bb42c</t>
+          <t>https://www.indeed.com/viewjob?jk=9331d42b3835041a</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Informatica Cloud Data Engineer (IDMC/IICS)</t>
+          <t>Databricks Platform Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Confiz</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Bentonville, AR, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Snowflake, Oracle, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Google Cloud Platform, Spark, Scala, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f156bc316e4a8e1e</t>
+          <t>https://www.indeed.com/viewjob?jk=5b713352ad723441</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Java Product Engineer</t>
+          <t>Data Bricks Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Diaconia, LLC.</t>
+          <t>Bavel systems LLP</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, Oracle, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
+          <t>AWS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, GCP, Scala, Kafka</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,19 +2036,19 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed19f7417f9c2e59</t>
+          <t>https://www.indeed.com/viewjob?jk=2d997e2a6aa4fbed</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Informatica Cloud Data Engineer (IDMC/IICS)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Azure, Snowflake, CI/CD, Jenkins</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Snowflake, Oracle, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87d9611a04bffadf</t>
+          <t>https://www.indeed.com/viewjob?jk=2526f9ca235bb42c</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer</t>
+          <t>Informatica Cloud Data Engineer (IDMC/IICS)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>LogicMonitor</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Data Modeling, ETL, Terraform</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Snowflake, Oracle, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92a2dfe6bebcb2dc</t>
+          <t>https://www.indeed.com/viewjob?jk=f156bc316e4a8e1e</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Java Product Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>FEED THE CHILDREN</t>
+          <t>Diaconia, LLC.</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Spark, Scala, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, Azure, Scala, Kafka, Oracle, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,137 +2141,137 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d4416990cb07c5b</t>
+          <t>https://www.indeed.com/viewjob?jk=ed19f7417f9c2e59</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Windows Engineer (Expert)</t>
+          <t>Senior Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>BAE Systems USA</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Hopkins, MN, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, Oracle, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09ee1d1985ee70d9</t>
+          <t>https://www.indeed.com/viewjob?jk=caea23a7afe82982</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Cloud Systems Engineer III</t>
+          <t>Senior Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Orange County's Credit Union</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Santa Ana, CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, Scala, ELT, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37e9b523a42f1787</t>
+          <t>https://www.indeed.com/viewjob?jk=2c6c9dc97e7a8c55</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Qureos</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Brookfield, WI, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c91b09d863e5b13</t>
+          <t>https://www.indeed.com/viewjob?jk=97ef6349d26627c1</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Software Engineer II - Streaming</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Rivian and Volkswagen Group Technologies</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Kafka Connect, ELT, CI/CD</t>
+          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Azure, Snowflake, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3871dec46927667b</t>
+          <t>https://www.indeed.com/viewjob?jk=87d9611a04bffadf</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (C#/Java/AI) - Underwriting Automation - Hybrid</t>
+          <t>Sr. Forward Deployed Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>LogicMonitor</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Data Modeling, ETL, Terraform</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f1adc20d8ab8b4a</t>
+          <t>https://www.indeed.com/viewjob?jk=92a2dfe6bebcb2dc</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (C#/Java/AI) - Underwriting Automation - Hybrid</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>FEED THE CHILDREN</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Spark, Scala, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86fdcdffd7cae712</t>
+          <t>https://www.indeed.com/viewjob?jk=3d4416990cb07c5b</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>ML-GenAI Engineer</t>
+          <t>Cloud Systems Engineer III</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Prodapt Solutions</t>
+          <t>Orange County's Credit Union</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Santa Ana, CA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Vertex AI, Scala, NoSQL, MLOps, MLflow, CI/CD</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Scala, ELT, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b71a1261fd024f4</t>
+          <t>https://www.indeed.com/viewjob?jk=37e9b523a42f1787</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Python Software Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Qureos</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Scala, Oracle, SQL Server, PostgreSQL, DynamoDB, CI/CD</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51db177a53e7ef14</t>
+          <t>https://www.indeed.com/viewjob?jk=3c91b09d863e5b13</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer II - Streaming</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>Rivian and Volkswagen Group Technologies</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, PostgreSQL, MySQL, Splunk, Maven</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Kafka Connect, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1d1f01448956ac8</t>
+          <t>https://www.indeed.com/viewjob?jk=3871dec46927667b</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Windows Engineer (Expert)</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>BAE Systems USA</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, PostgreSQL, MySQL, Splunk, Maven</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, Oracle, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c9d86fee622b07b</t>
+          <t>https://www.indeed.com/viewjob?jk=09ee1d1985ee70d9</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Analyst (Data Solutions)</t>
+          <t>Python Software Architect</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI, Tableau, Git</t>
+          <t>AWS, Glue, S3, RDS, Scala, Oracle, SQL Server, PostgreSQL, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60db44428bef76ed</t>
+          <t>https://www.indeed.com/viewjob?jk=51db177a53e7ef14</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Azure DevOps Architect</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>IPolarity LLC</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Whippany, NJ, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Glue, IAM, RDS, Azure, GCP, Scala, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, PostgreSQL, MySQL, Splunk, Maven</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=198e8bee7c6735a3</t>
+          <t>https://www.indeed.com/viewjob?jk=b1d1f01448956ac8</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Full Stack .NET Developer – C#, React, Azure/AWS</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>J2B GLOBAL LLC</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MongoDB, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, PostgreSQL, MySQL, Splunk, Maven</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ceec9a4f672d1616</t>
+          <t>https://www.indeed.com/viewjob?jk=5c9d86fee622b07b</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Java Engineer</t>
+          <t>Data Analyst (Data Solutions)</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>The Coca-Cola Company</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, MongoDB</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI, Tableau, Git</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9eed61967883578e</t>
+          <t>https://www.indeed.com/viewjob?jk=60db44428bef76ed</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Forward Deployed Data Engineer</t>
+          <t>Azure DevOps Architect</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>CoorsTek</t>
+          <t>IPolarity LLC</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Golden, CO, US USA</t>
+          <t>Whippany, NJ, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, Glue, IAM, RDS, Azure, GCP, Scala, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,32 +2666,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01c677c253d655bb</t>
+          <t>https://www.indeed.com/viewjob?jk=198e8bee7c6735a3</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Full Stack .NET Developer – C#, React, Azure/AWS</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Foley</t>
+          <t>J2B GLOBAL LLC</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Medallion Architecture, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MongoDB, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,32 +2701,32 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb528101e5b7e6f0</t>
+          <t>https://www.indeed.com/viewjob?jk=ceec9a4f672d1616</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>AI Solution Engineer</t>
+          <t>Senior Software Engineer (C#/Java/AI) - Underwriting Automation - Hybrid</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Agilify</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, Azure, Event Hubs, BigQuery, Scala, Kafka, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,32 +2736,32 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=173deae55fc0fc11</t>
+          <t>https://www.indeed.com/viewjob?jk=6f1adc20d8ab8b4a</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Network Engineer</t>
+          <t>Senior Software Engineer (C#/Java/AI) - Underwriting Automation - Hybrid</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Citizens</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Johnston, RI, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, CI/CD, Jenkins, Maven, Terraform, Docker, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93cf7434fe21677c</t>
+          <t>https://www.indeed.com/viewjob?jk=86fdcdffd7cae712</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Database Reliability Engineer</t>
+          <t>ML-GenAI Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Frontline Education</t>
+          <t>Prodapt Solutions</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Naperville, IL, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, ETL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Vertex AI, Scala, NoSQL, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03a470170ea48de6</t>
+          <t>https://www.indeed.com/viewjob?jk=1b71a1261fd024f4</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Database Reliability Engineer</t>
+          <t>Java Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Frontline Education</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, ETL, CI/CD, Terraform</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22e28cc34091c701</t>
+          <t>https://www.indeed.com/viewjob?jk=9eed61967883578e</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Database Reliability Engineer</t>
+          <t>Forward Deployed Data Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Frontline Education</t>
+          <t>CoorsTek</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Wayne, PA, US USA</t>
+          <t>Golden, CO, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, ETL, CI/CD, Terraform</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=406eb6619e461cdd</t>
+          <t>https://www.indeed.com/viewjob?jk=01c677c253d655bb</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>SR SOFTWARE ENGINEER</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Dollar General</t>
+          <t>Foley</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Goodlettsville, TN, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>S3, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, Cassandra, CI/CD, Docker</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Medallion Architecture, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbb1d7ed6fd57469</t>
+          <t>https://www.indeed.com/viewjob?jk=fb528101e5b7e6f0</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Software Engineer 3, Content Platforms</t>
+          <t>AI Solution Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Condé Nast</t>
+          <t>Agilify</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Kafka, PostgreSQL, MongoDB, Data Modeling, Splunk, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, S3, API Gateway, Azure, Event Hubs, BigQuery, Scala, Kafka, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d59c1e871e80877</t>
+          <t>https://www.indeed.com/viewjob?jk=173deae55fc0fc11</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Senior Network Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>EagleView</t>
+          <t>Citizens</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Johnston, RI, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, S3, RDS, Scala, CI/CD, Jenkins, Maven, Terraform, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eee26a905ec914aa</t>
+          <t>https://www.indeed.com/viewjob?jk=93cf7434fe21677c</t>
         </is>
       </c>
     </row>
@@ -3023,17 +3023,17 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Solution Architect – Data Migration &amp; Analytics</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>SpyCloud</t>
+          <t>Zensar Technologies</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Databricks, Spark, Scala, DynamoDB, ETL</t>
+          <t>AWS, Kinesis, S3, RDS, Data Lake Storage, Medallion Architecture, Scala, Snowflake, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a2f212e69e1f862</t>
+          <t>https://www.indeed.com/viewjob?jk=1f7b9a9c0a9082ee</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Database Reliability Engineer</t>
+          <t>FCCM Senior Consultant</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Frontline Education</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Wayne, PA, US USA</t>
+          <t>Iselin, NJ, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, ETL, CI/CD, Terraform</t>
+          <t>Spark, PySpark, Scala, Oracle, Data Modeling, ETL, CI/CD, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ca664998e6fb6c3</t>
+          <t>https://www.indeed.com/viewjob?jk=a3f4310b4c00f608</t>
         </is>
       </c>
     </row>
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae22c1a528cec63a</t>
+          <t>https://www.indeed.com/viewjob?jk=03a470170ea48de6</t>
         </is>
       </c>
     </row>
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97b21b525c894dd7</t>
+          <t>https://www.indeed.com/viewjob?jk=22e28cc34091c701</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Solution Architect – Data Migration &amp; Analytics</t>
+          <t>Senior Database Reliability Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Zensar Technologies</t>
+          <t>Frontline Education</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Wayne, PA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, RDS, Data Lake Storage, Medallion Architecture, Scala, Snowflake, Data Modeling, dbt</t>
+          <t>AWS, RDS, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, ETL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f7b9a9c0a9082ee</t>
+          <t>https://www.indeed.com/viewjob?jk=406eb6619e461cdd</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>FCCM Senior Consultant</t>
+          <t>SR SOFTWARE ENGINEER</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Dollar General</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Iselin, NJ, US USA</t>
+          <t>Goodlettsville, TN, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Spark, PySpark, Scala, Oracle, Data Modeling, ETL, CI/CD, Git, Python, SQL</t>
+          <t>S3, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, Cassandra, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3f4310b4c00f608</t>
+          <t>https://www.indeed.com/viewjob?jk=fbb1d7ed6fd57469</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer 3, Content Platforms</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>SpyCloud</t>
+          <t>Condé Nast</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Databricks, Spark, Scala, DynamoDB, ETL</t>
+          <t>AWS, Kafka, PostgreSQL, MongoDB, Data Modeling, Splunk, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b990fe917577735</t>
+          <t>https://www.indeed.com/viewjob?jk=1d59c1e871e80877</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Security Data Analyst - Parsing</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>SpyCloud</t>
+          <t>EagleView</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, API Gateway, RDS, Databricks, NoSQL, ETL, CI/CD</t>
+          <t>AWS, Lambda, S3, SQS, SNS, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=171de003fe5563fb</t>
+          <t>https://www.indeed.com/viewjob?jk=eee26a905ec914aa</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>MDM Integration Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>McLane Company</t>
+          <t>SpyCloud</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Temple, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, CI/CD, Terraform</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Databricks, Spark, Scala, DynamoDB, ETL</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,102 +3331,102 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3b598b8c3673649</t>
+          <t>https://www.indeed.com/viewjob?jk=8b990fe917577735</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Data Scientist / Senior Data Scientist (Risk Modeling)</t>
+          <t>Security Data Analyst - Parsing</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Berkshire Hathaway Specialty Insurance</t>
+          <t>SpyCloud</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Docker, Git, Python</t>
+          <t>AWS, Lambda, S3, SQS, API Gateway, RDS, Databricks, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c9e4130f1298022</t>
+          <t>https://www.indeed.com/viewjob?jk=171de003fe5563fb</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Data Scientist / Senior Data Scientist (Risk Modeling)</t>
+          <t>Senior Database Reliability Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Berkshire Hathaway Specialty Insurance</t>
+          <t>Frontline Education</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Wayne, PA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Docker, Git, Python</t>
+          <t>AWS, RDS, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, ETL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7f7784d943297ed</t>
+          <t>https://www.indeed.com/viewjob?jk=1ca664998e6fb6c3</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Senior Database Reliability Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Northwest Federal Credit Union</t>
+          <t>Frontline Education</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Naperville, IL, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, MySQL, Azure DevOps, Terraform, Azure Monitor</t>
+          <t>AWS, RDS, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, ETL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,32 +3436,32 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7291a950f8ec410d</t>
+          <t>https://www.indeed.com/viewjob?jk=ae22c1a528cec63a</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Software Engineer II - Platform Engineer/Databricks</t>
+          <t>Senior Database Reliability Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Frontline Education</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Jenkins, Maven, Terraform, Jenkins, Git</t>
+          <t>AWS, RDS, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, ETL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,32 +3471,32 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4448bee09655101c</t>
+          <t>https://www.indeed.com/viewjob?jk=97b21b525c894dd7</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>MDM Integration Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>State Street</t>
+          <t>McLane Company</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Quincy, MA, US USA</t>
+          <t>Temple, TX, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Splunk, CI/CD, Jenkins, Terraform, Jenkins</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb61fc433cd2352b</t>
+          <t>https://www.indeed.com/viewjob?jk=c3b598b8c3673649</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior MLOps Engineer I</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Zeitview</t>
+          <t>Northwest Federal Credit Union</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,34 +3531,34 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, PostgreSQL, MLOps, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, MySQL, Azure DevOps, Terraform, Azure Monitor</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c8710a47a6c9b4e</t>
+          <t>https://www.indeed.com/viewjob?jk=7291a950f8ec410d</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior MLOps Engineer I</t>
+          <t>Software Engineer II - Platform Engineer/Databricks</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Zeitview</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,34 +3566,34 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, PostgreSQL, MLOps, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Jenkins, Maven, Terraform, Jenkins, Git</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84de7dc9a3088a08</t>
+          <t>https://www.indeed.com/viewjob?jk=4448bee09655101c</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Karsun Solutions LLC</t>
+          <t>State Street</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Quincy, MA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Splunk, CI/CD, Jenkins, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f81c0ec4956c9db</t>
+          <t>https://www.indeed.com/viewjob?jk=eb61fc433cd2352b</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior R&amp;D Software Engineer, Fivetran AI</t>
+          <t>Data Scientist / Senior Data Scientist (Risk Modeling)</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Fivetran</t>
+          <t>Berkshire Hathaway Specialty Insurance</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,34 +3636,34 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, BigQuery, Snowflake, ETL, ELT, dbt, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Docker, Git, Python</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55c8e7c6018043d4</t>
+          <t>https://www.indeed.com/viewjob?jk=2c9e4130f1298022</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior R&amp;D Software Engineer, Fivetran AI</t>
+          <t>Data Scientist / Senior Data Scientist (Risk Modeling)</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Fivetran</t>
+          <t>Berkshire Hathaway Specialty Insurance</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,34 +3671,34 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, BigQuery, Snowflake, ETL, ELT, dbt, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Docker, Git, Python</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30bf0451dbc419d1</t>
+          <t>https://www.indeed.com/viewjob?jk=d7f7784d943297ed</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior R&amp;D Software Engineer, Fivetran AI</t>
+          <t>Senior .NET Developer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Fivetran</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, BigQuery, Snowflake, ETL, ELT, dbt, Docker</t>
+          <t>AWS, Lambda, ECS, Scala, Kafka, SQL Server, PostgreSQL, NoSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=501671e22555fe5c</t>
+          <t>https://www.indeed.com/viewjob?jk=35a2c65d6f2f7d06</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Senior R&amp;D Software Engineer, Fivetran AI</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Fivetran</t>
+          <t>Karsun Solutions LLC</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, BigQuery, Snowflake, ETL, ELT, dbt, Docker</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8b8baa922f2b05a</t>
+          <t>https://www.indeed.com/viewjob?jk=2f81c0ec4956c9db</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Sr Devops Engineer</t>
+          <t>Senior Architect</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>_coderio</t>
+          <t>Mass General Brigham</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Somerville, MA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=541df4abc8320b5a</t>
+          <t>https://www.indeed.com/viewjob?jk=dccbfd697359c720</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Senior .NET Developer</t>
+          <t>Senior Software Engineer IV / V (Java, React, AWS)</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Auto.Live</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, Scala, Kafka, SQL Server, PostgreSQL, NoSQL, Data Modeling, CI/CD</t>
+          <t>AWS, SQS, Scala, Kafka, MySQL, CI/CD, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35a2c65d6f2f7d06</t>
+          <t>https://www.indeed.com/viewjob?jk=42c2207352100be0</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Senior Architect</t>
+          <t>Senior Engineer, Corp Solutions</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Mass General Brigham</t>
+          <t>Papa John's</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Somerville, MA, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>RDS, Google Cloud Platform, GCP, CI/CD, Jenkins, Maven, Kubernetes, Jenkins, Git, Bitbucket</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dccbfd697359c720</t>
+          <t>https://www.indeed.com/viewjob?jk=6ae25ca0f2bd81f6</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Senior Software Engineer IV / V (Java, React, AWS)</t>
+          <t>Senior Amazon Connect Application Architect</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Auto.Live</t>
+          <t>TELUS Digital</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, SQS, Scala, Kafka, MySQL, CI/CD, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, Lambda, Kinesis, S3, RDS, Scala, DynamoDB, CI/CD, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42c2207352100be0</t>
+          <t>https://www.indeed.com/viewjob?jk=feceaa7f623de4d6</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Senior Engineer, Corp Solutions</t>
+          <t>Senior Amazon Connect Application Architect</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Papa John's</t>
+          <t>TELUS Digital</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, CI/CD, Jenkins, Maven, Kubernetes, Jenkins, Git, Bitbucket</t>
+          <t>AWS, Lambda, Kinesis, S3, RDS, Scala, DynamoDB, CI/CD, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ae25ca0f2bd81f6</t>
+          <t>https://www.indeed.com/viewjob?jk=ef89c4f9800f8a90</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=feceaa7f623de4d6</t>
+          <t>https://www.indeed.com/viewjob?jk=5fc58207e473b9f5</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef89c4f9800f8a90</t>
+          <t>https://www.indeed.com/viewjob?jk=1f8bb981d509050f</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Charlottesville, VA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5fc58207e473b9f5</t>
+          <t>https://www.indeed.com/viewjob?jk=4b3612752c893190</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Senior Amazon Connect Application Architect</t>
+          <t>Senior Software Engineer ( Seattle/Provo)</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>TELUS Digital</t>
+          <t>Press Ganey</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Provo, UT, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, RDS, Scala, DynamoDB, CI/CD, Terraform, AWS CloudFormation</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, Data Modeling, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f8bb981d509050f</t>
+          <t>https://www.indeed.com/viewjob?jk=1b27efa8ed4a1f97</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Senior Amazon Connect Application Architect</t>
+          <t>Senior MLOps Engineer I</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>TELUS Digital</t>
+          <t>Zeitview</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Charlottesville, VA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,34 +4091,34 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, RDS, Scala, DynamoDB, CI/CD, Terraform, AWS CloudFormation</t>
+          <t>AWS, RDS, Scala, PostgreSQL, MLOps, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b3612752c893190</t>
+          <t>https://www.indeed.com/viewjob?jk=5c8710a47a6c9b4e</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Senior Software Engineer ( Seattle/Provo)</t>
+          <t>Senior MLOps Engineer I</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Press Ganey</t>
+          <t>Zeitview</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Provo, UT, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,34 +4126,34 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, Data Modeling, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Scala, PostgreSQL, MLOps, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b27efa8ed4a1f97</t>
+          <t>https://www.indeed.com/viewjob?jk=84de7dc9a3088a08</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>AI Software Engineer IV</t>
+          <t>Senior R&amp;D Software Engineer, Fivetran AI</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>The Standard Insurance</t>
+          <t>Fivetran</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, MLflow, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Databricks, GCP, BigQuery, Snowflake, ETL, ELT, dbt, Docker</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3c232645c82fc83</t>
+          <t>https://www.indeed.com/viewjob?jk=55c8e7c6018043d4</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Sr. Business Intelligence Engineer</t>
+          <t>Senior R&amp;D Software Engineer, Fivetran AI</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Crane Worldwide Logistics</t>
+          <t>Fivetran</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Snowflake, Data Modeling, dbt, Power BI, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Databricks, GCP, BigQuery, Snowflake, ETL, ELT, dbt, Docker</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,24 +4206,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53344a199a269470</t>
+          <t>https://www.indeed.com/viewjob?jk=30bf0451dbc419d1</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Software Engineer- Greensboro, NC</t>
+          <t>Senior R&amp;D Software Engineer, Fivetran AI</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Stake Center Locating</t>
+          <t>Fivetran</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Greensboro, NC, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, SQL Server, ETL, ELT, Power BI, Git</t>
+          <t>AWS, RDS, Databricks, GCP, BigQuery, Snowflake, ETL, ELT, dbt, Docker</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,24 +4241,24 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c8332d54e7fcd1c</t>
+          <t>https://www.indeed.com/viewjob?jk=501671e22555fe5c</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior R&amp;D Software Engineer, Fivetran AI</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Qureos</t>
+          <t>Fivetran</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Docker, Git</t>
+          <t>AWS, RDS, Databricks, GCP, BigQuery, Snowflake, ETL, ELT, dbt, Docker</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,24 +4276,24 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad6582003e647074</t>
+          <t>https://www.indeed.com/viewjob?jk=f8b8baa922f2b05a</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Database Developer</t>
+          <t>Sr Devops Engineer</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Hollstadt Consulting</t>
+          <t>_coderio</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>RDS, Azure, Spark, PySpark, SQL Server, Data Modeling, ETL, Power BI, Jenkins, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,24 +4311,24 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdef6e08804da8cc</t>
+          <t>https://www.indeed.com/viewjob?jk=541df4abc8320b5a</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Database Developer (Contractor) - MNSITE-3762</t>
+          <t>AI Software Engineer IV</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>RE/SPEC Inc</t>
+          <t>The Standard Insurance</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>RDS, Azure, Spark, PySpark, SQL Server, Data Modeling, ETL, Power BI, Jenkins, Azure DevOps</t>
+          <t>RDS, Azure, Databricks, Scala, MLflow, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,24 +4346,24 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bac2143c91f124e3</t>
+          <t>https://www.indeed.com/viewjob?jk=b3c232645c82fc83</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>AI &amp; Machine Learning Engineer</t>
+          <t>Sr. Business Intelligence Engineer</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>OneBlood</t>
+          <t>Crane Worldwide Logistics</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Saint Petersburg, FL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,15 +4371,190 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, Snowflake, Data Modeling, dbt, Power BI, CI/CD, GitHub Actions, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=53344a199a269470</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Software Engineer- Greensboro, NC</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Stake Center Locating</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Greensboro, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, SQL Server, ETL, ELT, Power BI, Git</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2c8332d54e7fcd1c</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Qureos</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Louisville, KY, US USA</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Docker, Git</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ad6582003e647074</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Database Developer</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Hollstadt Consulting</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>MN, US USA</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Spark, PySpark, SQL Server, Data Modeling, ETL, Power BI, Jenkins, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bdef6e08804da8cc</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Database Developer (Contractor) - MNSITE-3762</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>RE/SPEC Inc</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Saint Paul, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Spark, PySpark, SQL Server, Data Modeling, ETL, Power BI, Jenkins, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bac2143c91f124e3</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>AI &amp; Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>OneBlood</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Saint Petersburg, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
           <t>AWS, Azure, Medallion Architecture, ETL, ELT, CI/CD, Git, Python, SQL, R</t>
         </is>
       </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
-      <c r="G113" t="inlineStr">
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=9242f2d7ab83418a</t>
         </is>

--- a/results/job_matches_2026-07-21.xlsx
+++ b/results/job_matches_2026-07-21.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G118"/>
+  <dimension ref="A1:G115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,17 +608,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AWS Cloud</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Rippling</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, ECS, IAM, RDS, Scala</t>
+          <t>IAM, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Event Hubs, Spark, PySpark</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42e3c5912b49c237</t>
+          <t>https://www.indeed.com/viewjob?jk=07c6726c35ad8fa5</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>AWS Cloud</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Rippling</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Event Hubs, Spark, PySpark</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07c6726c35ad8fa5</t>
+          <t>https://www.indeed.com/viewjob?jk=42e3c5912b49c237</t>
         </is>
       </c>
     </row>
@@ -783,17 +783,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Digital Pathology (Hybrid)</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Mayo Clinic</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Rochester, MN, US USA</t>
+          <t>Bridgewater, NJ, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, Hive, Spark, Kafka, Snowflake, ELT, Power BI, Tableau, DataOps</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Hadoop, Hive, Spark, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=761b34bda9b68b66</t>
+          <t>https://www.indeed.com/viewjob?jk=7567cb365890dc6b</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Data Engineer - Digital Pathology (Hybrid)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>Mayo Clinic</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Bridgewater, NJ, US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Hadoop, Hive, Spark, Scala</t>
+          <t>Google Cloud Platform, GCP, Hive, Spark, Kafka, Snowflake, ELT, Power BI, Tableau, DataOps</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=177a0dfa7a7c2758</t>
+          <t>https://www.indeed.com/viewjob?jk=761b34bda9b68b66</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Technical Architect</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>REI Systems</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sterling, VA, US USA</t>
+          <t>Bridgewater, NJ, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, ECS, IAM, RDS, Scala, Oracle, DynamoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Hadoop, Hive, Spark, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=175f2d223e3312d6</t>
+          <t>https://www.indeed.com/viewjob?jk=177a0dfa7a7c2758</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Architect (Azure + Databricks)</t>
+          <t>Senior Technical Architect</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Nine Core Technologies</t>
+          <t>REI Systems</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Milpitas, CA, US USA</t>
+          <t>Sterling, VA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Medallion Architecture, GCP</t>
+          <t>AWS, Lambda, API Gateway, ECS, IAM, RDS, Scala, Oracle, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=118ef7e12d0743d7</t>
+          <t>https://www.indeed.com/viewjob?jk=175f2d223e3312d6</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Software Engineer III - Data/Payments Technology</t>
+          <t>Data Architect (Azure + Databricks)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Nine Core Technologies</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Milpitas, CA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Scala, Kafka, Snowflake, Oracle</t>
+          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Medallion Architecture, GCP</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8366ecb2495ecb5</t>
+          <t>https://www.indeed.com/viewjob?jk=118ef7e12d0743d7</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Software Engineer III - Data/Payments Technology</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Hunt Military Communities</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Azure, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,67 +986,67 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29325c8c8e335924</t>
+          <t>https://www.indeed.com/viewjob?jk=c8366ecb2495ecb5</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Engineer II - (Remote)</t>
+          <t>Senior Data Engineer - ITS4</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Fanatics Betting &amp; Gaming</t>
+          <t>State of Minnesota - Minnesota IT Services</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Databricks, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
+          <t>AWS, Glue, S3, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54fa68f69cf2083f</t>
+          <t>https://www.indeed.com/viewjob?jk=1054e208948fd6fb</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CrossCountry Mortgage, LLC</t>
+          <t>Hunt Military Communities</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, RDS, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Azure, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26d0c8a6b975fef0</t>
+          <t>https://www.indeed.com/viewjob?jk=29325c8c8e335924</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Java Application Architect</t>
+          <t>Data Engineer II - (Remote)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Fanatics Betting &amp; Gaming</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, S3, RDS, Databricks, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06adce66e837b3b3</t>
+          <t>https://www.indeed.com/viewjob?jk=54fa68f69cf2083f</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Modeler</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>VeeRteq Solutions Inc.</t>
+          <t>CrossCountry Mortgage, LLC</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Hadoop, Scala, Snowflake, Databricks Lakehouse, Oracle</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, RDS, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99058f5a757f5431</t>
+          <t>https://www.indeed.com/viewjob?jk=26d0c8a6b975fef0</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Reporting Engineer</t>
+          <t>Java Application Architect</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Hitachi Rail</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MySQL, Star Schema, Fact Tables, Dimension Tables</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7504d94e8707d02b</t>
+          <t>https://www.indeed.com/viewjob?jk=06adce66e837b3b3</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Solutions Engineer - HYBRID/NC RESIDENTS ONLY</t>
+          <t>Reporting Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>PowerSecure Inc.</t>
+          <t>Hitachi Rail</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala</t>
+          <t>AWS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MySQL, Star Schema, Fact Tables, Dimension Tables</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc9b66f689cbeefb</t>
+          <t>https://www.indeed.com/viewjob?jk=7504d94e8707d02b</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Reporting Engineer</t>
+          <t>Data Solutions Engineer - HYBRID/NC RESIDENTS ONLY</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Hitachi Energy</t>
+          <t>PowerSecure Inc.</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MySQL, Star Schema, Fact Tables, Dimension Tables</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59ef3d85179316f9</t>
+          <t>https://www.indeed.com/viewjob?jk=dc9b66f689cbeefb</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Reporting Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Bloomerang</t>
+          <t>Hitachi Energy</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, Google Cloud Platform, BigQuery, Scala, Snowflake, PostgreSQL, MySQL</t>
+          <t>AWS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MySQL, Star Schema, Fact Tables, Dimension Tables</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0eff179e948461c2</t>
+          <t>https://www.indeed.com/viewjob?jk=59ef3d85179316f9</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Software Engineering LMTS</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Bloomerang</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, NoSQL</t>
+          <t>AWS, Redshift, RDS, Databricks, Google Cloud Platform, BigQuery, Scala, Snowflake, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=572e8633b0661a80</t>
+          <t>https://www.indeed.com/viewjob?jk=0eff179e948461c2</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Databricks Architect</t>
+          <t>AI Native Developer- EST</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Confiz</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Bentonville, AR, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,42 +1326,42 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Google Cloud Platform, Cloud Storage, Spark, PySpark</t>
+          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18be742c481fa20b</t>
+          <t>https://www.indeed.com/viewjob?jk=37e94025d78d00b3</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Software Engineer III : AI/ML Solutions</t>
+          <t>Software Engineering LMTS</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7bc806520585d5fd</t>
+          <t>https://www.indeed.com/viewjob?jk=572e8633b0661a80</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Cloud Solutions Engineer – Azure</t>
+          <t>Databricks Architect</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Confiz</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bentonville, AR, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Google Cloud Platform, Cloud Storage, Spark, PySpark</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc23fc3c19075d7c</t>
+          <t>https://www.indeed.com/viewjob?jk=18be742c481fa20b</t>
         </is>
       </c>
     </row>
@@ -1448,17 +1448,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Software Engineering Intern</t>
+          <t>Software Engineer III : AI/ML Solutions</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Copart, Inc</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7bf2ebcfa4a5f5e</t>
+          <t>https://www.indeed.com/viewjob?jk=7bc806520585d5fd</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior AI Security Automation Engineer</t>
+          <t>Cloud Solutions Engineer – Azure</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>State Street</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Quincy, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1063ffb870d53611</t>
+          <t>https://www.indeed.com/viewjob?jk=dc23fc3c19075d7c</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Sr. SW Engineer</t>
+          <t>Senior AI Security Automation Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>State Street</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Foster City, CA, US USA</t>
+          <t>Quincy, MA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, Data Modeling, ETL, Splunk, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, ELT</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f774d387b35a5b8</t>
+          <t>https://www.indeed.com/viewjob?jk=1063ffb870d53611</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Salesforce Business Systems Analyst</t>
+          <t>Software Engineering Intern</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Copart, Inc</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb817b0533864176</t>
+          <t>https://www.indeed.com/viewjob?jk=c7bf2ebcfa4a5f5e</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Salesforce Business Systems Analyst</t>
+          <t>Sr. SW Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Foster City, CA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, Data Modeling, ETL, Splunk, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b799aca0d95f271</t>
+          <t>https://www.indeed.com/viewjob?jk=8f774d387b35a5b8</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Salesforce Business Systems Analyst</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Bridgewater, NJ, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d193f030168c94d0</t>
+          <t>https://www.indeed.com/viewjob?jk=cb817b0533864176</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Big Data Engineer</t>
+          <t>Salesforce Business Systems Analyst</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Highmark Health</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Hive, Spark, Scala, Kafka, Oracle</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d94c95081afe04c8</t>
+          <t>https://www.indeed.com/viewjob?jk=7b799aca0d95f271</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer with Sales Incentive Compensation (SIC)</t>
+          <t>Big Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>UNIFY SOLUTIONS INC</t>
+          <t>Highmark Health</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, GCP, Scala</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Hive, Spark, Scala, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb057adb6c59f5ff</t>
+          <t>https://www.indeed.com/viewjob?jk=d94c95081afe04c8</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Solution Architect - Java/J2EE</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>PNC Financial Services Group</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Farmers Branch, TX, US USA</t>
+          <t>Bridgewater, NJ, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MongoDB, Cassandra</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a23b5c57a47b265</t>
+          <t>https://www.indeed.com/viewjob?jk=786fbdb63698b11b</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Software Architect - Java/Spring Boot/Kafka</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>PNC Financial Services Group</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Bridgewater, NJ, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MongoDB, Cassandra</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f929c4ac83ec17b7</t>
+          <t>https://www.indeed.com/viewjob?jk=d193f030168c94d0</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Software Engineering SMTS</t>
+          <t>Databricks Data Engineer with Sales Incentive Compensation (SIC)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>UNIFY SOLUTIONS INC</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, GCP, Scala</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98a642ee513df5f7</t>
+          <t>https://www.indeed.com/viewjob?jk=eb057adb6c59f5ff</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Software Engineering SMTS</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>NetApp</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Morrisville, NC, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0844aea628b28dab</t>
+          <t>https://www.indeed.com/viewjob?jk=98a642ee513df5f7</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Specialist Software Engineer</t>
+          <t>Senior Solution Architect - Java/J2EE</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>PNC Financial Services Group</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Farmers Branch, TX, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, RDS, Azure, Databricks, Scala, Oracle, SQL Server</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31c5d5f535a77ad9</t>
+          <t>https://www.indeed.com/viewjob?jk=3a23b5c57a47b265</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>LoopNet - Software Engineer II</t>
+          <t>Software Architect - Java/Spring Boot/Kafka</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>CoStar Group</t>
+          <t>PNC Financial Services Group</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, Databricks, BigQuery, Scala, Kafka, Snowflake, MySQL, DynamoDB</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51f6585eaae3edd6</t>
+          <t>https://www.indeed.com/viewjob?jk=f929c4ac83ec17b7</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>AI &amp; Data Engineer, Data Discovery Services</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Bristol Myers Squibb</t>
+          <t>NetApp</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Morrisville, NC, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, ECS, RDS, Azure, Databricks, Vertex AI</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,67 +1966,67 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9331d42b3835041a</t>
+          <t>https://www.indeed.com/viewjob?jk=0844aea628b28dab</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Databricks Platform Engineer</t>
+          <t>Specialist Software Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Confiz</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Bentonville, AR, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Google Cloud Platform, Spark, Scala, ELT, CI/CD</t>
+          <t>AWS, Lambda, Redshift, S3, RDS, Azure, Databricks, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b713352ad723441</t>
+          <t>https://www.indeed.com/viewjob?jk=31c5d5f535a77ad9</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data Bricks Data Engineer</t>
+          <t>LoopNet - Software Engineer II</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Bavel systems LLP</t>
+          <t>CoStar Group</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, GCP, Scala, Kafka</t>
+          <t>AWS, S3, SQS, Databricks, BigQuery, Scala, Kafka, Snowflake, MySQL, DynamoDB</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d997e2a6aa4fbed</t>
+          <t>https://www.indeed.com/viewjob?jk=51f6585eaae3edd6</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Informatica Cloud Data Engineer (IDMC/IICS)</t>
+          <t>AI &amp; Data Engineer, Data Discovery Services</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Bristol Myers Squibb</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Snowflake, Oracle, Data Modeling, ETL</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, ECS, RDS, Azure, Databricks, Vertex AI</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2526f9ca235bb42c</t>
+          <t>https://www.indeed.com/viewjob?jk=9331d42b3835041a</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Informatica Cloud Data Engineer (IDMC/IICS)</t>
+          <t>Databricks Platform Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Confiz</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Bentonville, AR, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Snowflake, Oracle, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Google Cloud Platform, Spark, Scala, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f156bc316e4a8e1e</t>
+          <t>https://www.indeed.com/viewjob?jk=5b713352ad723441</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Java Product Engineer</t>
+          <t>Data Bricks Data Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Diaconia, LLC.</t>
+          <t>Bavel systems LLP</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, Oracle, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
+          <t>AWS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, GCP, Scala, Kafka</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed19f7417f9c2e59</t>
+          <t>https://www.indeed.com/viewjob?jk=2d997e2a6aa4fbed</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Full Stack</t>
+          <t>Informatica Cloud Data Engineer (IDMC/IICS)</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Hopkins, MN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB, Cassandra</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Snowflake, Oracle, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=caea23a7afe82982</t>
+          <t>https://www.indeed.com/viewjob?jk=2526f9ca235bb42c</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Full Stack</t>
+          <t>Informatica Cloud Data Engineer (IDMC/IICS)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,17 +2201,17 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB, Cassandra</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Snowflake, Oracle, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c6c9dc97e7a8c55</t>
+          <t>https://www.indeed.com/viewjob?jk=f156bc316e4a8e1e</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Brookfield, WI, US USA</t>
+          <t>Hopkins, MN, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97ef6349d26627c1</t>
+          <t>https://www.indeed.com/viewjob?jk=caea23a7afe82982</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Azure, Snowflake, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87d9611a04bffadf</t>
+          <t>https://www.indeed.com/viewjob?jk=2c6c9dc97e7a8c55</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer</t>
+          <t>Senior Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>LogicMonitor</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Brookfield, WI, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Data Modeling, ETL, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92a2dfe6bebcb2dc</t>
+          <t>https://www.indeed.com/viewjob?jk=97ef6349d26627c1</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Java Product Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>FEED THE CHILDREN</t>
+          <t>Diaconia, LLC.</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Spark, Scala, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, Azure, Scala, Kafka, Oracle, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d4416990cb07c5b</t>
+          <t>https://www.indeed.com/viewjob?jk=ed19f7417f9c2e59</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Cloud Systems Engineer III</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Orange County's Credit Union</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Santa Ana, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, Scala, ELT, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Azure, Snowflake, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37e9b523a42f1787</t>
+          <t>https://www.indeed.com/viewjob?jk=87d9611a04bffadf</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Forward Deployed Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Qureos</t>
+          <t>LogicMonitor</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Data Modeling, ETL, Terraform</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,32 +2421,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c91b09d863e5b13</t>
+          <t>https://www.indeed.com/viewjob?jk=92a2dfe6bebcb2dc</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Software Engineer II - Streaming</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Rivian and Volkswagen Group Technologies</t>
+          <t>FEED THE CHILDREN</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Kafka Connect, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Spark, Scala, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3871dec46927667b</t>
+          <t>https://www.indeed.com/viewjob?jk=3d4416990cb07c5b</t>
         </is>
       </c>
     </row>
@@ -2498,17 +2498,17 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Python Software Architect</t>
+          <t>Cloud Systems Engineer III</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Orange County's Credit Union</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Santa Ana, CA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Scala, Oracle, SQL Server, PostgreSQL, DynamoDB, CI/CD</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Scala, ELT, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51db177a53e7ef14</t>
+          <t>https://www.indeed.com/viewjob?jk=37e9b523a42f1787</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>Qureos</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, PostgreSQL, MySQL, Splunk, Maven</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1d1f01448956ac8</t>
+          <t>https://www.indeed.com/viewjob?jk=3c91b09d863e5b13</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer II - Streaming</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>Rivian and Volkswagen Group Technologies</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, PostgreSQL, MySQL, Splunk, Maven</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Kafka Connect, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c9d86fee622b07b</t>
+          <t>https://www.indeed.com/viewjob?jk=3871dec46927667b</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Data Analyst (Data Solutions)</t>
+          <t>Senior Software Engineer (C#/Java/AI) - Underwriting Automation - Hybrid</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI, Tableau, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60db44428bef76ed</t>
+          <t>https://www.indeed.com/viewjob?jk=6f1adc20d8ab8b4a</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Azure DevOps Architect</t>
+          <t>Senior Software Engineer (C#/Java/AI) - Underwriting Automation - Hybrid</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>IPolarity LLC</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Whippany, NJ, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Glue, IAM, RDS, Azure, GCP, Scala, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=198e8bee7c6735a3</t>
+          <t>https://www.indeed.com/viewjob?jk=86fdcdffd7cae712</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Full Stack .NET Developer – C#, React, Azure/AWS</t>
+          <t>ML-GenAI Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>J2B GLOBAL LLC</t>
+          <t>Prodapt Solutions</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MongoDB, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Vertex AI, Scala, NoSQL, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ceec9a4f672d1616</t>
+          <t>https://www.indeed.com/viewjob?jk=1b71a1261fd024f4</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (C#/Java/AI) - Underwriting Automation - Hybrid</t>
+          <t>Python Software Architect</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL</t>
+          <t>AWS, Glue, S3, RDS, Scala, Oracle, SQL Server, PostgreSQL, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f1adc20d8ab8b4a</t>
+          <t>https://www.indeed.com/viewjob?jk=51db177a53e7ef14</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (C#/Java/AI) - Underwriting Automation - Hybrid</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, PostgreSQL, MySQL, Splunk, Maven</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86fdcdffd7cae712</t>
+          <t>https://www.indeed.com/viewjob?jk=b1d1f01448956ac8</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>ML-GenAI Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Prodapt Solutions</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Vertex AI, Scala, NoSQL, MLOps, MLflow, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, PostgreSQL, MySQL, Splunk, Maven</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b71a1261fd024f4</t>
+          <t>https://www.indeed.com/viewjob?jk=5c9d86fee622b07b</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Java Engineer</t>
+          <t>Data Analyst (Data Solutions)</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>The Coca-Cola Company</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, MongoDB</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI, Tableau, Git</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9eed61967883578e</t>
+          <t>https://www.indeed.com/viewjob?jk=60db44428bef76ed</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Forward Deployed Data Engineer</t>
+          <t>Azure DevOps Architect</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>CoorsTek</t>
+          <t>IPolarity LLC</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Golden, CO, US USA</t>
+          <t>Whippany, NJ, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, Glue, IAM, RDS, Azure, GCP, Scala, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,32 +2876,32 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01c677c253d655bb</t>
+          <t>https://www.indeed.com/viewjob?jk=198e8bee7c6735a3</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Java Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Foley</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Medallion Architecture, Scala, Data Modeling, ETL</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,32 +2911,32 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb528101e5b7e6f0</t>
+          <t>https://www.indeed.com/viewjob?jk=9eed61967883578e</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>AI Solution Engineer</t>
+          <t>Full Stack .NET Developer – C#, React, Azure/AWS</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Agilify</t>
+          <t>J2B GLOBAL LLC</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, Azure, Event Hubs, BigQuery, Scala, Kafka, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MongoDB, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=173deae55fc0fc11</t>
+          <t>https://www.indeed.com/viewjob?jk=ceec9a4f672d1616</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Network Engineer</t>
+          <t>Forward Deployed Data Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Citizens</t>
+          <t>CoorsTek</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Johnston, RI, US USA</t>
+          <t>Golden, CO, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, CI/CD, Jenkins, Maven, Terraform, Docker, Jenkins</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93cf7434fe21677c</t>
+          <t>https://www.indeed.com/viewjob?jk=01c677c253d655bb</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Sr. Database Administrator</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Vertafore</t>
+          <t>Foley</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, Terraform, Git</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Medallion Architecture, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=652e6c19792a8b61</t>
+          <t>https://www.indeed.com/viewjob?jk=fb528101e5b7e6f0</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Solution Architect – Data Migration &amp; Analytics</t>
+          <t>AI Solution Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Zensar Technologies</t>
+          <t>Agilify</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, RDS, Data Lake Storage, Medallion Architecture, Scala, Snowflake, Data Modeling, dbt</t>
+          <t>AWS, S3, API Gateway, Azure, Event Hubs, BigQuery, Scala, Kafka, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f7b9a9c0a9082ee</t>
+          <t>https://www.indeed.com/viewjob?jk=173deae55fc0fc11</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>FCCM Senior Consultant</t>
+          <t>Senior Network Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Citizens</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Iselin, NJ, US USA</t>
+          <t>Johnston, RI, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Spark, PySpark, Scala, Oracle, Data Modeling, ETL, CI/CD, Git, Python, SQL</t>
+          <t>AWS, S3, RDS, Scala, CI/CD, Jenkins, Maven, Terraform, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3f4310b4c00f608</t>
+          <t>https://www.indeed.com/viewjob?jk=93cf7434fe21677c</t>
         </is>
       </c>
     </row>
@@ -3268,17 +3268,17 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Sr. Database Administrator</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>EagleView</t>
+          <t>Vertafore</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Redshift, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, Terraform, Git</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eee26a905ec914aa</t>
+          <t>https://www.indeed.com/viewjob?jk=652e6c19792a8b61</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Solution Architect – Data Migration &amp; Analytics</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>SpyCloud</t>
+          <t>Zensar Technologies</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Databricks, Spark, Scala, DynamoDB, ETL</t>
+          <t>AWS, Kinesis, S3, RDS, Data Lake Storage, Medallion Architecture, Scala, Snowflake, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,14 +3331,14 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b990fe917577735</t>
+          <t>https://www.indeed.com/viewjob?jk=1f7b9a9c0a9082ee</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Security Data Analyst - Parsing</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, API Gateway, RDS, Databricks, NoSQL, ETL, CI/CD</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Databricks, Spark, Scala, DynamoDB, ETL</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=171de003fe5563fb</t>
+          <t>https://www.indeed.com/viewjob?jk=8b990fe917577735</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Database Reliability Engineer</t>
+          <t>Security Data Analyst - Parsing</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Frontline Education</t>
+          <t>SpyCloud</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Wayne, PA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, ETL, CI/CD, Terraform</t>
+          <t>AWS, Lambda, S3, SQS, API Gateway, RDS, Databricks, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ca664998e6fb6c3</t>
+          <t>https://www.indeed.com/viewjob?jk=171de003fe5563fb</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Database Reliability Engineer</t>
+          <t>MDM Integration Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Frontline Education</t>
+          <t>McLane Company</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Naperville, IL, US USA</t>
+          <t>Temple, TX, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, ETL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,77 +3436,77 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae22c1a528cec63a</t>
+          <t>https://www.indeed.com/viewjob?jk=c3b598b8c3673649</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Database Reliability Engineer</t>
+          <t>Data Scientist / Senior Data Scientist (Risk Modeling)</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Frontline Education</t>
+          <t>Berkshire Hathaway Specialty Insurance</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, ETL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Docker, Git, Python</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97b21b525c894dd7</t>
+          <t>https://www.indeed.com/viewjob?jk=2c9e4130f1298022</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>MDM Integration Engineer</t>
+          <t>Data Scientist / Senior Data Scientist (Risk Modeling)</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>McLane Company</t>
+          <t>Berkshire Hathaway Specialty Insurance</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Temple, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Docker, Git, Python</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3b598b8c3673649</t>
+          <t>https://www.indeed.com/viewjob?jk=d7f7784d943297ed</t>
         </is>
       </c>
     </row>
@@ -3618,17 +3618,17 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Data Scientist / Senior Data Scientist (Risk Modeling)</t>
+          <t>Senior MLOps Engineer I</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Berkshire Hathaway Specialty Insurance</t>
+          <t>Zeitview</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,34 +3636,34 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Docker, Git, Python</t>
+          <t>AWS, RDS, Scala, PostgreSQL, MLOps, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c9e4130f1298022</t>
+          <t>https://www.indeed.com/viewjob?jk=5c8710a47a6c9b4e</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Data Scientist / Senior Data Scientist (Risk Modeling)</t>
+          <t>Senior MLOps Engineer I</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Berkshire Hathaway Specialty Insurance</t>
+          <t>Zeitview</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,34 +3671,34 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Docker, Git, Python</t>
+          <t>AWS, RDS, Scala, PostgreSQL, MLOps, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7f7784d943297ed</t>
+          <t>https://www.indeed.com/viewjob?jk=84de7dc9a3088a08</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior .NET Developer</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Karsun Solutions LLC</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, Scala, Kafka, SQL Server, PostgreSQL, NoSQL, Data Modeling, CI/CD</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35a2c65d6f2f7d06</t>
+          <t>https://www.indeed.com/viewjob?jk=2f81c0ec4956c9db</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>Senior .NET Developer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Karsun Solutions LLC</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, ECS, Scala, Kafka, SQL Server, PostgreSQL, NoSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f81c0ec4956c9db</t>
+          <t>https://www.indeed.com/viewjob?jk=35a2c65d6f2f7d06</t>
         </is>
       </c>
     </row>
@@ -4073,17 +4073,17 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Senior MLOps Engineer I</t>
+          <t>Sr Devops Engineer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Zeitview</t>
+          <t>_coderio</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,34 +4091,34 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, PostgreSQL, MLOps, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c8710a47a6c9b4e</t>
+          <t>https://www.indeed.com/viewjob?jk=541df4abc8320b5a</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Senior MLOps Engineer I</t>
+          <t>AI Software Engineer IV</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Zeitview</t>
+          <t>The Standard Insurance</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,34 +4126,34 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, PostgreSQL, MLOps, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Scala, MLflow, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84de7dc9a3088a08</t>
+          <t>https://www.indeed.com/viewjob?jk=b3c232645c82fc83</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Senior R&amp;D Software Engineer, Fivetran AI</t>
+          <t>Sr. Business Intelligence Engineer</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Fivetran</t>
+          <t>Crane Worldwide Logistics</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, BigQuery, Snowflake, ETL, ELT, dbt, Docker</t>
+          <t>AWS, RDS, Azure, Snowflake, Data Modeling, dbt, Power BI, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55c8e7c6018043d4</t>
+          <t>https://www.indeed.com/viewjob?jk=53344a199a269470</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Senior R&amp;D Software Engineer, Fivetran AI</t>
+          <t>Software Engineer- Greensboro, NC</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Fivetran</t>
+          <t>Stake Center Locating</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Greensboro, NC, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, BigQuery, Snowflake, ETL, ELT, dbt, Docker</t>
+          <t>Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, SQL Server, ETL, ELT, Power BI, Git</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30bf0451dbc419d1</t>
+          <t>https://www.indeed.com/viewjob?jk=2c8332d54e7fcd1c</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=501671e22555fe5c</t>
+          <t>https://www.indeed.com/viewjob?jk=55c8e7c6018043d4</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4276,24 +4276,24 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8b8baa922f2b05a</t>
+          <t>https://www.indeed.com/viewjob?jk=30bf0451dbc419d1</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Sr Devops Engineer</t>
+          <t>Senior R&amp;D Software Engineer, Fivetran AI</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>_coderio</t>
+          <t>Fivetran</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Databricks, GCP, BigQuery, Snowflake, ETL, ELT, dbt, Docker</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,24 +4311,24 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=541df4abc8320b5a</t>
+          <t>https://www.indeed.com/viewjob?jk=501671e22555fe5c</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>AI Software Engineer IV</t>
+          <t>Senior R&amp;D Software Engineer, Fivetran AI</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>The Standard Insurance</t>
+          <t>Fivetran</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, MLflow, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Databricks, GCP, BigQuery, Snowflake, ETL, ELT, dbt, Docker</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,24 +4346,24 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3c232645c82fc83</t>
+          <t>https://www.indeed.com/viewjob?jk=f8b8baa922f2b05a</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Sr. Business Intelligence Engineer</t>
+          <t>Database Developer</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Crane Worldwide Logistics</t>
+          <t>Hollstadt Consulting</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Snowflake, Data Modeling, dbt, Power BI, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>RDS, Azure, Spark, PySpark, SQL Server, Data Modeling, ETL, Power BI, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,24 +4381,24 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53344a199a269470</t>
+          <t>https://www.indeed.com/viewjob?jk=bdef6e08804da8cc</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Software Engineer- Greensboro, NC</t>
+          <t>Database Developer (Contractor) - MNSITE-3762</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Stake Center Locating</t>
+          <t>RE/SPEC Inc</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Greensboro, NC, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, SQL Server, ETL, ELT, Power BI, Git</t>
+          <t>RDS, Azure, Spark, PySpark, SQL Server, Data Modeling, ETL, Power BI, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,24 +4416,24 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c8332d54e7fcd1c</t>
+          <t>https://www.indeed.com/viewjob?jk=bac2143c91f124e3</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>AI &amp; Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Qureos</t>
+          <t>OneBlood</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Saint Petersburg, FL, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Docker, Git</t>
+          <t>AWS, Azure, Medallion Architecture, ETL, ELT, CI/CD, Git, Python, SQL, R</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4450,111 +4450,6 @@
         </is>
       </c>
       <c r="G115" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ad6582003e647074</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>Database Developer</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>Hollstadt Consulting</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>MN, US USA</t>
-        </is>
-      </c>
-      <c r="D116" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Spark, PySpark, SQL Server, Data Modeling, ETL, Power BI, Jenkins, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=bdef6e08804da8cc</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>Database Developer (Contractor) - MNSITE-3762</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>RE/SPEC Inc</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>Saint Paul, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D117" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Spark, PySpark, SQL Server, Data Modeling, ETL, Power BI, Jenkins, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=bac2143c91f124e3</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>AI &amp; Machine Learning Engineer</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>OneBlood</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>Saint Petersburg, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D118" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Medallion Architecture, ETL, ELT, CI/CD, Git, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
-      <c r="G118" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=9242f2d7ab83418a</t>
         </is>

--- a/results/job_matches_2026-07-21.xlsx
+++ b/results/job_matches_2026-07-21.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G115"/>
+  <dimension ref="A1:G117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,17 +608,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>AWS Cloud</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Rippling</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Event Hubs, Spark, PySpark</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,14 +636,14 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07c6726c35ad8fa5</t>
+          <t>https://www.indeed.com/viewjob?jk=42e3c5912b49c237</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AWS Cloud</t>
+          <t>AWS Solutions Architect</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42e3c5912b49c237</t>
+          <t>https://www.indeed.com/viewjob?jk=cf903a5bb459577f</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AWS Solutions Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>CrossCountry Mortgage, LLC</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, ECS, IAM, RDS, Scala</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, RDS, Azure, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf903a5bb459577f</t>
+          <t>https://www.indeed.com/viewjob?jk=704b1f0ab6bff192</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Azure Databricks Architect Healthcare Payer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CrossCountry Mortgage, LLC</t>
+          <t>VeeRteq Solutions Inc.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, RDS, Azure, GCP, Spark, PySpark</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Hadoop, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=704b1f0ab6bff192</t>
+          <t>https://www.indeed.com/viewjob?jk=5652d49391bd82a2</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Azure Databricks Architect Healthcare Payer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>VeeRteq Solutions Inc.</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Bridgewater, NJ, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Hadoop, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Hadoop, Hive, Spark, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5652d49391bd82a2</t>
+          <t>https://www.indeed.com/viewjob?jk=7567cb365890dc6b</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Data Engineer - Digital Pathology (Hybrid)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>Mayo Clinic</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Bridgewater, NJ, US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Hadoop, Hive, Spark, Scala</t>
+          <t>Google Cloud Platform, GCP, Hive, Spark, Kafka, Snowflake, ELT, Power BI, Tableau, DataOps</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7567cb365890dc6b</t>
+          <t>https://www.indeed.com/viewjob?jk=761b34bda9b68b66</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Digital Pathology (Hybrid)</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Mayo Clinic</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Rochester, MN, US USA</t>
+          <t>Bridgewater, NJ, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, Hive, Spark, Kafka, Snowflake, ELT, Power BI, Tableau, DataOps</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Hadoop, Hive, Spark, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=761b34bda9b68b66</t>
+          <t>https://www.indeed.com/viewjob?jk=177a0dfa7a7c2758</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Technical Architect</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>REI Systems</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Bridgewater, NJ, US USA</t>
+          <t>Sterling, VA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Hadoop, Hive, Spark, Scala</t>
+          <t>AWS, Lambda, API Gateway, ECS, IAM, RDS, Scala, Oracle, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=177a0dfa7a7c2758</t>
+          <t>https://www.indeed.com/viewjob?jk=175f2d223e3312d6</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Technical Architect</t>
+          <t>Data Architect (Azure + Databricks)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>REI Systems</t>
+          <t>Nine Core Technologies</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Sterling, VA, US USA</t>
+          <t>Milpitas, CA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, ECS, IAM, RDS, Scala, Oracle, DynamoDB, NoSQL</t>
+          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Medallion Architecture, GCP</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=175f2d223e3312d6</t>
+          <t>https://www.indeed.com/viewjob?jk=118ef7e12d0743d7</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Architect (Azure + Databricks)</t>
+          <t>Software Engineer III - Data/Payments Technology</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Nine Core Technologies</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Milpitas, CA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Medallion Architecture, GCP</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=118ef7e12d0743d7</t>
+          <t>https://www.indeed.com/viewjob?jk=c8366ecb2495ecb5</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Software Engineer III - Data/Payments Technology</t>
+          <t>Senior Data Engineer - ITS4</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>State of Minnesota - Minnesota IT Services</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,34 +976,34 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Scala, Kafka, Snowflake, Oracle</t>
+          <t>AWS, Glue, S3, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8366ecb2495ecb5</t>
+          <t>https://www.indeed.com/viewjob?jk=1054e208948fd6fb</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - ITS4</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>State of Minnesota - Minnesota IT Services</t>
+          <t>Hunt Military Communities</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,42 +1011,42 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Azure, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1054e208948fd6fb</t>
+          <t>https://www.indeed.com/viewjob?jk=29325c8c8e335924</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Data Engineer II - (Remote)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Hunt Military Communities</t>
+          <t>Fanatics Betting &amp; Gaming</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Azure, Scala</t>
+          <t>AWS, S3, RDS, Databricks, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29325c8c8e335924</t>
+          <t>https://www.indeed.com/viewjob?jk=54fa68f69cf2083f</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Engineer II - (Remote)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Fanatics Betting &amp; Gaming</t>
+          <t>CrossCountry Mortgage, LLC</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Databricks, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, RDS, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54fa68f69cf2083f</t>
+          <t>https://www.indeed.com/viewjob?jk=26d0c8a6b975fef0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Java Application Architect</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>CrossCountry Mortgage, LLC</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, RDS, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26d0c8a6b975fef0</t>
+          <t>https://www.indeed.com/viewjob?jk=06adce66e837b3b3</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Java Application Architect</t>
+          <t>Reporting Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Hitachi Rail</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MySQL, Star Schema, Fact Tables, Dimension Tables</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06adce66e837b3b3</t>
+          <t>https://www.indeed.com/viewjob?jk=7504d94e8707d02b</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Reporting Engineer</t>
+          <t>Data Solutions Engineer - HYBRID/NC RESIDENTS ONLY</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Hitachi Rail</t>
+          <t>PowerSecure Inc.</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MySQL, Star Schema, Fact Tables, Dimension Tables</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7504d94e8707d02b</t>
+          <t>https://www.indeed.com/viewjob?jk=dc9b66f689cbeefb</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Solutions Engineer - HYBRID/NC RESIDENTS ONLY</t>
+          <t>Reporting Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>PowerSecure Inc.</t>
+          <t>Hitachi Energy</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala</t>
+          <t>AWS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MySQL, Star Schema, Fact Tables, Dimension Tables</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc9b66f689cbeefb</t>
+          <t>https://www.indeed.com/viewjob?jk=59ef3d85179316f9</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Reporting Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Hitachi Energy</t>
+          <t>Bloomerang</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MySQL, Star Schema, Fact Tables, Dimension Tables</t>
+          <t>AWS, Redshift, RDS, Databricks, Google Cloud Platform, BigQuery, Scala, Snowflake, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,19 +1266,19 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59ef3d85179316f9</t>
+          <t>https://www.indeed.com/viewjob?jk=0eff179e948461c2</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Native Developer- EST</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Bloomerang</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, Google Cloud Platform, BigQuery, Scala, Snowflake, PostgreSQL, MySQL</t>
+          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0eff179e948461c2</t>
+          <t>https://www.indeed.com/viewjob?jk=37e94025d78d00b3</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>AI Native Developer- EST</t>
+          <t>Software Engineering LMTS</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,34 +1326,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37e94025d78d00b3</t>
+          <t>https://www.indeed.com/viewjob?jk=572e8633b0661a80</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Software Engineering LMTS</t>
+          <t>Databricks Architect</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Confiz</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Bentonville, AR, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Google Cloud Platform, Cloud Storage, Spark, PySpark</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=572e8633b0661a80</t>
+          <t>https://www.indeed.com/viewjob?jk=18be742c481fa20b</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Databricks Architect</t>
+          <t>Sr. Data Engineer (HYBRID)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Confiz</t>
+          <t>Equinox</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Bentonville, AR, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Google Cloud Platform, Cloud Storage, Spark, PySpark</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, Scala, DynamoDB, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18be742c481fa20b</t>
+          <t>https://www.indeed.com/viewjob?jk=22216c34e7397891</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer (HYBRID)</t>
+          <t>Cloud Solutions Engineer – Azure</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Equinox</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, Scala, DynamoDB, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22216c34e7397891</t>
+          <t>https://www.indeed.com/viewjob?jk=dc23fc3c19075d7c</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Software Engineer III : AI/ML Solutions</t>
+          <t>Senior AI Security Automation Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>State Street</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Quincy, MA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, ELT</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7bc806520585d5fd</t>
+          <t>https://www.indeed.com/viewjob?jk=1063ffb870d53611</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Cloud Solutions Engineer – Azure</t>
+          <t>Software Engineering Intern</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Copart, Inc</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc23fc3c19075d7c</t>
+          <t>https://www.indeed.com/viewjob?jk=c7bf2ebcfa4a5f5e</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior AI Security Automation Engineer</t>
+          <t>Sr. SW Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>State Street</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Quincy, MA, US USA</t>
+          <t>Foster City, CA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, ELT</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, Data Modeling, ETL, Splunk, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1063ffb870d53611</t>
+          <t>https://www.indeed.com/viewjob?jk=8f774d387b35a5b8</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Software Engineering Intern</t>
+          <t>Salesforce Business Systems Analyst</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Copart, Inc</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7bf2ebcfa4a5f5e</t>
+          <t>https://www.indeed.com/viewjob?jk=cb817b0533864176</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Sr. SW Engineer</t>
+          <t>Salesforce Business Systems Analyst</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Foster City, CA, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, Data Modeling, ETL, Splunk, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f774d387b35a5b8</t>
+          <t>https://www.indeed.com/viewjob?jk=7b799aca0d95f271</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Salesforce Business Systems Analyst</t>
+          <t>Big Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Highmark Health</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Hive, Spark, Scala, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb817b0533864176</t>
+          <t>https://www.indeed.com/viewjob?jk=d94c95081afe04c8</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Salesforce Business Systems Analyst</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Bridgewater, NJ, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b799aca0d95f271</t>
+          <t>https://www.indeed.com/viewjob?jk=786fbdb63698b11b</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Big Data Engineer</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Highmark Health</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>Bridgewater, NJ, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Hive, Spark, Scala, Kafka, Oracle</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d94c95081afe04c8</t>
+          <t>https://www.indeed.com/viewjob?jk=d193f030168c94d0</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Databricks Data Engineer with Sales Incentive Compensation (SIC)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>UNIFY SOLUTIONS INC</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Bridgewater, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, GCP, Scala</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=786fbdb63698b11b</t>
+          <t>https://www.indeed.com/viewjob?jk=eb057adb6c59f5ff</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Senior Solution Architect - Java/J2EE</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>PNC Financial Services Group</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Bridgewater, NJ, US USA</t>
+          <t>Farmers Branch, TX, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d193f030168c94d0</t>
+          <t>https://www.indeed.com/viewjob?jk=3a23b5c57a47b265</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer with Sales Incentive Compensation (SIC)</t>
+          <t>Software Architect - Java/Spring Boot/Kafka</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>UNIFY SOLUTIONS INC</t>
+          <t>PNC Financial Services Group</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, GCP, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb057adb6c59f5ff</t>
+          <t>https://www.indeed.com/viewjob?jk=f929c4ac83ec17b7</t>
         </is>
       </c>
     </row>
@@ -1868,17 +1868,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Solution Architect - Java/J2EE</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>PNC Financial Services Group</t>
+          <t>NetApp</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Farmers Branch, TX, US USA</t>
+          <t>Morrisville, NC, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MongoDB, Cassandra</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a23b5c57a47b265</t>
+          <t>https://www.indeed.com/viewjob?jk=0844aea628b28dab</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Software Architect - Java/Spring Boot/Kafka</t>
+          <t>Specialist Software Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>PNC Financial Services Group</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MongoDB, Cassandra</t>
+          <t>AWS, Lambda, Redshift, S3, RDS, Azure, Databricks, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f929c4ac83ec17b7</t>
+          <t>https://www.indeed.com/viewjob?jk=31c5d5f535a77ad9</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>LoopNet - Software Engineer II</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>NetApp</t>
+          <t>CoStar Group</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Morrisville, NC, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, S3, SQS, Databricks, BigQuery, Scala, Kafka, Snowflake, MySQL, DynamoDB</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,67 +1966,67 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0844aea628b28dab</t>
+          <t>https://www.indeed.com/viewjob?jk=51f6585eaae3edd6</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Specialist Software Engineer</t>
+          <t>AI &amp; Data Engineer, Data Discovery Services</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Bristol Myers Squibb</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, RDS, Azure, Databricks, Scala, Oracle, SQL Server</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, ECS, RDS, Azure, Databricks, Vertex AI</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31c5d5f535a77ad9</t>
+          <t>https://www.indeed.com/viewjob?jk=9331d42b3835041a</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>LoopNet - Software Engineer II</t>
+          <t>Databricks Platform Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>CoStar Group</t>
+          <t>Confiz</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Bentonville, AR, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, Databricks, BigQuery, Scala, Kafka, Snowflake, MySQL, DynamoDB</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Google Cloud Platform, Spark, Scala, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51f6585eaae3edd6</t>
+          <t>https://www.indeed.com/viewjob?jk=5b713352ad723441</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>AI &amp; Data Engineer, Data Discovery Services</t>
+          <t>Data Bricks Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Bristol Myers Squibb</t>
+          <t>Bavel systems LLP</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, ECS, RDS, Azure, Databricks, Vertex AI</t>
+          <t>AWS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, GCP, Scala, Kafka</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9331d42b3835041a</t>
+          <t>https://www.indeed.com/viewjob?jk=2d997e2a6aa4fbed</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Databricks Platform Engineer</t>
+          <t>Informatica Cloud Data Engineer (IDMC/IICS)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Confiz</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Bentonville, AR, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Google Cloud Platform, Spark, Scala, ELT, CI/CD</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Snowflake, Oracle, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b713352ad723441</t>
+          <t>https://www.indeed.com/viewjob?jk=2526f9ca235bb42c</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Bricks Data Engineer</t>
+          <t>Informatica Cloud Data Engineer (IDMC/IICS)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Bavel systems LLP</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, GCP, Scala, Kafka</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Snowflake, Oracle, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d997e2a6aa4fbed</t>
+          <t>https://www.indeed.com/viewjob?jk=f156bc316e4a8e1e</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Informatica Cloud Data Engineer (IDMC/IICS)</t>
+          <t>Senior Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Hopkins, MN, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Snowflake, Oracle, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2526f9ca235bb42c</t>
+          <t>https://www.indeed.com/viewjob?jk=caea23a7afe82982</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Informatica Cloud Data Engineer (IDMC/IICS)</t>
+          <t>Senior Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,17 +2201,17 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Snowflake, Oracle, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f156bc316e4a8e1e</t>
+          <t>https://www.indeed.com/viewjob?jk=2c6c9dc97e7a8c55</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Hopkins, MN, US USA</t>
+          <t>Brookfield, WI, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=caea23a7afe82982</t>
+          <t>https://www.indeed.com/viewjob?jk=97ef6349d26627c1</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Full Stack</t>
+          <t>Java Product Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Diaconia, LLC.</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB, Cassandra</t>
+          <t>AWS, Azure, Scala, Kafka, Oracle, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c6c9dc97e7a8c55</t>
+          <t>https://www.indeed.com/viewjob?jk=ed19f7417f9c2e59</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Full Stack</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Brookfield, WI, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB, Cassandra</t>
+          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Azure, Snowflake, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97ef6349d26627c1</t>
+          <t>https://www.indeed.com/viewjob?jk=87d9611a04bffadf</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Java Product Engineer</t>
+          <t>Sr. Forward Deployed Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Diaconia, LLC.</t>
+          <t>LogicMonitor</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, Oracle, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Data Modeling, ETL, Terraform</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed19f7417f9c2e59</t>
+          <t>https://www.indeed.com/viewjob?jk=92a2dfe6bebcb2dc</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>FEED THE CHILDREN</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Azure, Snowflake, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Spark, Scala, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87d9611a04bffadf</t>
+          <t>https://www.indeed.com/viewjob?jk=3d4416990cb07c5b</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer</t>
+          <t>Windows Engineer (Expert)</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>LogicMonitor</t>
+          <t>BAE Systems USA</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Data Modeling, ETL, Terraform</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, Oracle, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,32 +2421,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92a2dfe6bebcb2dc</t>
+          <t>https://www.indeed.com/viewjob?jk=09ee1d1985ee70d9</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Cloud Systems Engineer III</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>FEED THE CHILDREN</t>
+          <t>Orange County's Credit Union</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Santa Ana, CA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Spark, Scala, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Scala, ELT, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d4416990cb07c5b</t>
+          <t>https://www.indeed.com/viewjob?jk=37e9b523a42f1787</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Windows Engineer (Expert)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>BAE Systems USA</t>
+          <t>Qureos</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, Oracle, Splunk, CI/CD</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09ee1d1985ee70d9</t>
+          <t>https://www.indeed.com/viewjob?jk=3c91b09d863e5b13</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Cloud Systems Engineer III</t>
+          <t>Software Engineer II - Streaming</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Orange County's Credit Union</t>
+          <t>Rivian and Volkswagen Group Technologies</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Santa Ana, CA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, Scala, ELT, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Kafka Connect, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37e9b523a42f1787</t>
+          <t>https://www.indeed.com/viewjob?jk=3871dec46927667b</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer (C#/Java/AI) - Underwriting Automation - Hybrid</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Qureos</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c91b09d863e5b13</t>
+          <t>https://www.indeed.com/viewjob?jk=6f1adc20d8ab8b4a</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Software Engineer II - Streaming</t>
+          <t>Senior Software Engineer (C#/Java/AI) - Underwriting Automation - Hybrid</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Rivian and Volkswagen Group Technologies</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Kafka Connect, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3871dec46927667b</t>
+          <t>https://www.indeed.com/viewjob?jk=86fdcdffd7cae712</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (C#/Java/AI) - Underwriting Automation - Hybrid</t>
+          <t>ML-GenAI Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Prodapt Solutions</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Vertex AI, Scala, NoSQL, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f1adc20d8ab8b4a</t>
+          <t>https://www.indeed.com/viewjob?jk=1b71a1261fd024f4</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (C#/Java/AI) - Underwriting Automation - Hybrid</t>
+          <t>Python Software Architect</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL</t>
+          <t>AWS, Glue, S3, RDS, Scala, Oracle, SQL Server, PostgreSQL, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86fdcdffd7cae712</t>
+          <t>https://www.indeed.com/viewjob?jk=51db177a53e7ef14</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>ML-GenAI Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Prodapt Solutions</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Vertex AI, Scala, NoSQL, MLOps, MLflow, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, PostgreSQL, MySQL, Splunk, Maven</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b71a1261fd024f4</t>
+          <t>https://www.indeed.com/viewjob?jk=b1d1f01448956ac8</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Python Software Architect</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Scala, Oracle, SQL Server, PostgreSQL, DynamoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, PostgreSQL, MySQL, Splunk, Maven</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51db177a53e7ef14</t>
+          <t>https://www.indeed.com/viewjob?jk=5c9d86fee622b07b</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Analyst (Data Solutions)</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>The Coca-Cola Company</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, PostgreSQL, MySQL, Splunk, Maven</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI, Tableau, Git</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1d1f01448956ac8</t>
+          <t>https://www.indeed.com/viewjob?jk=60db44428bef76ed</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Azure DevOps Architect</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>IPolarity LLC</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Whippany, NJ, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, PostgreSQL, MySQL, Splunk, Maven</t>
+          <t>AWS, Glue, IAM, RDS, Azure, GCP, Scala, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c9d86fee622b07b</t>
+          <t>https://www.indeed.com/viewjob?jk=198e8bee7c6735a3</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Analyst (Data Solutions)</t>
+          <t>Java Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI, Tableau, Git</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60db44428bef76ed</t>
+          <t>https://www.indeed.com/viewjob?jk=9eed61967883578e</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Azure DevOps Architect</t>
+          <t>Full Stack .NET Developer – C#, React, Azure/AWS</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>IPolarity LLC</t>
+          <t>J2B GLOBAL LLC</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Whippany, NJ, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Glue, IAM, RDS, Azure, GCP, Scala, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MongoDB, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,32 +2876,32 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=198e8bee7c6735a3</t>
+          <t>https://www.indeed.com/viewjob?jk=ceec9a4f672d1616</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Java Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, MongoDB</t>
+          <t>AWS, Google Cloud Platform, GCP, Hadoop, Scala, Snowflake, ETL, ELT, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,32 +2911,32 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9eed61967883578e</t>
+          <t>https://www.indeed.com/viewjob?jk=6c875e063114bb1c</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Full Stack .NET Developer – C#, React, Azure/AWS</t>
+          <t>Forward Deployed Data Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>J2B GLOBAL LLC</t>
+          <t>CoorsTek</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Golden, CO, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MongoDB, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ceec9a4f672d1616</t>
+          <t>https://www.indeed.com/viewjob?jk=01c677c253d655bb</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Forward Deployed Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>CoorsTek</t>
+          <t>Foley</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Golden, CO, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Medallion Architecture, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01c677c253d655bb</t>
+          <t>https://www.indeed.com/viewjob?jk=fb528101e5b7e6f0</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI Solution Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Foley</t>
+          <t>Agilify</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Medallion Architecture, Scala, Data Modeling, ETL</t>
+          <t>AWS, S3, API Gateway, Azure, Event Hubs, BigQuery, Scala, Kafka, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb528101e5b7e6f0</t>
+          <t>https://www.indeed.com/viewjob?jk=173deae55fc0fc11</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>AI Solution Engineer</t>
+          <t>Senior Network Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Agilify</t>
+          <t>Citizens</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Johnston, RI, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, Azure, Event Hubs, BigQuery, Scala, Kafka, CI/CD, GitHub Actions</t>
+          <t>AWS, S3, RDS, Scala, CI/CD, Jenkins, Maven, Terraform, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=173deae55fc0fc11</t>
+          <t>https://www.indeed.com/viewjob?jk=93cf7434fe21677c</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Network Engineer</t>
+          <t>Senior Database Reliability Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Citizens</t>
+          <t>Frontline Education</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Johnston, RI, US USA</t>
+          <t>Naperville, IL, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, CI/CD, Jenkins, Maven, Terraform, Docker, Jenkins</t>
+          <t>AWS, RDS, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, ETL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93cf7434fe21677c</t>
+          <t>https://www.indeed.com/viewjob?jk=03a470170ea48de6</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Naperville, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03a470170ea48de6</t>
+          <t>https://www.indeed.com/viewjob?jk=22e28cc34091c701</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Wayne, PA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22e28cc34091c701</t>
+          <t>https://www.indeed.com/viewjob?jk=406eb6619e461cdd</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Database Reliability Engineer</t>
+          <t>SR SOFTWARE ENGINEER</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Frontline Education</t>
+          <t>Dollar General</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Wayne, PA, US USA</t>
+          <t>Goodlettsville, TN, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, ETL, CI/CD, Terraform</t>
+          <t>S3, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, Cassandra, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=406eb6619e461cdd</t>
+          <t>https://www.indeed.com/viewjob?jk=fbb1d7ed6fd57469</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>SR SOFTWARE ENGINEER</t>
+          <t>Software Engineer 3, Content Platforms</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Dollar General</t>
+          <t>Condé Nast</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Goodlettsville, TN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>S3, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, Cassandra, CI/CD, Docker</t>
+          <t>AWS, Kafka, PostgreSQL, MongoDB, Data Modeling, Splunk, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbb1d7ed6fd57469</t>
+          <t>https://www.indeed.com/viewjob?jk=1d59c1e871e80877</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Software Engineer 3, Content Platforms</t>
+          <t>Sr. Database Administrator</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Condé Nast</t>
+          <t>Vertafore</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Kafka, PostgreSQL, MongoDB, Data Modeling, Splunk, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Redshift, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, Terraform, Git</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d59c1e871e80877</t>
+          <t>https://www.indeed.com/viewjob?jk=652e6c19792a8b61</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Sr. Database Administrator</t>
+          <t>Solution Architect – Data Migration &amp; Analytics</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Vertafore</t>
+          <t>Zensar Technologies</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, Terraform, Git</t>
+          <t>AWS, Kinesis, S3, RDS, Data Lake Storage, Medallion Architecture, Scala, Snowflake, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=652e6c19792a8b61</t>
+          <t>https://www.indeed.com/viewjob?jk=1f7b9a9c0a9082ee</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Solution Architect – Data Migration &amp; Analytics</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Zensar Technologies</t>
+          <t>SpyCloud</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, RDS, Data Lake Storage, Medallion Architecture, Scala, Snowflake, Data Modeling, dbt</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Databricks, Spark, Scala, DynamoDB, ETL</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,14 +3331,14 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f7b9a9c0a9082ee</t>
+          <t>https://www.indeed.com/viewjob?jk=8b990fe917577735</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Security Data Analyst - Parsing</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Databricks, Spark, Scala, DynamoDB, ETL</t>
+          <t>AWS, Lambda, S3, SQS, API Gateway, RDS, Databricks, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b990fe917577735</t>
+          <t>https://www.indeed.com/viewjob?jk=589dd47eef0f8740</t>
         </is>
       </c>
     </row>
@@ -3443,17 +3443,17 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Data Scientist / Senior Data Scientist (Risk Modeling)</t>
+          <t>Generative AI Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Berkshire Hathaway Specialty Insurance</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,29 +3461,29 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Docker, Git, Python</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Vertex AI, Hadoop, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c9e4130f1298022</t>
+          <t>https://www.indeed.com/viewjob?jk=4413ec7a4b00d4ae</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Data Scientist / Senior Data Scientist (Risk Modeling)</t>
+          <t>Generative AI Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Berkshire Hathaway Specialty Insurance</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3496,34 +3496,34 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Docker, Git, Python</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Vertex AI, Hadoop, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7f7784d943297ed</t>
+          <t>https://www.indeed.com/viewjob?jk=3e48a5b4af545b7e</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Data Scientist / Senior Data Scientist (Risk Modeling)</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Northwest Federal Credit Union</t>
+          <t>Berkshire Hathaway Specialty Insurance</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,34 +3531,34 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, MySQL, Azure DevOps, Terraform, Azure Monitor</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Docker, Git, Python</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7291a950f8ec410d</t>
+          <t>https://www.indeed.com/viewjob?jk=2c9e4130f1298022</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Software Engineer II - Platform Engineer/Databricks</t>
+          <t>Data Scientist / Senior Data Scientist (Risk Modeling)</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Berkshire Hathaway Specialty Insurance</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,34 +3566,34 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Jenkins, Maven, Terraform, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Docker, Git, Python</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4448bee09655101c</t>
+          <t>https://www.indeed.com/viewjob?jk=d7f7784d943297ed</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>State Street</t>
+          <t>Northwest Federal Credit Union</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Quincy, MA, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Splunk, CI/CD, Jenkins, Terraform, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, MySQL, Azure DevOps, Terraform, Azure Monitor</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb61fc433cd2352b</t>
+          <t>https://www.indeed.com/viewjob?jk=7291a950f8ec410d</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior MLOps Engineer I</t>
+          <t>Software Engineer II - Platform Engineer/Databricks</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Zeitview</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,34 +3636,34 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, PostgreSQL, MLOps, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Jenkins, Maven, Terraform, Jenkins, Git</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c8710a47a6c9b4e</t>
+          <t>https://www.indeed.com/viewjob?jk=4448bee09655101c</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior MLOps Engineer I</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Zeitview</t>
+          <t>State Street</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Quincy, MA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,34 +3671,34 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, PostgreSQL, MLOps, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Splunk, CI/CD, Jenkins, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84de7dc9a3088a08</t>
+          <t>https://www.indeed.com/viewjob?jk=eb61fc433cd2352b</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>Senior MLOps Engineer I</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Karsun Solutions LLC</t>
+          <t>Zeitview</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,34 +3706,34 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Scala, PostgreSQL, MLOps, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f81c0ec4956c9db</t>
+          <t>https://www.indeed.com/viewjob?jk=5c8710a47a6c9b4e</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Senior .NET Developer</t>
+          <t>Senior MLOps Engineer I</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Zeitview</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,34 +3741,34 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, Scala, Kafka, SQL Server, PostgreSQL, NoSQL, Data Modeling, CI/CD</t>
+          <t>AWS, RDS, Scala, PostgreSQL, MLOps, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35a2c65d6f2f7d06</t>
+          <t>https://www.indeed.com/viewjob?jk=84de7dc9a3088a08</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Senior Architect</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Mass General Brigham</t>
+          <t>Karsun Solutions LLC</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Somerville, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dccbfd697359c720</t>
+          <t>https://www.indeed.com/viewjob?jk=2f81c0ec4956c9db</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Senior Software Engineer IV / V (Java, React, AWS)</t>
+          <t>Senior .NET Developer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Auto.Live</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, SQS, Scala, Kafka, MySQL, CI/CD, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, Lambda, ECS, Scala, Kafka, SQL Server, PostgreSQL, NoSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42c2207352100be0</t>
+          <t>https://www.indeed.com/viewjob?jk=35a2c65d6f2f7d06</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Senior Engineer, Corp Solutions</t>
+          <t>Senior Architect</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Papa John's</t>
+          <t>Mass General Brigham</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Somerville, MA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, CI/CD, Jenkins, Maven, Kubernetes, Jenkins, Git, Bitbucket</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ae25ca0f2bd81f6</t>
+          <t>https://www.indeed.com/viewjob?jk=dccbfd697359c720</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Senior Amazon Connect Application Architect</t>
+          <t>Senior Software Engineer IV / V (Java, React, AWS)</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>TELUS Digital</t>
+          <t>Auto.Live</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, RDS, Scala, DynamoDB, CI/CD, Terraform, AWS CloudFormation</t>
+          <t>AWS, SQS, Scala, Kafka, MySQL, CI/CD, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=feceaa7f623de4d6</t>
+          <t>https://www.indeed.com/viewjob?jk=42c2207352100be0</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Senior Amazon Connect Application Architect</t>
+          <t>Senior Engineer, Corp Solutions</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>TELUS Digital</t>
+          <t>Papa John's</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, RDS, Scala, DynamoDB, CI/CD, Terraform, AWS CloudFormation</t>
+          <t>RDS, Google Cloud Platform, GCP, CI/CD, Jenkins, Maven, Kubernetes, Jenkins, Git, Bitbucket</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef89c4f9800f8a90</t>
+          <t>https://www.indeed.com/viewjob?jk=6ae25ca0f2bd81f6</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5fc58207e473b9f5</t>
+          <t>https://www.indeed.com/viewjob?jk=feceaa7f623de4d6</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f8bb981d509050f</t>
+          <t>https://www.indeed.com/viewjob?jk=ef89c4f9800f8a90</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Charlottesville, VA, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b3612752c893190</t>
+          <t>https://www.indeed.com/viewjob?jk=5fc58207e473b9f5</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Senior Software Engineer ( Seattle/Provo)</t>
+          <t>Senior Amazon Connect Application Architect</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Press Ganey</t>
+          <t>TELUS Digital</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Provo, UT, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, Data Modeling, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, Kinesis, S3, RDS, Scala, DynamoDB, CI/CD, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b27efa8ed4a1f97</t>
+          <t>https://www.indeed.com/viewjob?jk=1f8bb981d509050f</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Sr Devops Engineer</t>
+          <t>Senior Amazon Connect Application Architect</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>_coderio</t>
+          <t>TELUS Digital</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Charlottesville, VA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, Lambda, Kinesis, S3, RDS, Scala, DynamoDB, CI/CD, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=541df4abc8320b5a</t>
+          <t>https://www.indeed.com/viewjob?jk=4b3612752c893190</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>AI Software Engineer IV</t>
+          <t>Senior Software Engineer ( Seattle/Provo)</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>The Standard Insurance</t>
+          <t>Press Ganey</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Provo, UT, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, MLflow, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, Data Modeling, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3c232645c82fc83</t>
+          <t>https://www.indeed.com/viewjob?jk=1b27efa8ed4a1f97</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Sr. Business Intelligence Engineer</t>
+          <t>Sr Devops Engineer</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Crane Worldwide Logistics</t>
+          <t>_coderio</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Snowflake, Data Modeling, dbt, Power BI, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53344a199a269470</t>
+          <t>https://www.indeed.com/viewjob?jk=541df4abc8320b5a</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Software Engineer- Greensboro, NC</t>
+          <t>AI Software Engineer IV</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Stake Center Locating</t>
+          <t>The Standard Insurance</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Greensboro, NC, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, SQL Server, ETL, ELT, Power BI, Git</t>
+          <t>RDS, Azure, Databricks, Scala, MLflow, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,24 +4206,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c8332d54e7fcd1c</t>
+          <t>https://www.indeed.com/viewjob?jk=b3c232645c82fc83</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Senior R&amp;D Software Engineer, Fivetran AI</t>
+          <t>Sr. Business Intelligence Engineer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Fivetran</t>
+          <t>Crane Worldwide Logistics</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, BigQuery, Snowflake, ETL, ELT, dbt, Docker</t>
+          <t>AWS, RDS, Azure, Snowflake, Data Modeling, dbt, Power BI, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,24 +4241,24 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55c8e7c6018043d4</t>
+          <t>https://www.indeed.com/viewjob?jk=53344a199a269470</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Senior R&amp;D Software Engineer, Fivetran AI</t>
+          <t>Software Engineer- Greensboro, NC</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Fivetran</t>
+          <t>Stake Center Locating</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Greensboro, NC, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, BigQuery, Snowflake, ETL, ELT, dbt, Docker</t>
+          <t>Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, SQL Server, ETL, ELT, Power BI, Git</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30bf0451dbc419d1</t>
+          <t>https://www.indeed.com/viewjob?jk=2c8332d54e7fcd1c</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=501671e22555fe5c</t>
+          <t>https://www.indeed.com/viewjob?jk=55c8e7c6018043d4</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4346,24 +4346,24 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8b8baa922f2b05a</t>
+          <t>https://www.indeed.com/viewjob?jk=30bf0451dbc419d1</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Database Developer</t>
+          <t>Senior R&amp;D Software Engineer, Fivetran AI</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Hollstadt Consulting</t>
+          <t>Fivetran</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>RDS, Azure, Spark, PySpark, SQL Server, Data Modeling, ETL, Power BI, Jenkins, Azure DevOps</t>
+          <t>AWS, RDS, Databricks, GCP, BigQuery, Snowflake, ETL, ELT, dbt, Docker</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,24 +4381,24 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdef6e08804da8cc</t>
+          <t>https://www.indeed.com/viewjob?jk=501671e22555fe5c</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Database Developer (Contractor) - MNSITE-3762</t>
+          <t>Senior R&amp;D Software Engineer, Fivetran AI</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>RE/SPEC Inc</t>
+          <t>Fivetran</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>RDS, Azure, Spark, PySpark, SQL Server, Data Modeling, ETL, Power BI, Jenkins, Azure DevOps</t>
+          <t>AWS, RDS, Databricks, GCP, BigQuery, Snowflake, ETL, ELT, dbt, Docker</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,24 +4416,24 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bac2143c91f124e3</t>
+          <t>https://www.indeed.com/viewjob?jk=f8b8baa922f2b05a</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>AI &amp; Machine Learning Engineer</t>
+          <t>Database Developer</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>OneBlood</t>
+          <t>Hollstadt Consulting</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Saint Petersburg, FL, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,15 +4441,85 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
+          <t>RDS, Azure, Spark, PySpark, SQL Server, Data Modeling, ETL, Power BI, Jenkins, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bdef6e08804da8cc</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Database Developer (Contractor) - MNSITE-3762</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>RE/SPEC Inc</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Saint Paul, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Spark, PySpark, SQL Server, Data Modeling, ETL, Power BI, Jenkins, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bac2143c91f124e3</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>AI &amp; Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>OneBlood</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Saint Petersburg, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
           <t>AWS, Azure, Medallion Architecture, ETL, ELT, CI/CD, Git, Python, SQL, R</t>
         </is>
       </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
-      <c r="G115" t="inlineStr">
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=9242f2d7ab83418a</t>
         </is>

--- a/results/job_matches_2026-07-21.xlsx
+++ b/results/job_matches_2026-07-21.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G117"/>
+  <dimension ref="A1:G112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,25 +538,25 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Data Engineer - Databricks</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>megan soft</t>
+          <t>Steampunk</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>19.4</v>
+        <v>18.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Spark, Scala, Kafka, SQL Server</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, Step Functions, S3, RDS, Azure, Databricks</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74f99ec032c2a050</t>
+          <t>https://www.indeed.com/viewjob?jk=d8b9759a865fb48a</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Engineer - Databricks</t>
+          <t>AWS Cloud</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Steampunk</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, Step Functions, S3, RDS, Azure, Databricks</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,19 +601,19 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8b9759a865fb48a</t>
+          <t>https://www.indeed.com/viewjob?jk=42e3c5912b49c237</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AWS Cloud</t>
+          <t>Customer Solution Architect — Arango AI Product Suite</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>ARANGO</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, ECS, IAM, RDS, Scala</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Kafka, Snowflake, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,7 +636,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42e3c5912b49c237</t>
+          <t>https://www.indeed.com/viewjob?jk=632508141e5e7e23</t>
         </is>
       </c>
     </row>
@@ -1098,25 +1098,25 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Java Application Architect</t>
+          <t>Reporting Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Hitachi Rail</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MySQL, Star Schema, Fact Tables, Dimension Tables</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06adce66e837b3b3</t>
+          <t>https://www.indeed.com/viewjob?jk=7504d94e8707d02b</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Reporting Engineer</t>
+          <t>Data Solutions Engineer - HYBRID/NC RESIDENTS ONLY</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Hitachi Rail</t>
+          <t>PowerSecure Inc.</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MySQL, Star Schema, Fact Tables, Dimension Tables</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7504d94e8707d02b</t>
+          <t>https://www.indeed.com/viewjob?jk=dc9b66f689cbeefb</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Solutions Engineer - HYBRID/NC RESIDENTS ONLY</t>
+          <t>Reporting Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>PowerSecure Inc.</t>
+          <t>Hitachi Energy</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala</t>
+          <t>AWS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MySQL, Star Schema, Fact Tables, Dimension Tables</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc9b66f689cbeefb</t>
+          <t>https://www.indeed.com/viewjob?jk=59ef3d85179316f9</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Reporting Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Hitachi Energy</t>
+          <t>Bloomerang</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MySQL, Star Schema, Fact Tables, Dimension Tables</t>
+          <t>AWS, Redshift, RDS, Databricks, Google Cloud Platform, BigQuery, Scala, Snowflake, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,19 +1231,19 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59ef3d85179316f9</t>
+          <t>https://www.indeed.com/viewjob?jk=0eff179e948461c2</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Native Developer- EST</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Bloomerang</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, Google Cloud Platform, BigQuery, Scala, Snowflake, PostgreSQL, MySQL</t>
+          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0eff179e948461c2</t>
+          <t>https://www.indeed.com/viewjob?jk=37e94025d78d00b3</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>AI Native Developer- EST</t>
+          <t>Software Engineering LMTS</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37e94025d78d00b3</t>
+          <t>https://www.indeed.com/viewjob?jk=572e8633b0661a80</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Software Engineering LMTS</t>
+          <t>Databricks Architect</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Confiz</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Bentonville, AR, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Google Cloud Platform, Cloud Storage, Spark, PySpark</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=572e8633b0661a80</t>
+          <t>https://www.indeed.com/viewjob?jk=18be742c481fa20b</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Databricks Architect</t>
+          <t>Sr. Data Engineer (HYBRID)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Confiz</t>
+          <t>Equinox</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Bentonville, AR, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Google Cloud Platform, Cloud Storage, Spark, PySpark</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, Scala, DynamoDB, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18be742c481fa20b</t>
+          <t>https://www.indeed.com/viewjob?jk=22216c34e7397891</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer (HYBRID)</t>
+          <t>Cloud Solutions Engineer – Azure</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Equinox</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, Scala, DynamoDB, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22216c34e7397891</t>
+          <t>https://www.indeed.com/viewjob?jk=dc23fc3c19075d7c</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Cloud Solutions Engineer – Azure</t>
+          <t>Senior Snowflake Platform Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Groton, CT, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,17 +1431,17 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, IAM, RDS, Scala, Snowflake, Time Travel, clustering keys, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc23fc3c19075d7c</t>
+          <t>https://www.indeed.com/viewjob?jk=c5ad590ea8a95921</t>
         </is>
       </c>
     </row>
@@ -1483,17 +1483,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Software Engineering Intern</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Copart, Inc</t>
+          <t>Traackr</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Data Modeling, ETL, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7bf2ebcfa4a5f5e</t>
+          <t>https://www.indeed.com/viewjob?jk=df567011cf662897</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Sr. SW Engineer</t>
+          <t>Software Engineering Intern</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Copart, Inc</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Foster City, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, Data Modeling, ETL, Splunk, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f774d387b35a5b8</t>
+          <t>https://www.indeed.com/viewjob?jk=c7bf2ebcfa4a5f5e</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Salesforce Business Systems Analyst</t>
+          <t>Sr. SW Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Foster City, CA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, Data Modeling, ETL, Splunk, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb817b0533864176</t>
+          <t>https://www.indeed.com/viewjob?jk=8f774d387b35a5b8</t>
         </is>
       </c>
     </row>
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b799aca0d95f271</t>
+          <t>https://www.indeed.com/viewjob?jk=cb817b0533864176</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Big Data Engineer</t>
+          <t>Salesforce Business Systems Analyst</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Highmark Health</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Hive, Spark, Scala, Kafka, Oracle</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d94c95081afe04c8</t>
+          <t>https://www.indeed.com/viewjob?jk=7b799aca0d95f271</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Big Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>Highmark Health</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Bridgewater, NJ, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Hive, Spark, Scala, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=786fbdb63698b11b</t>
+          <t>https://www.indeed.com/viewjob?jk=d94c95081afe04c8</t>
         </is>
       </c>
     </row>
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d193f030168c94d0</t>
+          <t>https://www.indeed.com/viewjob?jk=786fbdb63698b11b</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer with Sales Incentive Compensation (SIC)</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>UNIFY SOLUTIONS INC</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Bridgewater, NJ, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, GCP, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb057adb6c59f5ff</t>
+          <t>https://www.indeed.com/viewjob?jk=d193f030168c94d0</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Solution Architect - Java/J2EE</t>
+          <t>Databricks Data Engineer with Sales Incentive Compensation (SIC)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>PNC Financial Services Group</t>
+          <t>UNIFY SOLUTIONS INC</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Farmers Branch, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MongoDB, Cassandra</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, GCP, Scala</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,14 +1791,14 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a23b5c57a47b265</t>
+          <t>https://www.indeed.com/viewjob?jk=eb057adb6c59f5ff</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Software Architect - Java/Spring Boot/Kafka</t>
+          <t>Senior Solution Architect - Java/J2EE</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Farmers Branch, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f929c4ac83ec17b7</t>
+          <t>https://www.indeed.com/viewjob?jk=3a23b5c57a47b265</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Software Engineering SMTS</t>
+          <t>Software Architect - Java/Spring Boot/Kafka</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>PNC Financial Services Group</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98a642ee513df5f7</t>
+          <t>https://www.indeed.com/viewjob?jk=f929c4ac83ec17b7</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Software Engineering SMTS</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>NetApp</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Morrisville, NC, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0844aea628b28dab</t>
+          <t>https://www.indeed.com/viewjob?jk=98a642ee513df5f7</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Specialist Software Engineer</t>
+          <t>Powertrain Applications Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, RDS, Azure, Databricks, Scala, Oracle, SQL Server</t>
+          <t>AWS, S3, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, SQL Server, ELT</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31c5d5f535a77ad9</t>
+          <t>https://www.indeed.com/viewjob?jk=af00d281c82c2777</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>LoopNet - Software Engineer II</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>CoStar Group</t>
+          <t>NetApp</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Morrisville, NC, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, Databricks, BigQuery, Scala, Kafka, Snowflake, MySQL, DynamoDB</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51f6585eaae3edd6</t>
+          <t>https://www.indeed.com/viewjob?jk=0844aea628b28dab</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>AI &amp; Data Engineer, Data Discovery Services</t>
+          <t>LoopNet - Software Engineer II</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Bristol Myers Squibb</t>
+          <t>CoStar Group</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, ECS, RDS, Azure, Databricks, Vertex AI</t>
+          <t>AWS, S3, SQS, Databricks, BigQuery, Scala, Kafka, Snowflake, MySQL, DynamoDB</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9331d42b3835041a</t>
+          <t>https://www.indeed.com/viewjob?jk=51f6585eaae3edd6</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Databricks Platform Engineer</t>
+          <t>AI &amp; Data Engineer, Data Discovery Services</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Confiz</t>
+          <t>Bristol Myers Squibb</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Bentonville, AR, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Google Cloud Platform, Spark, Scala, ELT, CI/CD</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, ECS, RDS, Azure, Databricks, Vertex AI</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b713352ad723441</t>
+          <t>https://www.indeed.com/viewjob?jk=9331d42b3835041a</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Bricks Data Engineer</t>
+          <t>Databricks Platform Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Bavel systems LLP</t>
+          <t>Confiz</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Bentonville, AR, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, GCP, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Google Cloud Platform, Spark, Scala, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d997e2a6aa4fbed</t>
+          <t>https://www.indeed.com/viewjob?jk=5b713352ad723441</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Informatica Cloud Data Engineer (IDMC/IICS)</t>
+          <t>Data Bricks Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Bavel systems LLP</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Snowflake, Oracle, Data Modeling, ETL</t>
+          <t>AWS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, GCP, Scala, Kafka</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2526f9ca235bb42c</t>
+          <t>https://www.indeed.com/viewjob?jk=2d997e2a6aa4fbed</t>
         </is>
       </c>
     </row>
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f156bc316e4a8e1e</t>
+          <t>https://www.indeed.com/viewjob?jk=2526f9ca235bb42c</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Full Stack</t>
+          <t>Informatica Cloud Data Engineer (IDMC/IICS)</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Hopkins, MN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,17 +2166,17 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB, Cassandra</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Snowflake, Oracle, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=caea23a7afe82982</t>
+          <t>https://www.indeed.com/viewjob?jk=f156bc316e4a8e1e</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Hopkins, MN, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c6c9dc97e7a8c55</t>
+          <t>https://www.indeed.com/viewjob?jk=caea23a7afe82982</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Brookfield, WI, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97ef6349d26627c1</t>
+          <t>https://www.indeed.com/viewjob?jk=2c6c9dc97e7a8c55</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Java Product Engineer</t>
+          <t>Senior Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Diaconia, LLC.</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Brookfield, WI, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, Oracle, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed19f7417f9c2e59</t>
+          <t>https://www.indeed.com/viewjob?jk=97ef6349d26627c1</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Java Product Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Diaconia, LLC.</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Azure, Snowflake, CI/CD, Jenkins</t>
+          <t>AWS, Azure, Scala, Kafka, Oracle, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87d9611a04bffadf</t>
+          <t>https://www.indeed.com/viewjob?jk=ed19f7417f9c2e59</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>LogicMonitor</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Data Modeling, ETL, Terraform</t>
+          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Azure, Snowflake, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92a2dfe6bebcb2dc</t>
+          <t>https://www.indeed.com/viewjob?jk=87d9611a04bffadf</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Sr. Forward Deployed Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>FEED THE CHILDREN</t>
+          <t>LogicMonitor</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Spark, Scala, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Data Modeling, ETL, Terraform</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d4416990cb07c5b</t>
+          <t>https://www.indeed.com/viewjob?jk=92a2dfe6bebcb2dc</t>
         </is>
       </c>
     </row>
@@ -2778,17 +2778,17 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Azure DevOps Architect</t>
+          <t>Java Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>IPolarity LLC</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Whippany, NJ, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Glue, IAM, RDS, Azure, GCP, Scala, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=198e8bee7c6735a3</t>
+          <t>https://www.indeed.com/viewjob?jk=9eed61967883578e</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Java Engineer</t>
+          <t>Full Stack .NET Developer – C#, React, Azure/AWS</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>J2B GLOBAL LLC</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, MongoDB</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MongoDB, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9eed61967883578e</t>
+          <t>https://www.indeed.com/viewjob?jk=ceec9a4f672d1616</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Full Stack .NET Developer – C#, React, Azure/AWS</t>
+          <t>Forward Deployed Data Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>J2B GLOBAL LLC</t>
+          <t>CoorsTek</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Golden, CO, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MongoDB, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ceec9a4f672d1616</t>
+          <t>https://www.indeed.com/viewjob?jk=01c677c253d655bb</t>
         </is>
       </c>
     </row>
@@ -2888,12 +2888,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Foley</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Google Cloud Platform, GCP, Hadoop, Scala, Snowflake, ETL, ELT, CI/CD, Airflow</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Medallion Architecture, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c875e063114bb1c</t>
+          <t>https://www.indeed.com/viewjob?jk=fb528101e5b7e6f0</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Forward Deployed Data Engineer</t>
+          <t>Senior Network Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>CoorsTek</t>
+          <t>Citizens</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Golden, CO, US USA</t>
+          <t>Johnston, RI, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, S3, RDS, Scala, CI/CD, Jenkins, Maven, Terraform, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01c677c253d655bb</t>
+          <t>https://www.indeed.com/viewjob?jk=93cf7434fe21677c</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Database Reliability Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Foley</t>
+          <t>Frontline Education</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Naperville, IL, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Medallion Architecture, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, ETL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb528101e5b7e6f0</t>
+          <t>https://www.indeed.com/viewjob?jk=03a470170ea48de6</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>AI Solution Engineer</t>
+          <t>Senior Database Reliability Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Agilify</t>
+          <t>Frontline Education</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, Azure, Event Hubs, BigQuery, Scala, Kafka, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, ETL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=173deae55fc0fc11</t>
+          <t>https://www.indeed.com/viewjob?jk=22e28cc34091c701</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Network Engineer</t>
+          <t>Senior Database Reliability Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Citizens</t>
+          <t>Frontline Education</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Johnston, RI, US USA</t>
+          <t>Wayne, PA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, CI/CD, Jenkins, Maven, Terraform, Docker, Jenkins</t>
+          <t>AWS, RDS, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, ETL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93cf7434fe21677c</t>
+          <t>https://www.indeed.com/viewjob?jk=406eb6619e461cdd</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Database Reliability Engineer</t>
+          <t>Sr. Database Administrator</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Frontline Education</t>
+          <t>Vertafore</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Naperville, IL, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, ETL, CI/CD, Terraform</t>
+          <t>AWS, Redshift, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, Terraform, Git</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03a470170ea48de6</t>
+          <t>https://www.indeed.com/viewjob?jk=652e6c19792a8b61</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Database Reliability Engineer</t>
+          <t>Solution Architect – Data Migration &amp; Analytics</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Frontline Education</t>
+          <t>Zensar Technologies</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, ETL, CI/CD, Terraform</t>
+          <t>AWS, Kinesis, S3, RDS, Data Lake Storage, Medallion Architecture, Scala, Snowflake, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22e28cc34091c701</t>
+          <t>https://www.indeed.com/viewjob?jk=1f7b9a9c0a9082ee</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Database Reliability Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Frontline Education</t>
+          <t>SpyCloud</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Wayne, PA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, ETL, CI/CD, Terraform</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Databricks, Spark, Scala, DynamoDB, ETL</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=406eb6619e461cdd</t>
+          <t>https://www.indeed.com/viewjob?jk=8b990fe917577735</t>
         </is>
       </c>
     </row>
@@ -3198,17 +3198,17 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Software Engineer 3, Content Platforms</t>
+          <t>Security Data Analyst - Parsing</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Condé Nast</t>
+          <t>SpyCloud</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Kafka, PostgreSQL, MongoDB, Data Modeling, Splunk, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, SQS, API Gateway, RDS, Databricks, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d59c1e871e80877</t>
+          <t>https://www.indeed.com/viewjob?jk=589dd47eef0f8740</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Sr. Database Administrator</t>
+          <t>Security Data Analyst - Parsing</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Vertafore</t>
+          <t>SpyCloud</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, Terraform, Git</t>
+          <t>AWS, Lambda, S3, SQS, API Gateway, RDS, Databricks, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=652e6c19792a8b61</t>
+          <t>https://www.indeed.com/viewjob?jk=171de003fe5563fb</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Solution Architect – Data Migration &amp; Analytics</t>
+          <t>Software Engineer 3, Content Platforms</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Zensar Technologies</t>
+          <t>Condé Nast</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, RDS, Data Lake Storage, Medallion Architecture, Scala, Snowflake, Data Modeling, dbt</t>
+          <t>AWS, Kafka, PostgreSQL, MongoDB, Data Modeling, Splunk, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f7b9a9c0a9082ee</t>
+          <t>https://www.indeed.com/viewjob?jk=1d59c1e871e80877</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>MDM Integration Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>SpyCloud</t>
+          <t>McLane Company</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Temple, TX, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Databricks, Spark, Scala, DynamoDB, ETL</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,102 +3331,102 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b990fe917577735</t>
+          <t>https://www.indeed.com/viewjob?jk=c3b598b8c3673649</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Security Data Analyst - Parsing</t>
+          <t>Data Scientist / Senior Data Scientist (Risk Modeling)</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>SpyCloud</t>
+          <t>Berkshire Hathaway Specialty Insurance</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, API Gateway, RDS, Databricks, NoSQL, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Docker, Git, Python</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=589dd47eef0f8740</t>
+          <t>https://www.indeed.com/viewjob?jk=2c9e4130f1298022</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Security Data Analyst - Parsing</t>
+          <t>Data Scientist / Senior Data Scientist (Risk Modeling)</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>SpyCloud</t>
+          <t>Berkshire Hathaway Specialty Insurance</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, API Gateway, RDS, Databricks, NoSQL, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Docker, Git, Python</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=171de003fe5563fb</t>
+          <t>https://www.indeed.com/viewjob?jk=d7f7784d943297ed</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>MDM Integration Engineer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>McLane Company</t>
+          <t>Northwest Federal Credit Union</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Temple, TX, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, MySQL, Azure DevOps, Terraform, Azure Monitor</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3b598b8c3673649</t>
+          <t>https://www.indeed.com/viewjob?jk=7291a950f8ec410d</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Generative AI Engineer</t>
+          <t>Software Engineer II - Platform Engineer/Databricks</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Vertex AI, Hadoop, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Jenkins, Maven, Terraform, Jenkins, Git</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4413ec7a4b00d4ae</t>
+          <t>https://www.indeed.com/viewjob?jk=4448bee09655101c</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Generative AI Engineer</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>State Street</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Quincy, MA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Vertex AI, Hadoop, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Splunk, CI/CD, Jenkins, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e48a5b4af545b7e</t>
+          <t>https://www.indeed.com/viewjob?jk=eb61fc433cd2352b</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Data Scientist / Senior Data Scientist (Risk Modeling)</t>
+          <t>Senior MLOps Engineer I</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Berkshire Hathaway Specialty Insurance</t>
+          <t>Zeitview</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,34 +3531,34 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Docker, Git, Python</t>
+          <t>AWS, RDS, Scala, PostgreSQL, MLOps, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c9e4130f1298022</t>
+          <t>https://www.indeed.com/viewjob?jk=5c8710a47a6c9b4e</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Data Scientist / Senior Data Scientist (Risk Modeling)</t>
+          <t>Senior MLOps Engineer I</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Berkshire Hathaway Specialty Insurance</t>
+          <t>Zeitview</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,34 +3566,34 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Docker, Git, Python</t>
+          <t>AWS, RDS, Scala, PostgreSQL, MLOps, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7f7784d943297ed</t>
+          <t>https://www.indeed.com/viewjob?jk=84de7dc9a3088a08</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Senior .NET Developer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Northwest Federal Credit Union</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, MySQL, Azure DevOps, Terraform, Azure Monitor</t>
+          <t>AWS, Lambda, ECS, Scala, Kafka, SQL Server, PostgreSQL, NoSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7291a950f8ec410d</t>
+          <t>https://www.indeed.com/viewjob?jk=35a2c65d6f2f7d06</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Software Engineer II - Platform Engineer/Databricks</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Karsun Solutions LLC</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Jenkins, Maven, Terraform, Jenkins, Git</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4448bee09655101c</t>
+          <t>https://www.indeed.com/viewjob?jk=2f81c0ec4956c9db</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Senior Architect</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>State Street</t>
+          <t>Mass General Brigham</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Quincy, MA, US USA</t>
+          <t>Somerville, MA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Splunk, CI/CD, Jenkins, Terraform, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb61fc433cd2352b</t>
+          <t>https://www.indeed.com/viewjob?jk=dccbfd697359c720</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior MLOps Engineer I</t>
+          <t>Senior Software Engineer IV / V (Java, React, AWS)</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Zeitview</t>
+          <t>Auto.Live</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,34 +3706,34 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, PostgreSQL, MLOps, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, SQS, Scala, Kafka, MySQL, CI/CD, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c8710a47a6c9b4e</t>
+          <t>https://www.indeed.com/viewjob?jk=42c2207352100be0</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Senior MLOps Engineer I</t>
+          <t>Senior Engineer, Corp Solutions</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Zeitview</t>
+          <t>Papa John's</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,34 +3741,34 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, PostgreSQL, MLOps, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Google Cloud Platform, GCP, CI/CD, Jenkins, Maven, Kubernetes, Jenkins, Git, Bitbucket</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84de7dc9a3088a08</t>
+          <t>https://www.indeed.com/viewjob?jk=6ae25ca0f2bd81f6</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>Senior Amazon Connect Application Architect</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Karsun Solutions LLC</t>
+          <t>TELUS Digital</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, Kinesis, S3, RDS, Scala, DynamoDB, CI/CD, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f81c0ec4956c9db</t>
+          <t>https://www.indeed.com/viewjob?jk=feceaa7f623de4d6</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Senior .NET Developer</t>
+          <t>Senior Amazon Connect Application Architect</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>TELUS Digital</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, Scala, Kafka, SQL Server, PostgreSQL, NoSQL, Data Modeling, CI/CD</t>
+          <t>AWS, Lambda, Kinesis, S3, RDS, Scala, DynamoDB, CI/CD, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35a2c65d6f2f7d06</t>
+          <t>https://www.indeed.com/viewjob?jk=ef89c4f9800f8a90</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Senior Architect</t>
+          <t>Senior Amazon Connect Application Architect</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Mass General Brigham</t>
+          <t>TELUS Digital</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Somerville, MA, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, Lambda, Kinesis, S3, RDS, Scala, DynamoDB, CI/CD, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dccbfd697359c720</t>
+          <t>https://www.indeed.com/viewjob?jk=5fc58207e473b9f5</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Senior Software Engineer IV / V (Java, React, AWS)</t>
+          <t>Senior Amazon Connect Application Architect</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Auto.Live</t>
+          <t>TELUS Digital</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, SQS, Scala, Kafka, MySQL, CI/CD, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, Lambda, Kinesis, S3, RDS, Scala, DynamoDB, CI/CD, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42c2207352100be0</t>
+          <t>https://www.indeed.com/viewjob?jk=1f8bb981d509050f</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Senior Engineer, Corp Solutions</t>
+          <t>Senior Amazon Connect Application Architect</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Papa John's</t>
+          <t>TELUS Digital</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Charlottesville, VA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, CI/CD, Jenkins, Maven, Kubernetes, Jenkins, Git, Bitbucket</t>
+          <t>AWS, Lambda, Kinesis, S3, RDS, Scala, DynamoDB, CI/CD, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ae25ca0f2bd81f6</t>
+          <t>https://www.indeed.com/viewjob?jk=4b3612752c893190</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Senior Amazon Connect Application Architect</t>
+          <t>Sr Devops Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>TELUS Digital</t>
+          <t>_coderio</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, RDS, Scala, DynamoDB, CI/CD, Terraform, AWS CloudFormation</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=feceaa7f623de4d6</t>
+          <t>https://www.indeed.com/viewjob?jk=541df4abc8320b5a</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Senior Amazon Connect Application Architect</t>
+          <t>AI Software Engineer IV</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>TELUS Digital</t>
+          <t>The Standard Insurance</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, RDS, Scala, DynamoDB, CI/CD, Terraform, AWS CloudFormation</t>
+          <t>RDS, Azure, Databricks, Scala, MLflow, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef89c4f9800f8a90</t>
+          <t>https://www.indeed.com/viewjob?jk=b3c232645c82fc83</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Senior Amazon Connect Application Architect</t>
+          <t>Sr. Business Intelligence Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>TELUS Digital</t>
+          <t>Crane Worldwide Logistics</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, RDS, Scala, DynamoDB, CI/CD, Terraform, AWS CloudFormation</t>
+          <t>AWS, RDS, Azure, Snowflake, Data Modeling, dbt, Power BI, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5fc58207e473b9f5</t>
+          <t>https://www.indeed.com/viewjob?jk=53344a199a269470</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Senior Amazon Connect Application Architect</t>
+          <t>Senior Software Engineer ( Seattle/Provo)</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>TELUS Digital</t>
+          <t>Press Ganey</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Provo, UT, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, RDS, Scala, DynamoDB, CI/CD, Terraform, AWS CloudFormation</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, Data Modeling, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f8bb981d509050f</t>
+          <t>https://www.indeed.com/viewjob?jk=1b27efa8ed4a1f97</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Senior Amazon Connect Application Architect</t>
+          <t>Software Engineer- Greensboro, NC</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>TELUS Digital</t>
+          <t>Stake Center Locating</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Charlottesville, VA, US USA</t>
+          <t>Greensboro, NC, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, RDS, Scala, DynamoDB, CI/CD, Terraform, AWS CloudFormation</t>
+          <t>Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, SQL Server, ETL, ELT, Power BI, Git</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b3612752c893190</t>
+          <t>https://www.indeed.com/viewjob?jk=2c8332d54e7fcd1c</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Senior Software Engineer ( Seattle/Provo)</t>
+          <t>Database Developer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Press Ganey</t>
+          <t>Hollstadt Consulting</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Provo, UT, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, Data Modeling, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Spark, PySpark, SQL Server, Data Modeling, ETL, Power BI, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b27efa8ed4a1f97</t>
+          <t>https://www.indeed.com/viewjob?jk=bdef6e08804da8cc</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Sr Devops Engineer</t>
+          <t>Database Developer (Contractor) - MNSITE-3762</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>_coderio</t>
+          <t>RE/SPEC Inc</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
+          <t>RDS, Azure, Spark, PySpark, SQL Server, Data Modeling, ETL, Power BI, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=541df4abc8320b5a</t>
+          <t>https://www.indeed.com/viewjob?jk=bac2143c91f124e3</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>AI Software Engineer IV</t>
+          <t>Senior R&amp;D Software Engineer, Fivetran AI</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>The Standard Insurance</t>
+          <t>Fivetran</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, MLflow, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Databricks, GCP, BigQuery, Snowflake, ETL, ELT, dbt, Docker</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,24 +4206,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3c232645c82fc83</t>
+          <t>https://www.indeed.com/viewjob?jk=55c8e7c6018043d4</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Sr. Business Intelligence Engineer</t>
+          <t>Senior R&amp;D Software Engineer, Fivetran AI</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Crane Worldwide Logistics</t>
+          <t>Fivetran</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Snowflake, Data Modeling, dbt, Power BI, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Databricks, GCP, BigQuery, Snowflake, ETL, ELT, dbt, Docker</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,24 +4241,24 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53344a199a269470</t>
+          <t>https://www.indeed.com/viewjob?jk=30bf0451dbc419d1</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Software Engineer- Greensboro, NC</t>
+          <t>Senior R&amp;D Software Engineer, Fivetran AI</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Stake Center Locating</t>
+          <t>Fivetran</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Greensboro, NC, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, SQL Server, ETL, ELT, Power BI, Git</t>
+          <t>AWS, RDS, Databricks, GCP, BigQuery, Snowflake, ETL, ELT, dbt, Docker</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c8332d54e7fcd1c</t>
+          <t>https://www.indeed.com/viewjob?jk=501671e22555fe5c</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4311,24 +4311,24 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55c8e7c6018043d4</t>
+          <t>https://www.indeed.com/viewjob?jk=f8b8baa922f2b05a</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Senior R&amp;D Software Engineer, Fivetran AI</t>
+          <t>AI &amp; Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Fivetran</t>
+          <t>OneBlood</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Saint Petersburg, FL, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, BigQuery, Snowflake, ETL, ELT, dbt, Docker</t>
+          <t>AWS, Azure, Medallion Architecture, ETL, ELT, CI/CD, Git, Python, SQL, R</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4345,181 +4345,6 @@
         </is>
       </c>
       <c r="G112" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=30bf0451dbc419d1</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>Senior R&amp;D Software Engineer, Fivetran AI</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>Fivetran</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>Denver, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D113" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, GCP, BigQuery, Snowflake, ETL, ELT, dbt, Docker</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=501671e22555fe5c</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>Senior R&amp;D Software Engineer, Fivetran AI</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>Fivetran</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>Oakland, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D114" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, GCP, BigQuery, Snowflake, ETL, ELT, dbt, Docker</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f8b8baa922f2b05a</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>Database Developer</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>Hollstadt Consulting</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>MN, US USA</t>
-        </is>
-      </c>
-      <c r="D115" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Spark, PySpark, SQL Server, Data Modeling, ETL, Power BI, Jenkins, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=bdef6e08804da8cc</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>Database Developer (Contractor) - MNSITE-3762</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>RE/SPEC Inc</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>Saint Paul, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D116" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Spark, PySpark, SQL Server, Data Modeling, ETL, Power BI, Jenkins, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=bac2143c91f124e3</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>AI &amp; Machine Learning Engineer</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>OneBlood</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>Saint Petersburg, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D117" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Medallion Architecture, ETL, ELT, CI/CD, Git, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
-      <c r="G117" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=9242f2d7ab83418a</t>
         </is>

--- a/results/job_matches_2026-07-21.xlsx
+++ b/results/job_matches_2026-07-21.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G112"/>
+  <dimension ref="A1:G109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1343,52 +1343,52 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer (HYBRID)</t>
+          <t>Software Engineer, New College Graduate,</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Equinox</t>
+          <t>Teradyne</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>North Reading, MA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, Scala, DynamoDB, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22216c34e7397891</t>
+          <t>https://www.indeed.com/viewjob?jk=4a9c723d1fa4a196</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Cloud Solutions Engineer – Azure</t>
+          <t>Sr. Data Engineer (HYBRID)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Equinox</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, Scala, DynamoDB, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc23fc3c19075d7c</t>
+          <t>https://www.indeed.com/viewjob?jk=22216c34e7397891</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Snowflake Platform Engineer</t>
+          <t>Cloud Solutions Engineer – Azure</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Groton, CT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Snowflake, Time Travel, clustering keys, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5ad590ea8a95921</t>
+          <t>https://www.indeed.com/viewjob?jk=dc23fc3c19075d7c</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior AI Security Automation Engineer</t>
+          <t>Senior Snowflake Platform Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>State Street</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Quincy, MA, US USA</t>
+          <t>Groton, CT, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,34 +1466,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, ELT</t>
+          <t>AWS, IAM, RDS, Scala, Snowflake, Time Travel, clustering keys, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1063ffb870d53611</t>
+          <t>https://www.indeed.com/viewjob?jk=c5ad590ea8a95921</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior AI Security Automation Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Traackr</t>
+          <t>State Street</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Quincy, MA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Data Modeling, ETL, ELT, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, ELT</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df567011cf662897</t>
+          <t>https://www.indeed.com/viewjob?jk=1063ffb870d53611</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Software Engineering Intern</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Copart, Inc</t>
+          <t>Traackr</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Data Modeling, ETL, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7bf2ebcfa4a5f5e</t>
+          <t>https://www.indeed.com/viewjob?jk=df567011cf662897</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Sr. SW Engineer</t>
+          <t>Software Engineering Intern</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Copart, Inc</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Foster City, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, Data Modeling, ETL, Splunk, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f774d387b35a5b8</t>
+          <t>https://www.indeed.com/viewjob?jk=c7bf2ebcfa4a5f5e</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Salesforce Business Systems Analyst</t>
+          <t>Sr. SW Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Foster City, CA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, Data Modeling, ETL, Splunk, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb817b0533864176</t>
+          <t>https://www.indeed.com/viewjob?jk=8f774d387b35a5b8</t>
         </is>
       </c>
     </row>
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b799aca0d95f271</t>
+          <t>https://www.indeed.com/viewjob?jk=cb817b0533864176</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Big Data Engineer</t>
+          <t>Salesforce Business Systems Analyst</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Highmark Health</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Hive, Spark, Scala, Kafka, Oracle</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d94c95081afe04c8</t>
+          <t>https://www.indeed.com/viewjob?jk=7b799aca0d95f271</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Big Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>Highmark Health</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Bridgewater, NJ, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Hive, Spark, Scala, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=786fbdb63698b11b</t>
+          <t>https://www.indeed.com/viewjob?jk=d94c95081afe04c8</t>
         </is>
       </c>
     </row>
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d193f030168c94d0</t>
+          <t>https://www.indeed.com/viewjob?jk=786fbdb63698b11b</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer with Sales Incentive Compensation (SIC)</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>UNIFY SOLUTIONS INC</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Bridgewater, NJ, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, GCP, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb057adb6c59f5ff</t>
+          <t>https://www.indeed.com/viewjob?jk=d193f030168c94d0</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Solution Architect - Java/J2EE</t>
+          <t>Databricks Data Engineer with Sales Incentive Compensation (SIC)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>PNC Financial Services Group</t>
+          <t>UNIFY SOLUTIONS INC</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Farmers Branch, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MongoDB, Cassandra</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, GCP, Scala</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,14 +1826,14 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a23b5c57a47b265</t>
+          <t>https://www.indeed.com/viewjob?jk=eb057adb6c59f5ff</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Software Architect - Java/Spring Boot/Kafka</t>
+          <t>Senior Solution Architect - Java/J2EE</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Farmers Branch, TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f929c4ac83ec17b7</t>
+          <t>https://www.indeed.com/viewjob?jk=3a23b5c57a47b265</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Software Engineering SMTS</t>
+          <t>Software Architect - Java/Spring Boot/Kafka</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>PNC Financial Services Group</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98a642ee513df5f7</t>
+          <t>https://www.indeed.com/viewjob?jk=f929c4ac83ec17b7</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Powertrain Applications Engineer</t>
+          <t>Software Engineering SMTS</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, SQL Server, ELT</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af00d281c82c2777</t>
+          <t>https://www.indeed.com/viewjob?jk=98a642ee513df5f7</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Powertrain Applications Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>NetApp</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Morrisville, NC, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, S3, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, SQL Server, ELT</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0844aea628b28dab</t>
+          <t>https://www.indeed.com/viewjob?jk=af00d281c82c2777</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>LoopNet - Software Engineer II</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>CoStar Group</t>
+          <t>NetApp</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Morrisville, NC, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, Databricks, BigQuery, Scala, Kafka, Snowflake, MySQL, DynamoDB</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51f6585eaae3edd6</t>
+          <t>https://www.indeed.com/viewjob?jk=0844aea628b28dab</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>AI &amp; Data Engineer, Data Discovery Services</t>
+          <t>LoopNet - Software Engineer II</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Bristol Myers Squibb</t>
+          <t>CoStar Group</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, ECS, RDS, Azure, Databricks, Vertex AI</t>
+          <t>AWS, S3, SQS, Databricks, BigQuery, Scala, Kafka, Snowflake, MySQL, DynamoDB</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9331d42b3835041a</t>
+          <t>https://www.indeed.com/viewjob?jk=51f6585eaae3edd6</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Databricks Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Confiz</t>
+          <t>datAvail</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Bentonville, AR, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Google Cloud Platform, Spark, Scala, ELT, CI/CD</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b713352ad723441</t>
+          <t>https://www.indeed.com/viewjob?jk=0b02e7a9293c05e9</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Bricks Data Engineer</t>
+          <t>AI &amp; Data Engineer, Data Discovery Services</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Bavel systems LLP</t>
+          <t>Bristol Myers Squibb</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, GCP, Scala, Kafka</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, ECS, RDS, Azure, Databricks, Vertex AI</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d997e2a6aa4fbed</t>
+          <t>https://www.indeed.com/viewjob?jk=9331d42b3835041a</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Informatica Cloud Data Engineer (IDMC/IICS)</t>
+          <t>Databricks Platform Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Confiz</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Bentonville, AR, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Snowflake, Oracle, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Google Cloud Platform, Spark, Scala, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2526f9ca235bb42c</t>
+          <t>https://www.indeed.com/viewjob?jk=5b713352ad723441</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Informatica Cloud Data Engineer (IDMC/IICS)</t>
+          <t>Data Bricks Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Bavel systems LLP</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Snowflake, Oracle, Data Modeling, ETL</t>
+          <t>AWS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, GCP, Scala, Kafka</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f156bc316e4a8e1e</t>
+          <t>https://www.indeed.com/viewjob?jk=2d997e2a6aa4fbed</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Full Stack</t>
+          <t>Informatica Cloud Data Engineer (IDMC/IICS)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Hopkins, MN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB, Cassandra</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Snowflake, Oracle, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=caea23a7afe82982</t>
+          <t>https://www.indeed.com/viewjob?jk=2526f9ca235bb42c</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Full Stack</t>
+          <t>Informatica Cloud Data Engineer (IDMC/IICS)</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB, Cassandra</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Snowflake, Oracle, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c6c9dc97e7a8c55</t>
+          <t>https://www.indeed.com/viewjob?jk=f156bc316e4a8e1e</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Full Stack</t>
+          <t>Software Engineer - .NET / SES</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Securiport</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Brookfield, WI, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB, Cassandra</t>
+          <t>AWS, Azure, Scala, Kafka, SQL Server, MySQL, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97ef6349d26627c1</t>
+          <t>https://www.indeed.com/viewjob?jk=e73c19b70ff97730</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Java Product Engineer</t>
+          <t>Software Engineer - .NET / APIS</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Diaconia, LLC.</t>
+          <t>Securiport</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, Oracle, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
+          <t>AWS, Azure, Scala, Kafka, SQL Server, MySQL, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed19f7417f9c2e59</t>
+          <t>https://www.indeed.com/viewjob?jk=8a904215046786df</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Hopkins, MN, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Azure, Snowflake, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87d9611a04bffadf</t>
+          <t>https://www.indeed.com/viewjob?jk=caea23a7afe82982</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer</t>
+          <t>Senior Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>LogicMonitor</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,77 +2376,77 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Data Modeling, ETL, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92a2dfe6bebcb2dc</t>
+          <t>https://www.indeed.com/viewjob?jk=2c6c9dc97e7a8c55</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Windows Engineer (Expert)</t>
+          <t>Senior Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>BAE Systems USA</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Brookfield, WI, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, Oracle, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09ee1d1985ee70d9</t>
+          <t>https://www.indeed.com/viewjob?jk=97ef6349d26627c1</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Cloud Systems Engineer III</t>
+          <t>Java Product Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Orange County's Credit Union</t>
+          <t>Diaconia, LLC.</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Santa Ana, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, Scala, ELT, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, Azure, Scala, Kafka, Oracle, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,32 +2456,32 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37e9b523a42f1787</t>
+          <t>https://www.indeed.com/viewjob?jk=ed19f7417f9c2e59</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Qureos</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Azure, Snowflake, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,32 +2491,32 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c91b09d863e5b13</t>
+          <t>https://www.indeed.com/viewjob?jk=87d9611a04bffadf</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Software Engineer II - Streaming</t>
+          <t>Sr. Forward Deployed Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Rivian and Volkswagen Group Technologies</t>
+          <t>LogicMonitor</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Kafka Connect, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Data Modeling, ETL, Terraform</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3871dec46927667b</t>
+          <t>https://www.indeed.com/viewjob?jk=92a2dfe6bebcb2dc</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (C#/Java/AI) - Underwriting Automation - Hybrid</t>
+          <t>Windows Engineer (Expert)</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>BAE Systems USA</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, Oracle, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f1adc20d8ab8b4a</t>
+          <t>https://www.indeed.com/viewjob?jk=09ee1d1985ee70d9</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (C#/Java/AI) - Underwriting Automation - Hybrid</t>
+          <t>Cloud Systems Engineer III</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Orange County's Credit Union</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Santa Ana, CA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Scala, ELT, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86fdcdffd7cae712</t>
+          <t>https://www.indeed.com/viewjob?jk=37e9b523a42f1787</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>ML-GenAI Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Prodapt Solutions</t>
+          <t>Qureos</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Vertex AI, Scala, NoSQL, MLOps, MLflow, CI/CD</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b71a1261fd024f4</t>
+          <t>https://www.indeed.com/viewjob?jk=3c91b09d863e5b13</t>
         </is>
       </c>
     </row>
@@ -2778,17 +2778,17 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Java Engineer</t>
+          <t>Senior Software Engineer (C#/Java/AI) - Underwriting Automation - Hybrid</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, MongoDB</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9eed61967883578e</t>
+          <t>https://www.indeed.com/viewjob?jk=6f1adc20d8ab8b4a</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Full Stack .NET Developer – C#, React, Azure/AWS</t>
+          <t>Senior Software Engineer (C#/Java/AI) - Underwriting Automation - Hybrid</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>J2B GLOBAL LLC</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MongoDB, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ceec9a4f672d1616</t>
+          <t>https://www.indeed.com/viewjob?jk=86fdcdffd7cae712</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Forward Deployed Data Engineer</t>
+          <t>Java Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>CoorsTek</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Golden, CO, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,32 +2876,32 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01c677c253d655bb</t>
+          <t>https://www.indeed.com/viewjob?jk=9eed61967883578e</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Full Stack .NET Developer – C#, React, Azure/AWS</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Foley</t>
+          <t>J2B GLOBAL LLC</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Medallion Architecture, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MongoDB, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,32 +2911,32 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb528101e5b7e6f0</t>
+          <t>https://www.indeed.com/viewjob?jk=ceec9a4f672d1616</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Network Engineer</t>
+          <t>ML-GenAI Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Citizens</t>
+          <t>Prodapt Solutions</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Johnston, RI, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, CI/CD, Jenkins, Maven, Terraform, Docker, Jenkins</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Vertex AI, Scala, NoSQL, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93cf7434fe21677c</t>
+          <t>https://www.indeed.com/viewjob?jk=1b71a1261fd024f4</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Database Reliability Engineer</t>
+          <t>Junior Data Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Frontline Education</t>
+          <t>Techfield</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Naperville, IL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, ETL, CI/CD, Terraform</t>
+          <t>AWS, S3, Azure, Hadoop, Hive, Spark, Scala, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03a470170ea48de6</t>
+          <t>https://www.indeed.com/viewjob?jk=95557e0528468ca2</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Database Reliability Engineer</t>
+          <t>Forward Deployed Data Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Frontline Education</t>
+          <t>CoorsTek</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Golden, CO, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, ETL, CI/CD, Terraform</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22e28cc34091c701</t>
+          <t>https://www.indeed.com/viewjob?jk=01c677c253d655bb</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Database Reliability Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Frontline Education</t>
+          <t>Foley</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Wayne, PA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, ETL, CI/CD, Terraform</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Medallion Architecture, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=406eb6619e461cdd</t>
+          <t>https://www.indeed.com/viewjob?jk=fb528101e5b7e6f0</t>
         </is>
       </c>
     </row>
@@ -3268,17 +3268,17 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Software Engineer 3, Content Platforms</t>
+          <t>Senior Database Reliability Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Condé Nast</t>
+          <t>Frontline Education</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Naperville, IL, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Kafka, PostgreSQL, MongoDB, Data Modeling, Splunk, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, ETL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d59c1e871e80877</t>
+          <t>https://www.indeed.com/viewjob?jk=03a470170ea48de6</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>MDM Integration Engineer</t>
+          <t>Senior Database Reliability Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>McLane Company</t>
+          <t>Frontline Education</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Temple, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, CI/CD, Terraform</t>
+          <t>AWS, RDS, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, ETL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,102 +3331,102 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3b598b8c3673649</t>
+          <t>https://www.indeed.com/viewjob?jk=22e28cc34091c701</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Data Scientist / Senior Data Scientist (Risk Modeling)</t>
+          <t>Senior Database Reliability Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Berkshire Hathaway Specialty Insurance</t>
+          <t>Frontline Education</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Wayne, PA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Docker, Git, Python</t>
+          <t>AWS, RDS, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, ETL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c9e4130f1298022</t>
+          <t>https://www.indeed.com/viewjob?jk=406eb6619e461cdd</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Data Scientist / Senior Data Scientist (Risk Modeling)</t>
+          <t>Software Engineer 3, Content Platforms</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Berkshire Hathaway Specialty Insurance</t>
+          <t>Condé Nast</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Docker, Git, Python</t>
+          <t>AWS, Kafka, PostgreSQL, MongoDB, Data Modeling, Splunk, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7f7784d943297ed</t>
+          <t>https://www.indeed.com/viewjob?jk=1d59c1e871e80877</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>MDM Integration Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Northwest Federal Credit Union</t>
+          <t>McLane Company</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Temple, TX, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, MySQL, Azure DevOps, Terraform, Azure Monitor</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7291a950f8ec410d</t>
+          <t>https://www.indeed.com/viewjob?jk=c3b598b8c3673649</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Software Engineer II - Platform Engineer/Databricks</t>
+          <t>Data Scientist / Senior Data Scientist (Risk Modeling)</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Berkshire Hathaway Specialty Insurance</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Jenkins, Maven, Terraform, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Docker, Git, Python</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4448bee09655101c</t>
+          <t>https://www.indeed.com/viewjob?jk=2c9e4130f1298022</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Data Scientist / Senior Data Scientist (Risk Modeling)</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>State Street</t>
+          <t>Berkshire Hathaway Specialty Insurance</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Quincy, MA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,34 +3496,34 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Splunk, CI/CD, Jenkins, Terraform, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Docker, Git, Python</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb61fc433cd2352b</t>
+          <t>https://www.indeed.com/viewjob?jk=d7f7784d943297ed</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior MLOps Engineer I</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Zeitview</t>
+          <t>Northwest Federal Credit Union</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,34 +3531,34 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, PostgreSQL, MLOps, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, MySQL, Azure DevOps, Terraform, Azure Monitor</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c8710a47a6c9b4e</t>
+          <t>https://www.indeed.com/viewjob?jk=7291a950f8ec410d</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior MLOps Engineer I</t>
+          <t>Software Engineer II - Platform Engineer/Databricks</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Zeitview</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,34 +3566,34 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, PostgreSQL, MLOps, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Jenkins, Maven, Terraform, Jenkins, Git</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84de7dc9a3088a08</t>
+          <t>https://www.indeed.com/viewjob?jk=4448bee09655101c</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior .NET Developer</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>State Street</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Quincy, MA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, Scala, Kafka, SQL Server, PostgreSQL, NoSQL, Data Modeling, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Splunk, CI/CD, Jenkins, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35a2c65d6f2f7d06</t>
+          <t>https://www.indeed.com/viewjob?jk=eb61fc433cd2352b</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>Senior .NET Developer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Karsun Solutions LLC</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, ECS, Scala, Kafka, SQL Server, PostgreSQL, NoSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f81c0ec4956c9db</t>
+          <t>https://www.indeed.com/viewjob?jk=35a2c65d6f2f7d06</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior Architect</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Mass General Brigham</t>
+          <t>Karsun Solutions LLC</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Somerville, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dccbfd697359c720</t>
+          <t>https://www.indeed.com/viewjob?jk=2f81c0ec4956c9db</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior Software Engineer IV / V (Java, React, AWS)</t>
+          <t>Senior Architect</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Auto.Live</t>
+          <t>Mass General Brigham</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Somerville, MA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, SQS, Scala, Kafka, MySQL, CI/CD, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42c2207352100be0</t>
+          <t>https://www.indeed.com/viewjob?jk=dccbfd697359c720</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Senior Engineer, Corp Solutions</t>
+          <t>Senior Software Engineer IV / V (Java, React, AWS)</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Papa John's</t>
+          <t>Auto.Live</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, CI/CD, Jenkins, Maven, Kubernetes, Jenkins, Git, Bitbucket</t>
+          <t>AWS, SQS, Scala, Kafka, MySQL, CI/CD, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ae25ca0f2bd81f6</t>
+          <t>https://www.indeed.com/viewjob?jk=42c2207352100be0</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Senior Amazon Connect Application Architect</t>
+          <t>Sr Devops Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>TELUS Digital</t>
+          <t>_coderio</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, RDS, Scala, DynamoDB, CI/CD, Terraform, AWS CloudFormation</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=feceaa7f623de4d6</t>
+          <t>https://www.indeed.com/viewjob?jk=541df4abc8320b5a</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Senior Amazon Connect Application Architect</t>
+          <t>AI Software Engineer IV</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>TELUS Digital</t>
+          <t>The Standard Insurance</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, RDS, Scala, DynamoDB, CI/CD, Terraform, AWS CloudFormation</t>
+          <t>RDS, Azure, Databricks, Scala, MLflow, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef89c4f9800f8a90</t>
+          <t>https://www.indeed.com/viewjob?jk=b3c232645c82fc83</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Senior Amazon Connect Application Architect</t>
+          <t>Sr. Business Intelligence Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>TELUS Digital</t>
+          <t>Crane Worldwide Logistics</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, RDS, Scala, DynamoDB, CI/CD, Terraform, AWS CloudFormation</t>
+          <t>AWS, RDS, Azure, Snowflake, Data Modeling, dbt, Power BI, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5fc58207e473b9f5</t>
+          <t>https://www.indeed.com/viewjob?jk=53344a199a269470</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Senior Amazon Connect Application Architect</t>
+          <t>Senior Software Engineer ( Seattle/Provo)</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>TELUS Digital</t>
+          <t>Press Ganey</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Provo, UT, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, RDS, Scala, DynamoDB, CI/CD, Terraform, AWS CloudFormation</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, Data Modeling, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f8bb981d509050f</t>
+          <t>https://www.indeed.com/viewjob?jk=1b27efa8ed4a1f97</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Senior Amazon Connect Application Architect</t>
+          <t>Software Engineer- Greensboro, NC</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>TELUS Digital</t>
+          <t>Stake Center Locating</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Charlottesville, VA, US USA</t>
+          <t>Greensboro, NC, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, RDS, Scala, DynamoDB, CI/CD, Terraform, AWS CloudFormation</t>
+          <t>Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, SQL Server, ETL, ELT, Power BI, Git</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b3612752c893190</t>
+          <t>https://www.indeed.com/viewjob?jk=2c8332d54e7fcd1c</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Sr Devops Engineer</t>
+          <t>Database Developer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>_coderio</t>
+          <t>Hollstadt Consulting</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
+          <t>RDS, Azure, Spark, PySpark, SQL Server, Data Modeling, ETL, Power BI, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=541df4abc8320b5a</t>
+          <t>https://www.indeed.com/viewjob?jk=bdef6e08804da8cc</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>AI Software Engineer IV</t>
+          <t>Database Developer (Contractor) - MNSITE-3762</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>The Standard Insurance</t>
+          <t>RE/SPEC Inc</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, MLflow, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>RDS, Azure, Spark, PySpark, SQL Server, Data Modeling, ETL, Power BI, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3c232645c82fc83</t>
+          <t>https://www.indeed.com/viewjob?jk=bac2143c91f124e3</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Sr. Business Intelligence Engineer</t>
+          <t>Senior R&amp;D Software Engineer, Fivetran AI</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Crane Worldwide Logistics</t>
+          <t>Fivetran</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Snowflake, Data Modeling, dbt, Power BI, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Databricks, GCP, BigQuery, Snowflake, ETL, ELT, dbt, Docker</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53344a199a269470</t>
+          <t>https://www.indeed.com/viewjob?jk=55c8e7c6018043d4</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Senior Software Engineer ( Seattle/Provo)</t>
+          <t>Senior R&amp;D Software Engineer, Fivetran AI</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Press Ganey</t>
+          <t>Fivetran</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Provo, UT, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, Data Modeling, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Databricks, GCP, BigQuery, Snowflake, ETL, ELT, dbt, Docker</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b27efa8ed4a1f97</t>
+          <t>https://www.indeed.com/viewjob?jk=30bf0451dbc419d1</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Software Engineer- Greensboro, NC</t>
+          <t>Senior R&amp;D Software Engineer, Fivetran AI</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Stake Center Locating</t>
+          <t>Fivetran</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Greensboro, NC, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, SQL Server, ETL, ELT, Power BI, Git</t>
+          <t>AWS, RDS, Databricks, GCP, BigQuery, Snowflake, ETL, ELT, dbt, Docker</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c8332d54e7fcd1c</t>
+          <t>https://www.indeed.com/viewjob?jk=501671e22555fe5c</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Database Developer</t>
+          <t>Senior R&amp;D Software Engineer, Fivetran AI</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Hollstadt Consulting</t>
+          <t>Fivetran</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>RDS, Azure, Spark, PySpark, SQL Server, Data Modeling, ETL, Power BI, Jenkins, Azure DevOps</t>
+          <t>AWS, RDS, Databricks, GCP, BigQuery, Snowflake, ETL, ELT, dbt, Docker</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdef6e08804da8cc</t>
+          <t>https://www.indeed.com/viewjob?jk=f8b8baa922f2b05a</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Database Developer (Contractor) - MNSITE-3762</t>
+          <t>Senior MLOps Engineer I</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>RE/SPEC Inc</t>
+          <t>Zeitview</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,34 +4161,34 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>RDS, Azure, Spark, PySpark, SQL Server, Data Modeling, ETL, Power BI, Jenkins, Azure DevOps</t>
+          <t>AWS, RDS, Scala, PostgreSQL, MLOps, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bac2143c91f124e3</t>
+          <t>https://www.indeed.com/viewjob?jk=5c8710a47a6c9b4e</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Senior R&amp;D Software Engineer, Fivetran AI</t>
+          <t>Senior MLOps Engineer I</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Fivetran</t>
+          <t>Zeitview</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,34 +4196,34 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, BigQuery, Snowflake, ETL, ELT, dbt, Docker</t>
+          <t>AWS, RDS, Scala, PostgreSQL, MLOps, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55c8e7c6018043d4</t>
+          <t>https://www.indeed.com/viewjob?jk=84de7dc9a3088a08</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Senior R&amp;D Software Engineer, Fivetran AI</t>
+          <t>AI &amp; Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Fivetran</t>
+          <t>OneBlood</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Saint Petersburg, FL, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, BigQuery, Snowflake, ETL, ELT, dbt, Docker</t>
+          <t>AWS, Azure, Medallion Architecture, ETL, ELT, CI/CD, Git, Python, SQL, R</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4240,111 +4240,6 @@
         </is>
       </c>
       <c r="G109" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=30bf0451dbc419d1</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>Senior R&amp;D Software Engineer, Fivetran AI</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>Fivetran</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>Denver, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D110" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, GCP, BigQuery, Snowflake, ETL, ELT, dbt, Docker</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=501671e22555fe5c</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>Senior R&amp;D Software Engineer, Fivetran AI</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>Fivetran</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>Oakland, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D111" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, GCP, BigQuery, Snowflake, ETL, ELT, dbt, Docker</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f8b8baa922f2b05a</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>AI &amp; Machine Learning Engineer</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>OneBlood</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>Saint Petersburg, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D112" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Medallion Architecture, ETL, ELT, CI/CD, Git, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
-      <c r="G112" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=9242f2d7ab83418a</t>
         </is>

--- a/results/job_matches_2026-07-21.xlsx
+++ b/results/job_matches_2026-07-21.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G109"/>
+  <dimension ref="A1:G104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,122 +503,122 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Specialist Software Engineer</t>
+          <t>Software Developer II - Meter Data Management Software (Full Stack, Databricks)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Transamerica</t>
+          <t>National Information Solutions Cooperative (NISC)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Cedar Rapids, IA, US USA</t>
+          <t>Bismarck, ND, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>20.8</v>
+        <v>18.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, API Gateway, ECS, RDS, Azure, Data Factory, Event Hubs, Zookeeper</t>
+          <t>AWS, EMR, Lambda, S3, SQS, SNS, RDS, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3cf053b4e78a7784</t>
+          <t>https://www.indeed.com/viewjob?jk=09a0c773ba869ab2</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Engineer - Databricks</t>
+          <t>Software Developer II - Meter Data Management Software (Full Stack, Databricks)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Steampunk</t>
+          <t>National Information Solutions Cooperative (NISC)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Cedar Rapids, IA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.1</v>
+        <v>18.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, Step Functions, S3, RDS, Azure, Databricks</t>
+          <t>AWS, EMR, Lambda, S3, SQS, SNS, RDS, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8b9759a865fb48a</t>
+          <t>https://www.indeed.com/viewjob?jk=33143989f3362efb</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AWS Cloud</t>
+          <t>Software Developer II - Meter Data Management Software (Full Stack, Databricks)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>National Information Solutions Cooperative (NISC)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Lake Saint Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.1</v>
+        <v>18.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, ECS, IAM, RDS, Scala</t>
+          <t>AWS, EMR, Lambda, S3, SQS, SNS, RDS, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42e3c5912b49c237</t>
+          <t>https://www.indeed.com/viewjob?jk=0b784c8205aa1d58</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Customer Solution Architect — Arango AI Product Suite</t>
+          <t>Data Engineer - Databricks</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ARANGO</t>
+          <t>Steampunk</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Kafka, Snowflake, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, Step Functions, S3, RDS, Azure, Databricks</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,14 +636,14 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=632508141e5e7e23</t>
+          <t>https://www.indeed.com/viewjob?jk=d8b9759a865fb48a</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AWS Solutions Architect</t>
+          <t>AWS Cloud</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf903a5bb459577f</t>
+          <t>https://www.indeed.com/viewjob?jk=42e3c5912b49c237</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Customer Solution Architect — Arango AI Product Suite</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>CrossCountry Mortgage, LLC</t>
+          <t>ARANGO</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, RDS, Azure, GCP, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Kafka, Snowflake, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=704b1f0ab6bff192</t>
+          <t>https://www.indeed.com/viewjob?jk=632508141e5e7e23</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Azure Databricks Architect Healthcare Payer</t>
+          <t>AWS Solutions Architect</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>VeeRteq Solutions Inc.</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Hadoop, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5652d49391bd82a2</t>
+          <t>https://www.indeed.com/viewjob?jk=cf903a5bb459577f</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Azure Databricks Architect Healthcare Payer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>VeeRteq Solutions Inc.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Bridgewater, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Hadoop, Hive, Spark, Scala</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Hadoop, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7567cb365890dc6b</t>
+          <t>https://www.indeed.com/viewjob?jk=5652d49391bd82a2</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Digital Pathology (Hybrid)</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Mayo Clinic</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Rochester, MN, US USA</t>
+          <t>Bridgewater, NJ, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, Hive, Spark, Kafka, Snowflake, ELT, Power BI, Tableau, DataOps</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Hadoop, Hive, Spark, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=761b34bda9b68b66</t>
+          <t>https://www.indeed.com/viewjob?jk=7567cb365890dc6b</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Data Engineer - Digital Pathology (Hybrid)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>Mayo Clinic</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Bridgewater, NJ, US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Hadoop, Hive, Spark, Scala</t>
+          <t>Google Cloud Platform, GCP, Hive, Spark, Kafka, Snowflake, ELT, Power BI, Tableau, DataOps</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=177a0dfa7a7c2758</t>
+          <t>https://www.indeed.com/viewjob?jk=761b34bda9b68b66</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Technical Architect</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>REI Systems</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sterling, VA, US USA</t>
+          <t>Bridgewater, NJ, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, ECS, IAM, RDS, Scala, Oracle, DynamoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Hadoop, Hive, Spark, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=175f2d223e3312d6</t>
+          <t>https://www.indeed.com/viewjob?jk=177a0dfa7a7c2758</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Architect (Azure + Databricks)</t>
+          <t>Senior Technical Architect</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Nine Core Technologies</t>
+          <t>REI Systems</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Milpitas, CA, US USA</t>
+          <t>Sterling, VA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Medallion Architecture, GCP</t>
+          <t>AWS, Lambda, API Gateway, ECS, IAM, RDS, Scala, Oracle, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=118ef7e12d0743d7</t>
+          <t>https://www.indeed.com/viewjob?jk=175f2d223e3312d6</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Software Engineer III - Data/Payments Technology</t>
+          <t>Senior Data Engineer - ITS4</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>State of Minnesota - Minnesota IT Services</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,34 +941,34 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Scala, Kafka, Snowflake, Oracle</t>
+          <t>AWS, Glue, S3, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8366ecb2495ecb5</t>
+          <t>https://www.indeed.com/viewjob?jk=1054e208948fd6fb</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - ITS4</t>
+          <t>Software Engineer III - Data/Payments Technology</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>State of Minnesota - Minnesota IT Services</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,17 +976,17 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1054e208948fd6fb</t>
+          <t>https://www.indeed.com/viewjob?jk=c8366ecb2495ecb5</t>
         </is>
       </c>
     </row>
@@ -1016,7 +1016,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1063,25 +1063,25 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Reporting Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>CrossCountry Mortgage, LLC</t>
+          <t>Hitachi Rail</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, RDS, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MySQL, Star Schema, Fact Tables, Dimension Tables</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26d0c8a6b975fef0</t>
+          <t>https://www.indeed.com/viewjob?jk=7504d94e8707d02b</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Reporting Engineer</t>
+          <t>Data Solutions Engineer - HYBRID/NC RESIDENTS ONLY</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Hitachi Rail</t>
+          <t>PowerSecure Inc.</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MySQL, Star Schema, Fact Tables, Dimension Tables</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7504d94e8707d02b</t>
+          <t>https://www.indeed.com/viewjob?jk=dc9b66f689cbeefb</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Solutions Engineer - HYBRID/NC RESIDENTS ONLY</t>
+          <t>Reporting Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>PowerSecure Inc.</t>
+          <t>Hitachi Energy</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala</t>
+          <t>AWS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MySQL, Star Schema, Fact Tables, Dimension Tables</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc9b66f689cbeefb</t>
+          <t>https://www.indeed.com/viewjob?jk=59ef3d85179316f9</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Reporting Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Hitachi Energy</t>
+          <t>Bloomerang</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MySQL, Star Schema, Fact Tables, Dimension Tables</t>
+          <t>AWS, Redshift, RDS, Databricks, Google Cloud Platform, BigQuery, Scala, Snowflake, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,19 +1196,19 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59ef3d85179316f9</t>
+          <t>https://www.indeed.com/viewjob?jk=0eff179e948461c2</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Native Developer- EST</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Bloomerang</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1221,34 +1221,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, Google Cloud Platform, BigQuery, Scala, Snowflake, PostgreSQL, MySQL</t>
+          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0eff179e948461c2</t>
+          <t>https://www.indeed.com/viewjob?jk=37e94025d78d00b3</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>AI Native Developer- EST</t>
+          <t>Software Engineering LMTS</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37e94025d78d00b3</t>
+          <t>https://www.indeed.com/viewjob?jk=572e8633b0661a80</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Software Engineering LMTS</t>
+          <t>Databricks Architect</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Confiz</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Bentonville, AR, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Google Cloud Platform, Cloud Storage, Spark, PySpark</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=572e8633b0661a80</t>
+          <t>https://www.indeed.com/viewjob?jk=18be742c481fa20b</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Databricks Architect</t>
+          <t>Software Engineer, New College Graduate,</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Confiz</t>
+          <t>Teradyne</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Bentonville, AR, US USA</t>
+          <t>North Reading, MA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,52 +1326,52 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Google Cloud Platform, Cloud Storage, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18be742c481fa20b</t>
+          <t>https://www.indeed.com/viewjob?jk=4a9c723d1fa4a196</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Software Engineer, New College Graduate,</t>
+          <t>Cloud Solutions Engineer – Azure</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Teradyne</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>North Reading, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a9c723d1fa4a196</t>
+          <t>https://www.indeed.com/viewjob?jk=dc23fc3c19075d7c</t>
         </is>
       </c>
     </row>
@@ -1413,17 +1413,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Cloud Solutions Engineer – Azure</t>
+          <t>Senior Snowflake Platform Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Groton, CT, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, IAM, RDS, Scala, Snowflake, Time Travel, clustering keys, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc23fc3c19075d7c</t>
+          <t>https://www.indeed.com/viewjob?jk=c5ad590ea8a95921</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Snowflake Platform Engineer</t>
+          <t>Senior AI Security Automation Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>State Street</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Groton, CT, US USA</t>
+          <t>Quincy, MA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,34 +1466,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Snowflake, Time Travel, clustering keys, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, ELT</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5ad590ea8a95921</t>
+          <t>https://www.indeed.com/viewjob?jk=1063ffb870d53611</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior AI Security Automation Engineer</t>
+          <t>Software Engineering Intern</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>State Street</t>
+          <t>Copart, Inc</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Quincy, MA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1063ffb870d53611</t>
+          <t>https://www.indeed.com/viewjob?jk=c7bf2ebcfa4a5f5e</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Sr. SW Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Traackr</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Foster City, CA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Data Modeling, ETL, ELT, MLOps, MLflow</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, Data Modeling, ETL, Splunk, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df567011cf662897</t>
+          <t>https://www.indeed.com/viewjob?jk=8f774d387b35a5b8</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Software Engineering Intern</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Copart, Inc</t>
+          <t>Traackr</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,42 +1571,42 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Data Modeling, ETL, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7bf2ebcfa4a5f5e</t>
+          <t>https://www.indeed.com/viewjob?jk=df567011cf662897</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Sr. SW Engineer</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Foster City, CA, US USA</t>
+          <t>Bridgewater, NJ, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, Data Modeling, ETL, Splunk, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f774d387b35a5b8</t>
+          <t>https://www.indeed.com/viewjob?jk=786fbdb63698b11b</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Salesforce Business Systems Analyst</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Bridgewater, NJ, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb817b0533864176</t>
+          <t>https://www.indeed.com/viewjob?jk=d193f030168c94d0</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Salesforce Business Systems Analyst</t>
+          <t>Big Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Highmark Health</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Hive, Spark, Scala, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b799aca0d95f271</t>
+          <t>https://www.indeed.com/viewjob?jk=d94c95081afe04c8</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Big Data Engineer</t>
+          <t>Databricks Data Engineer with Sales Incentive Compensation (SIC)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Highmark Health</t>
+          <t>UNIFY SOLUTIONS INC</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Hive, Spark, Scala, Kafka, Oracle</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, GCP, Scala</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d94c95081afe04c8</t>
+          <t>https://www.indeed.com/viewjob?jk=eb057adb6c59f5ff</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Sr. Software Engineer (AWS / Java / Node.js / Python) CONTRACT</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>Broadridge</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Bridgewater, NJ, US USA</t>
+          <t>Edgewood, NY, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, ETL, ELT, Power BI</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Scala, PostgreSQL, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=786fbdb63698b11b</t>
+          <t>https://www.indeed.com/viewjob?jk=98d7e7ab4a96ab08</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Senior AI Solutions Architect</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>Neo4j</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Bridgewater, NJ, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Hadoop, Hive, Spark, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d193f030168c94d0</t>
+          <t>https://www.indeed.com/viewjob?jk=0dbb073f20120e13</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer with Sales Incentive Compensation (SIC)</t>
+          <t>Senior Solution Architect - Java/J2EE</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>UNIFY SOLUTIONS INC</t>
+          <t>PNC Financial Services Group</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Farmers Branch, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, GCP, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,14 +1826,14 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb057adb6c59f5ff</t>
+          <t>https://www.indeed.com/viewjob?jk=3a23b5c57a47b265</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Solution Architect - Java/J2EE</t>
+          <t>Software Architect - Java/Spring Boot/Kafka</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Farmers Branch, TX, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a23b5c57a47b265</t>
+          <t>https://www.indeed.com/viewjob?jk=f929c4ac83ec17b7</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Software Architect - Java/Spring Boot/Kafka</t>
+          <t>Software Engineering SMTS</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>PNC Financial Services Group</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MongoDB, Cassandra</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f929c4ac83ec17b7</t>
+          <t>https://www.indeed.com/viewjob?jk=98a642ee513df5f7</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Software Engineering SMTS</t>
+          <t>Powertrain Applications Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, NoSQL</t>
+          <t>AWS, S3, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, SQL Server, ELT</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98a642ee513df5f7</t>
+          <t>https://www.indeed.com/viewjob?jk=af00d281c82c2777</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Powertrain Applications Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>NetApp</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Morrisville, NC, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, SQL Server, ELT</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,67 +1966,67 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af00d281c82c2777</t>
+          <t>https://www.indeed.com/viewjob?jk=0844aea628b28dab</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>NetApp</t>
+          <t>datAvail</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Morrisville, NC, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0844aea628b28dab</t>
+          <t>https://www.indeed.com/viewjob?jk=0b02e7a9293c05e9</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>LoopNet - Software Engineer II</t>
+          <t>AI &amp; Data Engineer, Data Discovery Services</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>CoStar Group</t>
+          <t>Bristol Myers Squibb</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, Databricks, BigQuery, Scala, Kafka, Snowflake, MySQL, DynamoDB</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, ECS, RDS, Azure, Databricks, Vertex AI</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51f6585eaae3edd6</t>
+          <t>https://www.indeed.com/viewjob?jk=9331d42b3835041a</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Databricks Platform Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>datAvail</t>
+          <t>Confiz</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Bentonville, AR, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Google Cloud Platform, Spark, Scala, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b02e7a9293c05e9</t>
+          <t>https://www.indeed.com/viewjob?jk=5b713352ad723441</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>AI &amp; Data Engineer, Data Discovery Services</t>
+          <t>Data Bricks Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Bristol Myers Squibb</t>
+          <t>Bavel systems LLP</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, ECS, RDS, Azure, Databricks, Vertex AI</t>
+          <t>AWS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, GCP, Scala, Kafka</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9331d42b3835041a</t>
+          <t>https://www.indeed.com/viewjob?jk=2d997e2a6aa4fbed</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Databricks Platform Engineer</t>
+          <t>Java Product Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Confiz</t>
+          <t>Diaconia, LLC.</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Bentonville, AR, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Google Cloud Platform, Spark, Scala, ELT, CI/CD</t>
+          <t>AWS, Azure, Scala, Kafka, Oracle, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b713352ad723441</t>
+          <t>https://www.indeed.com/viewjob?jk=ed19f7417f9c2e59</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Bricks Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Bavel systems LLP</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, GCP, Scala, Kafka</t>
+          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Azure, Snowflake, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d997e2a6aa4fbed</t>
+          <t>https://www.indeed.com/viewjob?jk=87d9611a04bffadf</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Informatica Cloud Data Engineer (IDMC/IICS)</t>
+          <t>Senior Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Hopkins, MN, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Snowflake, Oracle, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2526f9ca235bb42c</t>
+          <t>https://www.indeed.com/viewjob?jk=caea23a7afe82982</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Informatica Cloud Data Engineer (IDMC/IICS)</t>
+          <t>Senior Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Snowflake, Oracle, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f156bc316e4a8e1e</t>
+          <t>https://www.indeed.com/viewjob?jk=2c6c9dc97e7a8c55</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Software Engineer - .NET / SES</t>
+          <t>Senior Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Securiport</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Brookfield, WI, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, SQL Server, MySQL, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e73c19b70ff97730</t>
+          <t>https://www.indeed.com/viewjob?jk=97ef6349d26627c1</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Software Engineer - .NET / APIS</t>
+          <t>Specialist - Data Engineering</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Securiport</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, SQL Server, MySQL, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
+          <t>RDS, Hadoop, Spark, Scala, SQL Server, ETL, Tableau, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a904215046786df</t>
+          <t>https://www.indeed.com/viewjob?jk=55c8d9fe21fbf89b</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Full Stack</t>
+          <t>Cloud DevOps Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Mastronardi Produce</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Hopkins, MN, US USA</t>
+          <t>Livonia, MI, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB, Cassandra</t>
+          <t>AWS, RDS, Azure, MLOps, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,102 +2351,102 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=caea23a7afe82982</t>
+          <t>https://www.indeed.com/viewjob?jk=7fa1ca8e2ddf6df8</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Full Stack</t>
+          <t>Cloud Systems Engineer III</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Orange County's Credit Union</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Santa Ana, CA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB, Cassandra</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Scala, ELT, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c6c9dc97e7a8c55</t>
+          <t>https://www.indeed.com/viewjob?jk=37e9b523a42f1787</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Full Stack</t>
+          <t>Python Software Architect</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Brookfield, WI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB, Cassandra</t>
+          <t>AWS, Glue, S3, RDS, Scala, Oracle, SQL Server, PostgreSQL, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97ef6349d26627c1</t>
+          <t>https://www.indeed.com/viewjob?jk=51db177a53e7ef14</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Java Product Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Diaconia, LLC.</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, Oracle, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, PostgreSQL, MySQL, Splunk, Maven</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,32 +2456,32 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed19f7417f9c2e59</t>
+          <t>https://www.indeed.com/viewjob?jk=b1d1f01448956ac8</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Azure, Snowflake, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, PostgreSQL, MySQL, Splunk, Maven</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,32 +2491,32 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87d9611a04bffadf</t>
+          <t>https://www.indeed.com/viewjob?jk=5c9d86fee622b07b</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer</t>
+          <t>Data Analyst (Data Solutions)</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>LogicMonitor</t>
+          <t>The Coca-Cola Company</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Data Modeling, ETL, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI, Tableau, Git</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92a2dfe6bebcb2dc</t>
+          <t>https://www.indeed.com/viewjob?jk=60db44428bef76ed</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Windows Engineer (Expert)</t>
+          <t>Java Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>BAE Systems USA</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, Oracle, Splunk, CI/CD</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09ee1d1985ee70d9</t>
+          <t>https://www.indeed.com/viewjob?jk=9eed61967883578e</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Cloud Systems Engineer III</t>
+          <t>Full Stack .NET Developer – C#, React, Azure/AWS</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Orange County's Credit Union</t>
+          <t>J2B GLOBAL LLC</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Santa Ana, CA, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, Scala, ELT, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MongoDB, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37e9b523a42f1787</t>
+          <t>https://www.indeed.com/viewjob?jk=ceec9a4f672d1616</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Application Support Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Qureos</t>
+          <t>Availity, LLC.</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,252 +2621,252 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, S3, IAM, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c91b09d863e5b13</t>
+          <t>https://www.indeed.com/viewjob?jk=7b138daabe966037</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Python Software Architect</t>
+          <t>Data Engineer (Azure &amp; Snowflake) - Remote</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Mindex</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Scala, Oracle, SQL Server, PostgreSQL, DynamoDB, CI/CD</t>
+          <t>Azure, Data Factory, Data Lake Storage, Cloud Storage, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51db177a53e7ef14</t>
+          <t>https://www.indeed.com/viewjob?jk=329cdc7ca8132e90</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer (Azure &amp; Snowflake) - Remote</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>Mindex</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, PostgreSQL, MySQL, Splunk, Maven</t>
+          <t>Azure, Data Factory, Data Lake Storage, Cloud Storage, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1d1f01448956ac8</t>
+          <t>https://www.indeed.com/viewjob?jk=7a4ebf0e5f5c11c0</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer (Azure &amp; Snowflake) - Remote</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>Mindex</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, PostgreSQL, MySQL, Splunk, Maven</t>
+          <t>Azure, Data Factory, Data Lake Storage, Cloud Storage, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c9d86fee622b07b</t>
+          <t>https://www.indeed.com/viewjob?jk=7c6a06a8d28780bf</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Analyst (Data Solutions)</t>
+          <t>Data Engineer (Azure &amp; Snowflake) - Remote</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company</t>
+          <t>Mindex</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI, Tableau, Git</t>
+          <t>Azure, Data Factory, Data Lake Storage, Cloud Storage, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60db44428bef76ed</t>
+          <t>https://www.indeed.com/viewjob?jk=cd6304cc9580794e</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (C#/Java/AI) - Underwriting Automation - Hybrid</t>
+          <t>Sr Cloud Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Lennar</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, IAM, RDS</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f1adc20d8ab8b4a</t>
+          <t>https://www.indeed.com/viewjob?jk=d0b237d7cb0a351b</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (C#/Java/AI) - Underwriting Automation - Hybrid</t>
+          <t>Junior Data Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Techfield</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL</t>
+          <t>AWS, S3, Azure, Hadoop, Hive, Spark, Scala, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86fdcdffd7cae712</t>
+          <t>https://www.indeed.com/viewjob?jk=95557e0528468ca2</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Java Engineer</t>
+          <t>Forward Deployed Data Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>CoorsTek</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Golden, CO, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, MongoDB</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,32 +2876,32 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9eed61967883578e</t>
+          <t>https://www.indeed.com/viewjob?jk=01c677c253d655bb</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Full Stack .NET Developer – C#, React, Azure/AWS</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>J2B GLOBAL LLC</t>
+          <t>Foley</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MongoDB, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Medallion Architecture, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,59 +2911,59 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ceec9a4f672d1616</t>
+          <t>https://www.indeed.com/viewjob?jk=fb528101e5b7e6f0</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>ML-GenAI Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Prodapt Solutions</t>
+          <t>Unity Technologies</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Vertex AI, Scala, NoSQL, MLOps, MLflow, CI/CD</t>
+          <t>RDS, Azure, Google Cloud Platform, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b71a1261fd024f4</t>
+          <t>https://www.indeed.com/viewjob?jk=652b63d35a6266a3</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Junior Data Engineer</t>
+          <t>Sr. Database Administrator</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Techfield</t>
+          <t>Vertafore</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Hadoop, Hive, Spark, Scala, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, Redshift, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, Terraform, Git</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95557e0528468ca2</t>
+          <t>https://www.indeed.com/viewjob?jk=652e6c19792a8b61</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Forward Deployed Data Engineer</t>
+          <t>Solution Architect – Data Migration &amp; Analytics</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>CoorsTek</t>
+          <t>Zensar Technologies</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Golden, CO, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, Kinesis, S3, RDS, Data Lake Storage, Medallion Architecture, Scala, Snowflake, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01c677c253d655bb</t>
+          <t>https://www.indeed.com/viewjob?jk=1f7b9a9c0a9082ee</t>
         </is>
       </c>
     </row>
@@ -3028,12 +3028,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Foley</t>
+          <t>SpyCloud</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Medallion Architecture, Scala, Data Modeling, ETL</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Databricks, Spark, Scala, DynamoDB, ETL</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb528101e5b7e6f0</t>
+          <t>https://www.indeed.com/viewjob?jk=8b990fe917577735</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Sr. Database Administrator</t>
+          <t>Full-Stack AI Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Vertafore</t>
+          <t>Micron Technology</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, Terraform, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=652e6c19792a8b61</t>
+          <t>https://www.indeed.com/viewjob?jk=cb2b319c05d2be3e</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Solution Architect – Data Migration &amp; Analytics</t>
+          <t>SR SOFTWARE ENGINEER</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Zensar Technologies</t>
+          <t>Dollar General</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Goodlettsville, TN, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, RDS, Data Lake Storage, Medallion Architecture, Scala, Snowflake, Data Modeling, dbt</t>
+          <t>S3, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, Cassandra, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,14 +3121,14 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f7b9a9c0a9082ee</t>
+          <t>https://www.indeed.com/viewjob?jk=fbb1d7ed6fd57469</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Security Data Analyst - Parsing</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Databricks, Spark, Scala, DynamoDB, ETL</t>
+          <t>AWS, Lambda, S3, SQS, API Gateway, RDS, Databricks, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b990fe917577735</t>
+          <t>https://www.indeed.com/viewjob?jk=589dd47eef0f8740</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>SR SOFTWARE ENGINEER</t>
+          <t>Security Data Analyst - Parsing</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Dollar General</t>
+          <t>SpyCloud</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Goodlettsville, TN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>S3, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, Cassandra, CI/CD, Docker</t>
+          <t>AWS, Lambda, S3, SQS, API Gateway, RDS, Databricks, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,32 +3191,32 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbb1d7ed6fd57469</t>
+          <t>https://www.indeed.com/viewjob?jk=171de003fe5563fb</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Security Data Analyst - Parsing</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>SpyCloud</t>
+          <t>Northwest Federal Credit Union</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, API Gateway, RDS, Databricks, NoSQL, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, MySQL, Azure DevOps, Terraform, Azure Monitor</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,32 +3226,32 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=589dd47eef0f8740</t>
+          <t>https://www.indeed.com/viewjob?jk=7291a950f8ec410d</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Security Data Analyst - Parsing</t>
+          <t>Software Engineer II - Platform Engineer/Databricks</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>SpyCloud</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, API Gateway, RDS, Databricks, NoSQL, ETL, CI/CD</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Jenkins, Maven, Terraform, Jenkins, Git</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,32 +3261,32 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=171de003fe5563fb</t>
+          <t>https://www.indeed.com/viewjob?jk=4448bee09655101c</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Database Reliability Engineer</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Frontline Education</t>
+          <t>State Street</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Naperville, IL, US USA</t>
+          <t>Quincy, MA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, ETL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Splunk, CI/CD, Jenkins, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,164 +3296,164 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03a470170ea48de6</t>
+          <t>https://www.indeed.com/viewjob?jk=eb61fc433cd2352b</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Database Reliability Engineer</t>
+          <t>Sr Datawarehouse Architect for New York City NY</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Frontline Education</t>
+          <t>Centillion Infotech LLC</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, ETL, CI/CD, Terraform</t>
+          <t>RDS, Azure, Databricks, Spark, Scala, Data Modeling, ETL, ELT, Python, SQL</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22e28cc34091c701</t>
+          <t>https://www.indeed.com/viewjob?jk=a11b6e886c2b743d</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Database Reliability Engineer</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Frontline Education</t>
+          <t>TaxSlayer</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Wayne, PA, US USA</t>
+          <t>Augusta, GA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, ETL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=406eb6619e461cdd</t>
+          <t>https://www.indeed.com/viewjob?jk=e38ede1f1c848056</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Software Engineer 3, Content Platforms</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Condé Nast</t>
+          <t>TaxSlayer</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Evans, GA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Kafka, PostgreSQL, MongoDB, Data Modeling, Splunk, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d59c1e871e80877</t>
+          <t>https://www.indeed.com/viewjob?jk=f9cec52a87c2914b</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>MDM Integration Engineer</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>McLane Company</t>
+          <t>TaxSlayer</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Temple, TX, US USA</t>
+          <t>North Augusta, SC, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3b598b8c3673649</t>
+          <t>https://www.indeed.com/viewjob?jk=1f84a2d5bc189bc0</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Data Scientist / Senior Data Scientist (Risk Modeling)</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Berkshire Hathaway Specialty Insurance</t>
+          <t>TaxSlayer</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Augusta, GA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Docker, Git, Python</t>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c9e4130f1298022</t>
+          <t>https://www.indeed.com/viewjob?jk=9540e403cb0fe0bc</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Data Scientist / Senior Data Scientist (Risk Modeling)</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Berkshire Hathaway Specialty Insurance</t>
+          <t>TaxSlayer</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Aiken, SC, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,34 +3496,34 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Docker, Git, Python</t>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7f7784d943297ed</t>
+          <t>https://www.indeed.com/viewjob?jk=39572bc0cbf1e1ab</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Northwest Federal Credit Union</t>
+          <t>TaxSlayer</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Grovetown, GA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,34 +3531,34 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, MySQL, Azure DevOps, Terraform, Azure Monitor</t>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7291a950f8ec410d</t>
+          <t>https://www.indeed.com/viewjob?jk=f96379913f2a0b13</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Software Engineer II - Platform Engineer/Databricks</t>
+          <t>Senior .NET Developer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Jenkins, Maven, Terraform, Jenkins, Git</t>
+          <t>AWS, Lambda, ECS, Scala, Kafka, SQL Server, PostgreSQL, NoSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4448bee09655101c</t>
+          <t>https://www.indeed.com/viewjob?jk=35a2c65d6f2f7d06</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>State Street</t>
+          <t>Karsun Solutions LLC</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Quincy, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Splunk, CI/CD, Jenkins, Terraform, Jenkins</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb61fc433cd2352b</t>
+          <t>https://www.indeed.com/viewjob?jk=2f81c0ec4956c9db</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior .NET Developer</t>
+          <t>Senior Architect</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Mass General Brigham</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Somerville, MA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, Scala, Kafka, SQL Server, PostgreSQL, NoSQL, Data Modeling, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,19 +3646,19 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35a2c65d6f2f7d06</t>
+          <t>https://www.indeed.com/viewjob?jk=dccbfd697359c720</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>Senior Software Engineer IV / V (Java, React, AWS)</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Karsun Solutions LLC</t>
+          <t>Auto.Live</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, SQS, Scala, Kafka, MySQL, CI/CD, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f81c0ec4956c9db</t>
+          <t>https://www.indeed.com/viewjob?jk=42c2207352100be0</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior Architect</t>
+          <t>Sr Devops Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Mass General Brigham</t>
+          <t>_coderio</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Somerville, MA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dccbfd697359c720</t>
+          <t>https://www.indeed.com/viewjob?jk=541df4abc8320b5a</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Senior Software Engineer IV / V (Java, React, AWS)</t>
+          <t>AI Software Engineer IV</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Auto.Live</t>
+          <t>The Standard Insurance</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, SQS, Scala, Kafka, MySQL, CI/CD, Terraform, Docker, Kubernetes, Git</t>
+          <t>RDS, Azure, Databricks, Scala, MLflow, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42c2207352100be0</t>
+          <t>https://www.indeed.com/viewjob?jk=b3c232645c82fc83</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Sr Devops Engineer</t>
+          <t>Sr. Business Intelligence Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>_coderio</t>
+          <t>Crane Worldwide Logistics</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Snowflake, Data Modeling, dbt, Power BI, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=541df4abc8320b5a</t>
+          <t>https://www.indeed.com/viewjob?jk=53344a199a269470</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>AI Software Engineer IV</t>
+          <t>Senior Software Engineer ( Seattle/Provo)</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>The Standard Insurance</t>
+          <t>Press Ganey</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Provo, UT, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, MLflow, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, Data Modeling, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3c232645c82fc83</t>
+          <t>https://www.indeed.com/viewjob?jk=1b27efa8ed4a1f97</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Sr. Business Intelligence Engineer</t>
+          <t>Senior R&amp;D Software Engineer, Fivetran AI</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Crane Worldwide Logistics</t>
+          <t>Fivetran</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Snowflake, Data Modeling, dbt, Power BI, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Databricks, GCP, BigQuery, Snowflake, ETL, ELT, dbt, Docker</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53344a199a269470</t>
+          <t>https://www.indeed.com/viewjob?jk=55c8e7c6018043d4</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Senior Software Engineer ( Seattle/Provo)</t>
+          <t>Senior R&amp;D Software Engineer, Fivetran AI</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Press Ganey</t>
+          <t>Fivetran</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Provo, UT, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, Data Modeling, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Databricks, GCP, BigQuery, Snowflake, ETL, ELT, dbt, Docker</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b27efa8ed4a1f97</t>
+          <t>https://www.indeed.com/viewjob?jk=30bf0451dbc419d1</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Software Engineer- Greensboro, NC</t>
+          <t>Senior R&amp;D Software Engineer, Fivetran AI</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Stake Center Locating</t>
+          <t>Fivetran</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Greensboro, NC, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, SQL Server, ETL, ELT, Power BI, Git</t>
+          <t>AWS, RDS, Databricks, GCP, BigQuery, Snowflake, ETL, ELT, dbt, Docker</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c8332d54e7fcd1c</t>
+          <t>https://www.indeed.com/viewjob?jk=501671e22555fe5c</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Database Developer</t>
+          <t>Senior R&amp;D Software Engineer, Fivetran AI</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Hollstadt Consulting</t>
+          <t>Fivetran</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>RDS, Azure, Spark, PySpark, SQL Server, Data Modeling, ETL, Power BI, Jenkins, Azure DevOps</t>
+          <t>AWS, RDS, Databricks, GCP, BigQuery, Snowflake, ETL, ELT, dbt, Docker</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,19 +3961,19 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdef6e08804da8cc</t>
+          <t>https://www.indeed.com/viewjob?jk=f8b8baa922f2b05a</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Database Developer (Contractor) - MNSITE-3762</t>
+          <t>Database Developer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>RE/SPEC Inc</t>
+          <t>Integres, LLC</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -3991,29 +3991,29 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bac2143c91f124e3</t>
+          <t>https://www.indeed.com/viewjob?jk=cc8d97653729dfa4</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Senior R&amp;D Software Engineer, Fivetran AI</t>
+          <t>Database Developer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Fivetran</t>
+          <t>Hollstadt Consulting</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, BigQuery, Snowflake, ETL, ELT, dbt, Docker</t>
+          <t>RDS, Azure, Spark, PySpark, SQL Server, Data Modeling, ETL, Power BI, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55c8e7c6018043d4</t>
+          <t>https://www.indeed.com/viewjob?jk=bdef6e08804da8cc</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Senior R&amp;D Software Engineer, Fivetran AI</t>
+          <t>AI &amp; Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Fivetran</t>
+          <t>OneBlood</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Saint Petersburg, FL, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, BigQuery, Snowflake, ETL, ELT, dbt, Docker</t>
+          <t>AWS, Azure, Medallion Architecture, ETL, ELT, CI/CD, Git, Python, SQL, R</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4065,181 +4065,6 @@
         </is>
       </c>
       <c r="G104" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=30bf0451dbc419d1</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>Senior R&amp;D Software Engineer, Fivetran AI</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>Fivetran</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>Denver, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D105" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, GCP, BigQuery, Snowflake, ETL, ELT, dbt, Docker</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=501671e22555fe5c</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>Senior R&amp;D Software Engineer, Fivetran AI</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>Fivetran</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>Oakland, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D106" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, GCP, BigQuery, Snowflake, ETL, ELT, dbt, Docker</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f8b8baa922f2b05a</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>Senior MLOps Engineer I</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>Zeitview</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D107" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, PostgreSQL, MLOps, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>2026-07-21</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5c8710a47a6c9b4e</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>Senior MLOps Engineer I</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>Zeitview</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D108" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, PostgreSQL, MLOps, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>2026-07-21</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=84de7dc9a3088a08</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>AI &amp; Machine Learning Engineer</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>OneBlood</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>Saint Petersburg, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D109" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Medallion Architecture, ETL, ELT, CI/CD, Git, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=9242f2d7ab83418a</t>
         </is>

--- a/results/job_matches_2026-07-21.xlsx
+++ b/results/job_matches_2026-07-21.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G104"/>
+  <dimension ref="A1:G106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,17 +608,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer - Databricks</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Steampunk</t>
+          <t>Luxoft</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,34 +626,34 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, Step Functions, S3, RDS, Azure, Databricks</t>
+          <t>RDS, Azure, Databricks, Hadoop, HDFS, MapReduce, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8b9759a865fb48a</t>
+          <t>https://www.indeed.com/viewjob?jk=8438fc0eeeabc119</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AWS Cloud</t>
+          <t>Data Engineer - Databricks</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Steampunk</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, ECS, IAM, RDS, Scala</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, Step Functions, S3, RDS, Azure, Databricks</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,19 +671,19 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42e3c5912b49c237</t>
+          <t>https://www.indeed.com/viewjob?jk=d8b9759a865fb48a</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Customer Solution Architect — Arango AI Product Suite</t>
+          <t>AWS Cloud</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ARANGO</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Kafka, Snowflake, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,19 +706,19 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=632508141e5e7e23</t>
+          <t>https://www.indeed.com/viewjob?jk=42e3c5912b49c237</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AWS Solutions Architect</t>
+          <t>Customer Solution Architect — Arango AI Product Suite</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>ARANGO</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, ECS, IAM, RDS, Scala</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Kafka, Snowflake, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf903a5bb459577f</t>
+          <t>https://www.indeed.com/viewjob?jk=632508141e5e7e23</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Azure Databricks Architect Healthcare Payer</t>
+          <t>AWS Solutions Architect</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>VeeRteq Solutions Inc.</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Hadoop, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5652d49391bd82a2</t>
+          <t>https://www.indeed.com/viewjob?jk=cf903a5bb459577f</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Azure Databricks Architect Healthcare Payer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>VeeRteq Solutions Inc.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Bridgewater, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Hadoop, Hive, Spark, Scala</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Hadoop, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7567cb365890dc6b</t>
+          <t>https://www.indeed.com/viewjob?jk=5652d49391bd82a2</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Digital Pathology (Hybrid)</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Mayo Clinic</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Rochester, MN, US USA</t>
+          <t>Bridgewater, NJ, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, Hive, Spark, Kafka, Snowflake, ELT, Power BI, Tableau, DataOps</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Hadoop, Hive, Spark, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=761b34bda9b68b66</t>
+          <t>https://www.indeed.com/viewjob?jk=7567cb365890dc6b</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Data Engineer - Digital Pathology (Hybrid)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>Mayo Clinic</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Bridgewater, NJ, US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Hadoop, Hive, Spark, Scala</t>
+          <t>Google Cloud Platform, GCP, Hive, Spark, Kafka, Snowflake, ELT, Power BI, Tableau, DataOps</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=177a0dfa7a7c2758</t>
+          <t>https://www.indeed.com/viewjob?jk=761b34bda9b68b66</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Technical Architect</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>REI Systems</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Sterling, VA, US USA</t>
+          <t>Bridgewater, NJ, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, ECS, IAM, RDS, Scala, Oracle, DynamoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Hadoop, Hive, Spark, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,42 +916,42 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=175f2d223e3312d6</t>
+          <t>https://www.indeed.com/viewjob?jk=177a0dfa7a7c2758</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - ITS4</t>
+          <t>Senior Technical Architect</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>State of Minnesota - Minnesota IT Services</t>
+          <t>REI Systems</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Sterling, VA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark</t>
+          <t>AWS, Lambda, API Gateway, ECS, IAM, RDS, Scala, Oracle, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1054e208948fd6fb</t>
+          <t>https://www.indeed.com/viewjob?jk=175f2d223e3312d6</t>
         </is>
       </c>
     </row>
@@ -993,17 +993,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Senior Data Engineer - ITS4</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Hunt Military Communities</t>
+          <t>State of Minnesota - Minnesota IT Services</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Azure, Scala</t>
+          <t>AWS, Glue, S3, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29325c8c8e335924</t>
+          <t>https://www.indeed.com/viewjob?jk=1054e208948fd6fb</t>
         </is>
       </c>
     </row>
@@ -1098,7 +1098,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Solutions Engineer - HYBRID/NC RESIDENTS ONLY</t>
+          <t>Data Engineer - HYBRID/NC RESIDENTS ONLY</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1133,17 +1133,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Reporting Engineer</t>
+          <t>AI Native Developer- EST</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Hitachi Energy</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,34 +1151,34 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MySQL, Star Schema, Fact Tables, Dimension Tables</t>
+          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59ef3d85179316f9</t>
+          <t>https://www.indeed.com/viewjob?jk=37e94025d78d00b3</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineering LMTS</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Bloomerang</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, Google Cloud Platform, BigQuery, Scala, Snowflake, PostgreSQL, MySQL</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0eff179e948461c2</t>
+          <t>https://www.indeed.com/viewjob?jk=572e8633b0661a80</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>AI Native Developer- EST</t>
+          <t>Databricks Architect</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>Confiz</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bentonville, AR, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,34 +1221,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Google Cloud Platform, Cloud Storage, Spark, PySpark</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37e94025d78d00b3</t>
+          <t>https://www.indeed.com/viewjob?jk=18be742c481fa20b</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Software Engineering LMTS</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, NoSQL</t>
+          <t>AWS, Kinesis, SQS, SNS, RDS, Azure, Oracle, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=572e8633b0661a80</t>
+          <t>https://www.indeed.com/viewjob?jk=1916ff73e89dbf5f</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Databricks Architect</t>
+          <t>Software Engineer, New College Graduate,</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Confiz</t>
+          <t>Teradyne</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Bentonville, AR, US USA</t>
+          <t>North Reading, MA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,42 +1291,42 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Google Cloud Platform, Cloud Storage, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18be742c481fa20b</t>
+          <t>https://www.indeed.com/viewjob?jk=4a9c723d1fa4a196</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Software Engineer, New College Graduate,</t>
+          <t>Software Engineer III - Risk Decision Technology</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Teradyne</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>North Reading, MA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, S3, RDS, GCP, BigQuery, Dataflow, Hadoop, Hive, HBase, Kafka</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a9c723d1fa4a196</t>
+          <t>https://www.indeed.com/viewjob?jk=9cecf643a53b2209</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Cloud Solutions Engineer – Azure</t>
+          <t>Associate Cloud Data Engineer II</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Amway</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Ada, MI, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Hadoop, Spark, Scala</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc23fc3c19075d7c</t>
+          <t>https://www.indeed.com/viewjob?jk=ab4ff42758b01e3c</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer (HYBRID)</t>
+          <t>Cloud Solutions Engineer – Azure</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Equinox</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, Scala, DynamoDB, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22216c34e7397891</t>
+          <t>https://www.indeed.com/viewjob?jk=dc23fc3c19075d7c</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Snowflake Platform Engineer</t>
+          <t>Senior AI Security Automation Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>State Street</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Groton, CT, US USA</t>
+          <t>Quincy, MA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Snowflake, Time Travel, clustering keys, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, ELT</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5ad590ea8a95921</t>
+          <t>https://www.indeed.com/viewjob?jk=1acc92079f390921</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior AI Security Automation Engineer</t>
+          <t>Senior Snowflake Platform Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>State Street</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Quincy, MA, US USA</t>
+          <t>Groton, CT, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,34 +1466,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, ELT</t>
+          <t>AWS, IAM, RDS, Scala, Snowflake, Time Travel, clustering keys, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1063ffb870d53611</t>
+          <t>https://www.indeed.com/viewjob?jk=c5ad590ea8a95921</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Software Engineering Intern</t>
+          <t>Senior AI Security Automation Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Copart, Inc</t>
+          <t>State Street</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Quincy, MA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, ELT</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7bf2ebcfa4a5f5e</t>
+          <t>https://www.indeed.com/viewjob?jk=1063ffb870d53611</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Sr. SW Engineer</t>
+          <t>Software Engineering Intern</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Copart, Inc</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Foster City, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, Data Modeling, ETL, Splunk, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f774d387b35a5b8</t>
+          <t>https://www.indeed.com/viewjob?jk=c7bf2ebcfa4a5f5e</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Traackr</t>
+          <t>Fairlife, LLC</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Data Modeling, ETL, ELT, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Medallion Architecture, Spark, PySpark, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df567011cf662897</t>
+          <t>https://www.indeed.com/viewjob?jk=34038fa38ced9dcd</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Sr. SW Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Bridgewater, NJ, US USA</t>
+          <t>Foster City, CA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, ETL, ELT, Power BI</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, Data Modeling, ETL, Splunk, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,42 +1616,42 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=786fbdb63698b11b</t>
+          <t>https://www.indeed.com/viewjob?jk=8f774d387b35a5b8</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>Traackr</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Bridgewater, NJ, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Data Modeling, ETL, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d193f030168c94d0</t>
+          <t>https://www.indeed.com/viewjob?jk=df567011cf662897</t>
         </is>
       </c>
     </row>
@@ -1693,17 +1693,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer with Sales Incentive Compensation (SIC)</t>
+          <t>Data Platform &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>UNIFY SOLUTIONS INC</t>
+          <t>Indigenous Pact PBC</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, GCP, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb057adb6c59f5ff</t>
+          <t>https://www.indeed.com/viewjob?jk=d8deaa38cca423e7</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer (AWS / Java / Node.js / Python) CONTRACT</t>
+          <t>Data Platform &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Broadridge</t>
+          <t>Indigenous Pact PBC</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Edgewood, NY, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Scala, PostgreSQL, DynamoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98d7e7ab4a96ab08</t>
+          <t>https://www.indeed.com/viewjob?jk=d1649dc6e6d00bbb</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior AI Solutions Architect</t>
+          <t>Data Platform &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Neo4j</t>
+          <t>Indigenous Pact PBC</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Hadoop, Hive, Spark, Scala, NoSQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0dbb073f20120e13</t>
+          <t>https://www.indeed.com/viewjob?jk=4211cb353fe7a94e</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Solution Architect - Java/J2EE</t>
+          <t>Data Platform &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>PNC Financial Services Group</t>
+          <t>Indigenous Pact PBC</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Farmers Branch, TX, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MongoDB, Cassandra</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a23b5c57a47b265</t>
+          <t>https://www.indeed.com/viewjob?jk=24f9b2c310f5bfa3</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Software Architect - Java/Spring Boot/Kafka</t>
+          <t>Data Platform &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>PNC Financial Services Group</t>
+          <t>Indigenous Pact PBC</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MongoDB, Cassandra</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f929c4ac83ec17b7</t>
+          <t>https://www.indeed.com/viewjob?jk=58f8c703d51d3a40</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Software Engineering SMTS</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Bridgewater, NJ, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98a642ee513df5f7</t>
+          <t>https://www.indeed.com/viewjob?jk=786fbdb63698b11b</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Powertrain Applications Engineer</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Bridgewater, NJ, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, SQL Server, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af00d281c82c2777</t>
+          <t>https://www.indeed.com/viewjob?jk=d193f030168c94d0</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Databricks Data Engineer with Sales Incentive Compensation (SIC)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>NetApp</t>
+          <t>UNIFY SOLUTIONS INC</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Morrisville, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, GCP, Scala</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0844aea628b28dab</t>
+          <t>https://www.indeed.com/viewjob?jk=eb057adb6c59f5ff</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior AI Solutions Architect</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>datAvail</t>
+          <t>Neo4j</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Hadoop, Hive, Spark, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b02e7a9293c05e9</t>
+          <t>https://www.indeed.com/viewjob?jk=0dbb073f20120e13</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>AI &amp; Data Engineer, Data Discovery Services</t>
+          <t>Senior Solution Architect - Java/J2EE</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Bristol Myers Squibb</t>
+          <t>PNC Financial Services Group</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Farmers Branch, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, ECS, RDS, Azure, Databricks, Vertex AI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9331d42b3835041a</t>
+          <t>https://www.indeed.com/viewjob?jk=3a23b5c57a47b265</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Databricks Platform Engineer</t>
+          <t>Software Architect - Java/Spring Boot/Kafka</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Confiz</t>
+          <t>PNC Financial Services Group</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Bentonville, AR, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Google Cloud Platform, Spark, Scala, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b713352ad723441</t>
+          <t>https://www.indeed.com/viewjob?jk=f929c4ac83ec17b7</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Bricks Data Engineer</t>
+          <t>Software Engineering SMTS</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Bavel systems LLP</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, GCP, Scala, Kafka</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d997e2a6aa4fbed</t>
+          <t>https://www.indeed.com/viewjob?jk=98a642ee513df5f7</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Java Product Engineer</t>
+          <t>Powertrain Applications Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Diaconia, LLC.</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, Oracle, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
+          <t>AWS, S3, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, SQL Server, ELT</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,59 +2141,59 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed19f7417f9c2e59</t>
+          <t>https://www.indeed.com/viewjob?jk=af00d281c82c2777</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Sr. Software Engineer (AWS / Java / Node.js / Python) CONTRACT</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Broadridge</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Edgewood, NY, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Azure, Snowflake, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Scala, PostgreSQL, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87d9611a04bffadf</t>
+          <t>https://www.indeed.com/viewjob?jk=98d7e7ab4a96ab08</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Full Stack</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>datAvail</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Hopkins, MN, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB, Cassandra</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=caea23a7afe82982</t>
+          <t>https://www.indeed.com/viewjob?jk=0b02e7a9293c05e9</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Full Stack</t>
+          <t>AI &amp; Data Engineer, Data Discovery Services</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Bristol Myers Squibb</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB, Cassandra</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, ECS, RDS, Azure, Databricks, Vertex AI</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c6c9dc97e7a8c55</t>
+          <t>https://www.indeed.com/viewjob?jk=9331d42b3835041a</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Full Stack</t>
+          <t>Databricks Platform Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Confiz</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Brookfield, WI, US USA</t>
+          <t>Bentonville, AR, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB, Cassandra</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Google Cloud Platform, Spark, Scala, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97ef6349d26627c1</t>
+          <t>https://www.indeed.com/viewjob?jk=5b713352ad723441</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Specialist - Data Engineering</t>
+          <t>Java Product Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>Diaconia, LLC.</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,164 +2306,164 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Spark, Scala, SQL Server, ETL, Tableau, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, Azure, Scala, Kafka, Oracle, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55c8d9fe21fbf89b</t>
+          <t>https://www.indeed.com/viewjob?jk=ed19f7417f9c2e59</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Cloud DevOps Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Mastronardi Produce</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Livonia, MI, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, MLOps, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Azure, Snowflake, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fa1ca8e2ddf6df8</t>
+          <t>https://www.indeed.com/viewjob?jk=87d9611a04bffadf</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Cloud Systems Engineer III</t>
+          <t>Senior Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Orange County's Credit Union</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Santa Ana, CA, US USA</t>
+          <t>Hopkins, MN, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, Scala, ELT, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37e9b523a42f1787</t>
+          <t>https://www.indeed.com/viewjob?jk=caea23a7afe82982</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Python Software Architect</t>
+          <t>Senior Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Scala, Oracle, SQL Server, PostgreSQL, DynamoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51db177a53e7ef14</t>
+          <t>https://www.indeed.com/viewjob?jk=2c6c9dc97e7a8c55</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Brookfield, WI, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, PostgreSQL, MySQL, Splunk, Maven</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1d1f01448956ac8</t>
+          <t>https://www.indeed.com/viewjob?jk=97ef6349d26627c1</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Specialist - Data Engineering</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2477,38 +2477,38 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, PostgreSQL, MySQL, Splunk, Maven</t>
+          <t>RDS, Hadoop, Spark, Scala, SQL Server, ETL, Tableau, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c9d86fee622b07b</t>
+          <t>https://www.indeed.com/viewjob?jk=55c8d9fe21fbf89b</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Analyst (Data Solutions)</t>
+          <t>Cloud DevOps Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company</t>
+          <t>Mastronardi Produce</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Livonia, MI, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI, Tableau, Git</t>
+          <t>AWS, RDS, Azure, MLOps, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60db44428bef76ed</t>
+          <t>https://www.indeed.com/viewjob?jk=7fa1ca8e2ddf6df8</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Java Engineer</t>
+          <t>Cloud Systems Engineer III</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>Orange County's Credit Union</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Santa Ana, CA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, MongoDB</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Scala, ELT, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9eed61967883578e</t>
+          <t>https://www.indeed.com/viewjob?jk=37e9b523a42f1787</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Full Stack .NET Developer – C#, React, Azure/AWS</t>
+          <t>Python Software Architect</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>J2B GLOBAL LLC</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MongoDB, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Glue, S3, RDS, Scala, Oracle, SQL Server, PostgreSQL, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ceec9a4f672d1616</t>
+          <t>https://www.indeed.com/viewjob?jk=51db177a53e7ef14</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Application Support Engineer</t>
+          <t>Software Engineer, MTS, Enterprise Security, Identity &amp; Access Management</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Availity, LLC.</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MongoDB</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b138daabe966037</t>
+          <t>https://www.indeed.com/viewjob?jk=08079db08d267e47</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Engineer (Azure &amp; Snowflake) - Remote</t>
+          <t>Application Support Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Mindex</t>
+          <t>Availity, LLC.</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Data Lake Storage, Cloud Storage, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, S3, IAM, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,129 +2666,129 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=329cdc7ca8132e90</t>
+          <t>https://www.indeed.com/viewjob?jk=7b138daabe966037</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Engineer (Azure &amp; Snowflake) - Remote</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Mindex</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Data Lake Storage, Cloud Storage, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, PostgreSQL, MySQL, Splunk, Maven</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a4ebf0e5f5c11c0</t>
+          <t>https://www.indeed.com/viewjob?jk=b1d1f01448956ac8</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Engineer (Azure &amp; Snowflake) - Remote</t>
+          <t>Java Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Mindex</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Data Lake Storage, Cloud Storage, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c6a06a8d28780bf</t>
+          <t>https://www.indeed.com/viewjob?jk=9eed61967883578e</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Engineer (Azure &amp; Snowflake) - Remote</t>
+          <t>Data Analyst (Data Solutions)</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Mindex</t>
+          <t>The Coca-Cola Company</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Data Lake Storage, Cloud Storage, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI, Tableau, Git</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd6304cc9580794e</t>
+          <t>https://www.indeed.com/viewjob?jk=60db44428bef76ed</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Sr Cloud Engineer</t>
+          <t>Junior Data Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Lennar</t>
+          <t>Techfield</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, IAM, RDS</t>
+          <t>AWS, S3, Azure, Hadoop, Hive, Spark, Scala, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0b237d7cb0a351b</t>
+          <t>https://www.indeed.com/viewjob?jk=95557e0528468ca2</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Junior Data Engineer</t>
+          <t>Reporting Solutions Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Techfield</t>
+          <t>Wpromote, LLC</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Hadoop, Hive, Spark, Scala, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, dbt, Tableau</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95557e0528468ca2</t>
+          <t>https://www.indeed.com/viewjob?jk=1cad2ebf6af99a7d</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Forward Deployed Data Engineer</t>
+          <t>Data Engineer (Azure &amp; Snowflake) - Remote</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>CoorsTek</t>
+          <t>Mindex</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Golden, CO, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Data Modeling, ETL, ELT, Power BI</t>
+          <t>Azure, Data Factory, Data Lake Storage, Cloud Storage, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01c677c253d655bb</t>
+          <t>https://www.indeed.com/viewjob?jk=329cdc7ca8132e90</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer (Azure &amp; Snowflake) - Remote</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Foley</t>
+          <t>Mindex</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Medallion Architecture, Scala, Data Modeling, ETL</t>
+          <t>Azure, Data Factory, Data Lake Storage, Cloud Storage, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb528101e5b7e6f0</t>
+          <t>https://www.indeed.com/viewjob?jk=7a4ebf0e5f5c11c0</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer (Azure &amp; Snowflake) - Remote</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Unity Technologies</t>
+          <t>Mindex</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
+          <t>Azure, Data Factory, Data Lake Storage, Cloud Storage, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=652b63d35a6266a3</t>
+          <t>https://www.indeed.com/viewjob?jk=7c6a06a8d28780bf</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Sr. Database Administrator</t>
+          <t>Data Engineer (Azure &amp; Snowflake) - Remote</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Vertafore</t>
+          <t>Mindex</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, Terraform, Git</t>
+          <t>Azure, Data Factory, Data Lake Storage, Cloud Storage, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=652e6c19792a8b61</t>
+          <t>https://www.indeed.com/viewjob?jk=cd6304cc9580794e</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Solution Architect – Data Migration &amp; Analytics</t>
+          <t>Sr Cloud Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Zensar Technologies</t>
+          <t>Lennar</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, RDS, Data Lake Storage, Medallion Architecture, Scala, Snowflake, Data Modeling, dbt</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, IAM, RDS</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f7b9a9c0a9082ee</t>
+          <t>https://www.indeed.com/viewjob?jk=d0b237d7cb0a351b</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Forward Deployed Data Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>SpyCloud</t>
+          <t>CoorsTek</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Golden, CO, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Databricks, Spark, Scala, DynamoDB, ETL</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b990fe917577735</t>
+          <t>https://www.indeed.com/viewjob?jk=01c677c253d655bb</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Full-Stack AI Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Micron Technology</t>
+          <t>Foley</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Medallion Architecture, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb2b319c05d2be3e</t>
+          <t>https://www.indeed.com/viewjob?jk=fb528101e5b7e6f0</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>SR SOFTWARE ENGINEER</t>
+          <t>Sr. Solutions Architect - Public Sector (SLED)</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Dollar General</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Goodlettsville, TN, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>S3, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, Cassandra, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, ELT</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbb1d7ed6fd57469</t>
+          <t>https://www.indeed.com/viewjob?jk=deaebb012d17a528</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Security Data Analyst - Parsing</t>
+          <t>Sr. Database Administrator</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>SpyCloud</t>
+          <t>Vertafore</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, API Gateway, RDS, Databricks, NoSQL, ETL, CI/CD</t>
+          <t>AWS, Redshift, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, Terraform, Git</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=589dd47eef0f8740</t>
+          <t>https://www.indeed.com/viewjob?jk=652e6c19792a8b61</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Security Data Analyst - Parsing</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>SpyCloud</t>
+          <t>Unity Technologies</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,42 +3181,42 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, API Gateway, RDS, Databricks, NoSQL, ETL, CI/CD</t>
+          <t>RDS, Azure, Google Cloud Platform, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=171de003fe5563fb</t>
+          <t>https://www.indeed.com/viewjob?jk=652b63d35a6266a3</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Northwest Federal Credit Union</t>
+          <t>SpyCloud</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, MySQL, Azure DevOps, Terraform, Azure Monitor</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Databricks, Spark, Scala, DynamoDB, ETL</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,32 +3226,32 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7291a950f8ec410d</t>
+          <t>https://www.indeed.com/viewjob?jk=7a2f212e69e1f862</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Software Engineer II - Platform Engineer/Databricks</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>SpyCloud</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Jenkins, Maven, Terraform, Jenkins, Git</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Databricks, Spark, Scala, DynamoDB, ETL</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,32 +3261,32 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4448bee09655101c</t>
+          <t>https://www.indeed.com/viewjob?jk=8b990fe917577735</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Full-Stack AI Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>State Street</t>
+          <t>Micron Technology</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Quincy, MA, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Splunk, CI/CD, Jenkins, Terraform, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,129 +3296,129 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb61fc433cd2352b</t>
+          <t>https://www.indeed.com/viewjob?jk=cb2b319c05d2be3e</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Sr Datawarehouse Architect for New York City NY</t>
+          <t>SR SOFTWARE ENGINEER</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Centillion Infotech LLC</t>
+          <t>Dollar General</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Goodlettsville, TN, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, Scala, Data Modeling, ETL, ELT, Python, SQL</t>
+          <t>S3, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, Cassandra, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a11b6e886c2b743d</t>
+          <t>https://www.indeed.com/viewjob?jk=fbb1d7ed6fd57469</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Security Data Analyst - Parsing</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>TaxSlayer</t>
+          <t>SpyCloud</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Augusta, GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, SQS, API Gateway, RDS, Databricks, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e38ede1f1c848056</t>
+          <t>https://www.indeed.com/viewjob?jk=589dd47eef0f8740</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Security Data Analyst - Parsing</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>TaxSlayer</t>
+          <t>SpyCloud</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Evans, GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, SQS, API Gateway, RDS, Databricks, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9cec52a87c2914b</t>
+          <t>https://www.indeed.com/viewjob?jk=171de003fe5563fb</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Sr Datawarehouse Architect for New York City NY</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>TaxSlayer</t>
+          <t>Centillion Infotech LLC</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>North Augusta, SC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Spark, Scala, Data Modeling, ETL, ELT, Python, SQL</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f84a2d5bc189bc0</t>
+          <t>https://www.indeed.com/viewjob?jk=a11b6e886c2b743d</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>TaxSlayer</t>
+          <t>Northwest Federal Credit Union</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Augusta, GA, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, MySQL, Azure DevOps, Terraform, Azure Monitor</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9540e403cb0fe0bc</t>
+          <t>https://www.indeed.com/viewjob?jk=7291a950f8ec410d</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Software Engineer II - Platform Engineer/Databricks</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>TaxSlayer</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Aiken, SC, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,34 +3496,34 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Jenkins, Maven, Terraform, Jenkins, Git</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39572bc0cbf1e1ab</t>
+          <t>https://www.indeed.com/viewjob?jk=4448bee09655101c</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Senior .NET Developer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>TaxSlayer</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Grovetown, GA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,34 +3531,34 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Lambda, ECS, Scala, Kafka, SQL Server, PostgreSQL, NoSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f96379913f2a0b13</t>
+          <t>https://www.indeed.com/viewjob?jk=35a2c65d6f2f7d06</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior .NET Developer</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Karsun Solutions LLC</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, Scala, Kafka, SQL Server, PostgreSQL, NoSQL, Data Modeling, CI/CD</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35a2c65d6f2f7d06</t>
+          <t>https://www.indeed.com/viewjob?jk=2f81c0ec4956c9db</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Karsun Solutions LLC</t>
+          <t>TaxSlayer</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Augusta, GA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,34 +3601,34 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f81c0ec4956c9db</t>
+          <t>https://www.indeed.com/viewjob?jk=e38ede1f1c848056</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Architect</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Mass General Brigham</t>
+          <t>TaxSlayer</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Somerville, MA, US USA</t>
+          <t>Evans, GA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,34 +3636,34 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dccbfd697359c720</t>
+          <t>https://www.indeed.com/viewjob?jk=f9cec52a87c2914b</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior Software Engineer IV / V (Java, React, AWS)</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Auto.Live</t>
+          <t>TaxSlayer</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>North Augusta, SC, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,34 +3671,34 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, SQS, Scala, Kafka, MySQL, CI/CD, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42c2207352100be0</t>
+          <t>https://www.indeed.com/viewjob?jk=1f84a2d5bc189bc0</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Sr Devops Engineer</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>_coderio</t>
+          <t>TaxSlayer</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Augusta, GA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,34 +3706,34 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=541df4abc8320b5a</t>
+          <t>https://www.indeed.com/viewjob?jk=9540e403cb0fe0bc</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>AI Software Engineer IV</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>The Standard Insurance</t>
+          <t>TaxSlayer</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Aiken, SC, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,34 +3741,34 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, MLflow, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3c232645c82fc83</t>
+          <t>https://www.indeed.com/viewjob?jk=39572bc0cbf1e1ab</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Sr. Business Intelligence Engineer</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Crane Worldwide Logistics</t>
+          <t>TaxSlayer</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Grovetown, GA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,34 +3776,34 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Snowflake, Data Modeling, dbt, Power BI, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53344a199a269470</t>
+          <t>https://www.indeed.com/viewjob?jk=f96379913f2a0b13</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Senior Software Engineer ( Seattle/Provo)</t>
+          <t>Sr Devops Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Press Ganey</t>
+          <t>_coderio</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Provo, UT, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, Data Modeling, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b27efa8ed4a1f97</t>
+          <t>https://www.indeed.com/viewjob?jk=541df4abc8320b5a</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Senior R&amp;D Software Engineer, Fivetran AI</t>
+          <t>AI Software Engineer IV</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Fivetran</t>
+          <t>The Standard Insurance</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, BigQuery, Snowflake, ETL, ELT, dbt, Docker</t>
+          <t>RDS, Azure, Databricks, Scala, MLflow, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55c8e7c6018043d4</t>
+          <t>https://www.indeed.com/viewjob?jk=b3c232645c82fc83</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Senior R&amp;D Software Engineer, Fivetran AI</t>
+          <t>Sr. Business Intelligence Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Fivetran</t>
+          <t>Crane Worldwide Logistics</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, BigQuery, Snowflake, ETL, ELT, dbt, Docker</t>
+          <t>AWS, RDS, Azure, Snowflake, Data Modeling, dbt, Power BI, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30bf0451dbc419d1</t>
+          <t>https://www.indeed.com/viewjob?jk=53344a199a269470</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Senior R&amp;D Software Engineer, Fivetran AI</t>
+          <t>Senior Software Engineer ( Seattle/Provo)</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Fivetran</t>
+          <t>Press Ganey</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Provo, UT, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, BigQuery, Snowflake, ETL, ELT, dbt, Docker</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, Data Modeling, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=501671e22555fe5c</t>
+          <t>https://www.indeed.com/viewjob?jk=1b27efa8ed4a1f97</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8b8baa922f2b05a</t>
+          <t>https://www.indeed.com/viewjob?jk=55c8e7c6018043d4</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Database Developer</t>
+          <t>Senior R&amp;D Software Engineer, Fivetran AI</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Integres, LLC</t>
+          <t>Fivetran</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,34 +3986,34 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>RDS, Azure, Spark, PySpark, SQL Server, Data Modeling, ETL, Power BI, Jenkins, Azure DevOps</t>
+          <t>AWS, RDS, Databricks, GCP, BigQuery, Snowflake, ETL, ELT, dbt, Docker</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc8d97653729dfa4</t>
+          <t>https://www.indeed.com/viewjob?jk=30bf0451dbc419d1</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Database Developer</t>
+          <t>Senior R&amp;D Software Engineer, Fivetran AI</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Hollstadt Consulting</t>
+          <t>Fivetran</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>RDS, Azure, Spark, PySpark, SQL Server, Data Modeling, ETL, Power BI, Jenkins, Azure DevOps</t>
+          <t>AWS, RDS, Databricks, GCP, BigQuery, Snowflake, ETL, ELT, dbt, Docker</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdef6e08804da8cc</t>
+          <t>https://www.indeed.com/viewjob?jk=501671e22555fe5c</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>AI &amp; Machine Learning Engineer</t>
+          <t>Senior R&amp;D Software Engineer, Fivetran AI</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>OneBlood</t>
+          <t>Fivetran</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Saint Petersburg, FL, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,15 +4056,85 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
+          <t>AWS, RDS, Databricks, GCP, BigQuery, Snowflake, ETL, ELT, dbt, Docker</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f8b8baa922f2b05a</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Database Developer</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Integres, LLC</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Saint Paul, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Spark, PySpark, SQL Server, Data Modeling, ETL, Power BI, Jenkins, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cc8d97653729dfa4</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>AI &amp; Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>OneBlood</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Saint Petersburg, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
           <t>AWS, Azure, Medallion Architecture, ETL, ELT, CI/CD, Git, Python, SQL, R</t>
         </is>
       </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=9242f2d7ab83418a</t>
         </is>

--- a/results/job_matches_2026-07-21.xlsx
+++ b/results/job_matches_2026-07-21.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G106"/>
+  <dimension ref="A1:G108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -748,52 +748,52 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AWS Solutions Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Sedgwick</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, ECS, IAM, RDS, Scala</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, IAM, RDS, Azure, Data Factory, Blob Storage</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf903a5bb459577f</t>
+          <t>https://www.indeed.com/viewjob?jk=0c782baa6dabb867</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Azure Databricks Architect Healthcare Payer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>VeeRteq Solutions Inc.</t>
+          <t>Sedgwick</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,77 +801,77 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Hadoop, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, IAM, RDS, Azure, Data Factory, Blob Storage</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5652d49391bd82a2</t>
+          <t>https://www.indeed.com/viewjob?jk=377853022880bb36</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>Sedgwick</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Bridgewater, NJ, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Hadoop, Hive, Spark, Scala</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, IAM, RDS, Azure, Data Factory, Blob Storage</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7567cb365890dc6b</t>
+          <t>https://www.indeed.com/viewjob?jk=f2003e26eeb22b6c</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Digital Pathology (Hybrid)</t>
+          <t>Azure Databricks Architect Healthcare Payer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Mayo Clinic</t>
+          <t>VeeRteq Solutions Inc.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Rochester, MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, Hive, Spark, Kafka, Snowflake, ELT, Power BI, Tableau, DataOps</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Hadoop, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=761b34bda9b68b66</t>
+          <t>https://www.indeed.com/viewjob?jk=5652d49391bd82a2</t>
         </is>
       </c>
     </row>
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=177a0dfa7a7c2758</t>
+          <t>https://www.indeed.com/viewjob?jk=7567cb365890dc6b</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Technical Architect</t>
+          <t>Senior Data Engineer - Digital Pathology (Hybrid)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>REI Systems</t>
+          <t>Mayo Clinic</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Sterling, VA, US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, ECS, IAM, RDS, Scala, Oracle, DynamoDB, NoSQL</t>
+          <t>Google Cloud Platform, GCP, Hive, Spark, Kafka, Snowflake, ELT, Power BI, Tableau, DataOps</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=175f2d223e3312d6</t>
+          <t>https://www.indeed.com/viewjob?jk=761b34bda9b68b66</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Software Engineer III - Data/Payments Technology</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Bridgewater, NJ, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Scala, Kafka, Snowflake, Oracle</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Hadoop, Hive, Spark, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,102 +986,102 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8366ecb2495ecb5</t>
+          <t>https://www.indeed.com/viewjob?jk=177a0dfa7a7c2758</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - ITS4</t>
+          <t>Senior Technical Architect</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>State of Minnesota - Minnesota IT Services</t>
+          <t>REI Systems</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Sterling, VA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark</t>
+          <t>AWS, Lambda, API Gateway, ECS, IAM, RDS, Scala, Oracle, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1054e208948fd6fb</t>
+          <t>https://www.indeed.com/viewjob?jk=175f2d223e3312d6</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Engineer II - (Remote)</t>
+          <t>Senior DevOps Engineer (NOAA badge required)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Fanatics Betting &amp; Gaming</t>
+          <t>Element 84</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Alexandria, VA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Databricks, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
+          <t>AWS, Glue, Redshift, Athena, API Gateway, RDS, Azure, Databricks, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54fa68f69cf2083f</t>
+          <t>https://www.indeed.com/viewjob?jk=034929104db4d3fc</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Reporting Engineer</t>
+          <t>Software Engineer III - Data/Payments Technology</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Hitachi Rail</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MySQL, Star Schema, Fact Tables, Dimension Tables</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,94 +1091,94 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7504d94e8707d02b</t>
+          <t>https://www.indeed.com/viewjob?jk=c8366ecb2495ecb5</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Engineer - HYBRID/NC RESIDENTS ONLY</t>
+          <t>Senior Data Engineer - ITS4</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>PowerSecure Inc.</t>
+          <t>State of Minnesota - Minnesota IT Services</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, S3, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc9b66f689cbeefb</t>
+          <t>https://www.indeed.com/viewjob?jk=1054e208948fd6fb</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>AI Native Developer- EST</t>
+          <t>Data Engineer II - (Remote)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>Fanatics Betting &amp; Gaming</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
+          <t>AWS, S3, RDS, Databricks, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37e94025d78d00b3</t>
+          <t>https://www.indeed.com/viewjob?jk=54fa68f69cf2083f</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Software Engineering LMTS</t>
+          <t>.Net Engineer-Data Engineering</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,34 +1186,34 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, NoSQL</t>
+          <t>Azure, Data Factory, Scala, Snowflake, SQL Server, PostgreSQL, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=572e8633b0661a80</t>
+          <t>https://www.indeed.com/viewjob?jk=90c0e5d8f944baf1</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Databricks Architect</t>
+          <t>Reporting Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Confiz</t>
+          <t>Hitachi Rail</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Bentonville, AR, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Google Cloud Platform, Cloud Storage, Spark, PySpark</t>
+          <t>AWS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MySQL, Star Schema, Fact Tables, Dimension Tables</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18be742c481fa20b</t>
+          <t>https://www.indeed.com/viewjob?jk=7504d94e8707d02b</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>AI Native Developer- EST</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, SNS, RDS, Azure, Oracle, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1916ff73e89dbf5f</t>
+          <t>https://www.indeed.com/viewjob?jk=37e94025d78d00b3</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Software Engineer, New College Graduate,</t>
+          <t>Software Engineering LMTS</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Teradyne</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>North Reading, MA, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,42 +1291,42 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a9c723d1fa4a196</t>
+          <t>https://www.indeed.com/viewjob?jk=572e8633b0661a80</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Software Engineer III - Risk Decision Technology</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, GCP, BigQuery, Dataflow, Hadoop, Hive, HBase, Kafka</t>
+          <t>AWS, Kinesis, SQS, SNS, RDS, Azure, Oracle, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,94 +1336,94 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9cecf643a53b2209</t>
+          <t>https://www.indeed.com/viewjob?jk=1916ff73e89dbf5f</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Associate Cloud Data Engineer II</t>
+          <t>Databricks Architect</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Amway</t>
+          <t>Confiz</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Ada, MI, US USA</t>
+          <t>Bentonville, AR, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Hadoop, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Google Cloud Platform, Cloud Storage, Spark, PySpark</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab4ff42758b01e3c</t>
+          <t>https://www.indeed.com/viewjob?jk=18be742c481fa20b</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Cloud Solutions Engineer – Azure</t>
+          <t>Software Engineer, New College Graduate,</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Teradyne</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>North Reading, MA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc23fc3c19075d7c</t>
+          <t>https://www.indeed.com/viewjob?jk=4a9c723d1fa4a196</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior AI Security Automation Engineer</t>
+          <t>Software Engineer III - Risk Decision Technology</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>State Street</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Quincy, MA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, ELT</t>
+          <t>AWS, S3, RDS, GCP, BigQuery, Dataflow, Hadoop, Hive, HBase, Kafka</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1acc92079f390921</t>
+          <t>https://www.indeed.com/viewjob?jk=9cecf643a53b2209</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Snowflake Platform Engineer</t>
+          <t>Associate Cloud Data Engineer II</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Amway</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Groton, CT, US USA</t>
+          <t>Ada, MI, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,34 +1466,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Snowflake, Time Travel, clustering keys, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Hadoop, Spark, Scala</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5ad590ea8a95921</t>
+          <t>https://www.indeed.com/viewjob?jk=ab4ff42758b01e3c</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior AI Security Automation Engineer</t>
+          <t>Cloud Solutions Engineer – Azure</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>State Street</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Quincy, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1063ffb870d53611</t>
+          <t>https://www.indeed.com/viewjob?jk=dc23fc3c19075d7c</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Software Engineering Intern</t>
+          <t>Senior AI Security Automation Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Copart, Inc</t>
+          <t>State Street</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Quincy, MA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,17 +1536,17 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, ELT</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7bf2ebcfa4a5f5e</t>
+          <t>https://www.indeed.com/viewjob?jk=1acc92079f390921</t>
         </is>
       </c>
     </row>
@@ -1588,17 +1588,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Sr. SW Engineer</t>
+          <t>Senior Snowflake Platform Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Foster City, CA, US USA</t>
+          <t>Groton, CT, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, Data Modeling, ETL, Splunk, CI/CD, Terraform</t>
+          <t>AWS, IAM, RDS, Scala, Snowflake, Time Travel, clustering keys, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f774d387b35a5b8</t>
+          <t>https://www.indeed.com/viewjob?jk=c5ad590ea8a95921</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior AI Security Automation Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Traackr</t>
+          <t>State Street</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Quincy, MA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,52 +1641,52 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Data Modeling, ETL, ELT, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, ELT</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df567011cf662897</t>
+          <t>https://www.indeed.com/viewjob?jk=1063ffb870d53611</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Big Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Highmark Health</t>
+          <t>Traackr</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Hive, Spark, Scala, Kafka, Oracle</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Data Modeling, ETL, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d94c95081afe04c8</t>
+          <t>https://www.indeed.com/viewjob?jk=df567011cf662897</t>
         </is>
       </c>
     </row>
@@ -1938,17 +1938,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer with Sales Incentive Compensation (SIC)</t>
+          <t>Sr. Software Engineer (AWS / Java / Node.js / Python) CONTRACT</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>UNIFY SOLUTIONS INC</t>
+          <t>Broadridge</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Edgewood, NY, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, GCP, Scala</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Scala, PostgreSQL, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb057adb6c59f5ff</t>
+          <t>https://www.indeed.com/viewjob?jk=98d7e7ab4a96ab08</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior AI Solutions Architect</t>
+          <t>Cybersecurity Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Neo4j</t>
+          <t>Leidos</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Hadoop, Hive, Spark, Scala, NoSQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ELT, CI/CD, Azure DevOps, Kubernetes</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0dbb073f20120e13</t>
+          <t>https://www.indeed.com/viewjob?jk=baa14defff29cc46</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Solution Architect - Java/J2EE</t>
+          <t>Senior AI Solutions Architect</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>PNC Financial Services Group</t>
+          <t>Neo4j</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Farmers Branch, TX, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,24 +2026,24 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MongoDB, Cassandra</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Hadoop, Hive, Spark, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a23b5c57a47b265</t>
+          <t>https://www.indeed.com/viewjob?jk=0dbb073f20120e13</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Software Architect - Java/Spring Boot/Kafka</t>
+          <t>Senior Solution Architect - Java/J2EE</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Farmers Branch, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f929c4ac83ec17b7</t>
+          <t>https://www.indeed.com/viewjob?jk=3a23b5c57a47b265</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Software Engineering SMTS</t>
+          <t>Software Architect - Java/Spring Boot/Kafka</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>PNC Financial Services Group</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98a642ee513df5f7</t>
+          <t>https://www.indeed.com/viewjob?jk=f929c4ac83ec17b7</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Powertrain Applications Engineer</t>
+          <t>Software Engineering SMTS</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, SQL Server, ELT</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af00d281c82c2777</t>
+          <t>https://www.indeed.com/viewjob?jk=98a642ee513df5f7</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer (AWS / Java / Node.js / Python) CONTRACT</t>
+          <t>Powertrain Applications Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Broadridge</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Edgewood, NY, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,17 +2166,17 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Scala, PostgreSQL, DynamoDB, CI/CD</t>
+          <t>AWS, S3, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, SQL Server, ELT</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98d7e7ab4a96ab08</t>
+          <t>https://www.indeed.com/viewjob?jk=af00d281c82c2777</t>
         </is>
       </c>
     </row>
@@ -2288,17 +2288,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Java Product Engineer</t>
+          <t>AWS Devops Cloud Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Diaconia, LLC.</t>
+          <t>Onebridge</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, Oracle, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
+          <t>AWS, Lambda, Redshift, S3, ECS, IAM, RDS, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed19f7417f9c2e59</t>
+          <t>https://www.indeed.com/viewjob?jk=9b690190bc20de39</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Software Engineer - .NET / APIS</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Securiport</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Azure, Snowflake, CI/CD, Jenkins</t>
+          <t>AWS, Azure, Scala, Kafka, SQL Server, MySQL, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87d9611a04bffadf</t>
+          <t>https://www.indeed.com/viewjob?jk=c3893b067061f946</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Full Stack</t>
+          <t>Software Engineer - .NET / SES</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Securiport</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Hopkins, MN, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB, Cassandra</t>
+          <t>AWS, Azure, Scala, Kafka, SQL Server, MySQL, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=caea23a7afe82982</t>
+          <t>https://www.indeed.com/viewjob?jk=93ea5f1fa5709b99</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Full Stack</t>
+          <t>Java Product Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Diaconia, LLC.</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB, Cassandra</t>
+          <t>AWS, Azure, Scala, Kafka, Oracle, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c6c9dc97e7a8c55</t>
+          <t>https://www.indeed.com/viewjob?jk=ed19f7417f9c2e59</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Full Stack</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Brookfield, WI, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB, Cassandra</t>
+          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Azure, Snowflake, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97ef6349d26627c1</t>
+          <t>https://www.indeed.com/viewjob?jk=87d9611a04bffadf</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Specialist - Data Engineering</t>
+          <t>Senior Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Hopkins, MN, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Spark, Scala, SQL Server, ETL, Tableau, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,32 +2491,32 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55c8d9fe21fbf89b</t>
+          <t>https://www.indeed.com/viewjob?jk=caea23a7afe82982</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Cloud DevOps Engineer</t>
+          <t>Senior Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Mastronardi Produce</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Livonia, MI, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, MLOps, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,94 +2526,94 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fa1ca8e2ddf6df8</t>
+          <t>https://www.indeed.com/viewjob?jk=2c6c9dc97e7a8c55</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Cloud Systems Engineer III</t>
+          <t>Senior Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Orange County's Credit Union</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Santa Ana, CA, US USA</t>
+          <t>Brookfield, WI, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, Scala, ELT, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37e9b523a42f1787</t>
+          <t>https://www.indeed.com/viewjob?jk=97ef6349d26627c1</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Python Software Architect</t>
+          <t>Specialist - Data Engineering</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Scala, Oracle, SQL Server, PostgreSQL, DynamoDB, CI/CD</t>
+          <t>RDS, Hadoop, Spark, Scala, SQL Server, ETL, Tableau, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51db177a53e7ef14</t>
+          <t>https://www.indeed.com/viewjob?jk=55c8d9fe21fbf89b</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Software Engineer, MTS, Enterprise Security, Identity &amp; Access Management</t>
+          <t>Cloud DevOps Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Mastronardi Produce</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Livonia, MI, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, MLOps, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08079db08d267e47</t>
+          <t>https://www.indeed.com/viewjob?jk=7fa1ca8e2ddf6df8</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Application Support Engineer</t>
+          <t>Cloud Systems Engineer III</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Availity, LLC.</t>
+          <t>Orange County's Credit Union</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Santa Ana, CA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MongoDB</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Scala, ELT, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b138daabe966037</t>
+          <t>https://www.indeed.com/viewjob?jk=37e9b523a42f1787</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Application Support Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>Availity, LLC.</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, PostgreSQL, MySQL, Splunk, Maven</t>
+          <t>AWS, S3, IAM, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1d1f01448956ac8</t>
+          <t>https://www.indeed.com/viewjob?jk=7b138daabe966037</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Java Engineer</t>
+          <t>Software Engineer, MTS, Enterprise Security, Identity &amp; Access Management</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, MongoDB</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9eed61967883578e</t>
+          <t>https://www.indeed.com/viewjob?jk=08079db08d267e47</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Analyst (Data Solutions)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI, Tableau, Git</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, PostgreSQL, MySQL, Splunk, Maven</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,59 +2771,59 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60db44428bef76ed</t>
+          <t>https://www.indeed.com/viewjob?jk=b1d1f01448956ac8</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Junior Data Engineer</t>
+          <t>Data Analyst (Data Solutions)</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Techfield</t>
+          <t>The Coca-Cola Company</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Hadoop, Hive, Spark, Scala, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI, Tableau, Git</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95557e0528468ca2</t>
+          <t>https://www.indeed.com/viewjob?jk=60db44428bef76ed</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Reporting Solutions Engineer</t>
+          <t>Junior Data Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Wpromote, LLC</t>
+          <t>Techfield</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, dbt, Tableau</t>
+          <t>AWS, S3, Azure, Hadoop, Hive, Spark, Scala, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cad2ebf6af99a7d</t>
+          <t>https://www.indeed.com/viewjob?jk=95557e0528468ca2</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Engineer (Azure &amp; Snowflake) - Remote</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Mindex</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Data Lake Storage, Cloud Storage, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, Google Cloud Platform, GCP, Hadoop, Scala, Snowflake, ETL, ELT, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=329cdc7ca8132e90</t>
+          <t>https://www.indeed.com/viewjob?jk=6c875e063114bb1c</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Data Engineer (Azure &amp; Snowflake) - Remote</t>
+          <t>Reporting Solutions Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Mindex</t>
+          <t>Wpromote, LLC</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Data Lake Storage, Cloud Storage, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, dbt, Tableau</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a4ebf0e5f5c11c0</t>
+          <t>https://www.indeed.com/viewjob?jk=1cad2ebf6af99a7d</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c6a06a8d28780bf</t>
+          <t>https://www.indeed.com/viewjob?jk=329cdc7ca8132e90</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd6304cc9580794e</t>
+          <t>https://www.indeed.com/viewjob?jk=7a4ebf0e5f5c11c0</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Sr Cloud Engineer</t>
+          <t>Data Engineer (Azure &amp; Snowflake) - Remote</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Lennar</t>
+          <t>Mindex</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, IAM, RDS</t>
+          <t>Azure, Data Factory, Data Lake Storage, Cloud Storage, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0b237d7cb0a351b</t>
+          <t>https://www.indeed.com/viewjob?jk=7c6a06a8d28780bf</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Forward Deployed Data Engineer</t>
+          <t>Data Engineer (Azure &amp; Snowflake) - Remote</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>CoorsTek</t>
+          <t>Mindex</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Golden, CO, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Data Modeling, ETL, ELT, Power BI</t>
+          <t>Azure, Data Factory, Data Lake Storage, Cloud Storage, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01c677c253d655bb</t>
+          <t>https://www.indeed.com/viewjob?jk=cd6304cc9580794e</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr Cloud Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Foley</t>
+          <t>Lennar</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,34 +3076,34 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Medallion Architecture, Scala, Data Modeling, ETL</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, IAM, RDS</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb528101e5b7e6f0</t>
+          <t>https://www.indeed.com/viewjob?jk=d0b237d7cb0a351b</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Sr. Solutions Architect - Public Sector (SLED)</t>
+          <t>DBHDS - SQL Database Administrator</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Betis Group, Inc.</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, ELT</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=deaebb012d17a528</t>
+          <t>https://www.indeed.com/viewjob?jk=9b671e1c355c84c5</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Sr. Database Administrator</t>
+          <t>Forward Deployed Data Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Vertafore</t>
+          <t>CoorsTek</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Golden, CO, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, Terraform, Git</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=652e6c19792a8b61</t>
+          <t>https://www.indeed.com/viewjob?jk=01c677c253d655bb</t>
         </is>
       </c>
     </row>
@@ -3198,17 +3198,17 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Backend Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>SpyCloud</t>
+          <t>Ubiety</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Databricks, Spark, Scala, DynamoDB, ETL</t>
+          <t>AWS, Kinesis, RDS, GCP, Scala, Kafka, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a2f212e69e1f862</t>
+          <t>https://www.indeed.com/viewjob?jk=8fd4531981abb3e6</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Solutions Architect - Public Sector (SLED)</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>SpyCloud</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Databricks, Spark, Scala, DynamoDB, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, ELT</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b990fe917577735</t>
+          <t>https://www.indeed.com/viewjob?jk=9d898f82946c9db3</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Full-Stack AI Engineer</t>
+          <t>Sr. Solutions Architect - Public Sector (SLED)</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Micron Technology</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, ELT</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb2b319c05d2be3e</t>
+          <t>https://www.indeed.com/viewjob?jk=deaebb012d17a528</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>SR SOFTWARE ENGINEER</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Dollar General</t>
+          <t>SpyCloud</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Goodlettsville, TN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>S3, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, Cassandra, CI/CD, Docker</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Databricks, Spark, Scala, DynamoDB, ETL</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbb1d7ed6fd57469</t>
+          <t>https://www.indeed.com/viewjob?jk=7a2f212e69e1f862</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Security Data Analyst - Parsing</t>
+          <t>Full-Stack AI Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>SpyCloud</t>
+          <t>Micron Technology</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, API Gateway, RDS, Databricks, NoSQL, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=589dd47eef0f8740</t>
+          <t>https://www.indeed.com/viewjob?jk=cb2b319c05d2be3e</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Security Data Analyst - Parsing</t>
+          <t>SR SOFTWARE ENGINEER</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>SpyCloud</t>
+          <t>Dollar General</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Goodlettsville, TN, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, API Gateway, RDS, Databricks, NoSQL, ETL, CI/CD</t>
+          <t>S3, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, Cassandra, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,129 +3401,129 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=171de003fe5563fb</t>
+          <t>https://www.indeed.com/viewjob?jk=fbb1d7ed6fd57469</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Sr Datawarehouse Architect for New York City NY</t>
+          <t>Security Data Analyst - Parsing</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Centillion Infotech LLC</t>
+          <t>SpyCloud</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, Scala, Data Modeling, ETL, ELT, Python, SQL</t>
+          <t>AWS, Lambda, S3, SQS, API Gateway, RDS, Databricks, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a11b6e886c2b743d</t>
+          <t>https://www.indeed.com/viewjob?jk=589dd47eef0f8740</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Northwest Federal Credit Union</t>
+          <t>We Write Code</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, MySQL, Azure DevOps, Terraform, Azure Monitor</t>
+          <t>AWS, Glue, Redshift, S3, ECS, IAM, Azure, Snowflake, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7291a950f8ec410d</t>
+          <t>https://www.indeed.com/viewjob?jk=0821497679584e2d</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Software Engineer II - Platform Engineer/Databricks</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Unum</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Jenkins, Maven, Terraform, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, AWS CloudFormation, Jenkins</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4448bee09655101c</t>
+          <t>https://www.indeed.com/viewjob?jk=04a647a34b37a72a</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior .NET Developer</t>
+          <t>Sr Datawarehouse Architect for New York City NY</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Centillion Infotech LLC</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,34 +3531,34 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, Scala, Kafka, SQL Server, PostgreSQL, NoSQL, Data Modeling, CI/CD</t>
+          <t>RDS, Azure, Databricks, Spark, Scala, Data Modeling, ETL, ELT, Python, SQL</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35a2c65d6f2f7d06</t>
+          <t>https://www.indeed.com/viewjob?jk=a11b6e886c2b743d</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Karsun Solutions LLC</t>
+          <t>Northwest Federal Credit Union</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, MySQL, Azure DevOps, Terraform, Azure Monitor</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f81c0ec4956c9db</t>
+          <t>https://www.indeed.com/viewjob?jk=7291a950f8ec410d</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Platform Engineer, Data Services</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>TaxSlayer</t>
+          <t>Vytalize Health</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Augusta, GA, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, EMR, Athena, RDS, Databricks, GCP, Scala, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e38ede1f1c848056</t>
+          <t>https://www.indeed.com/viewjob?jk=00036ac2c3d4f673</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>TaxSlayer</t>
+          <t>College Board</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Evans, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, Scala, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9cec52a87c2914b</t>
+          <t>https://www.indeed.com/viewjob?jk=78ac72ba3ec01f22</t>
         </is>
       </c>
     </row>
@@ -3658,12 +3658,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>TaxSlayer</t>
+          <t>Rhodes Financial Services</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>North Augusta, SC, US USA</t>
+          <t>Augusta, GA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f84a2d5bc189bc0</t>
+          <t>https://www.indeed.com/viewjob?jk=291d753a3842da49</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Senior .NET Developer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>TaxSlayer</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Augusta, GA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,34 +3706,34 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Lambda, ECS, Scala, Kafka, SQL Server, PostgreSQL, NoSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9540e403cb0fe0bc</t>
+          <t>https://www.indeed.com/viewjob?jk=35a2c65d6f2f7d06</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>TaxSlayer</t>
+          <t>Karsun Solutions LLC</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Aiken, SC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,17 +3741,17 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39572bc0cbf1e1ab</t>
+          <t>https://www.indeed.com/viewjob?jk=2f81c0ec4956c9db</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Grovetown, GA, US USA</t>
+          <t>Augusta, GA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f96379913f2a0b13</t>
+          <t>https://www.indeed.com/viewjob?jk=e38ede1f1c848056</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Sr Devops Engineer</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>_coderio</t>
+          <t>TaxSlayer</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Evans, GA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,34 +3811,34 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=541df4abc8320b5a</t>
+          <t>https://www.indeed.com/viewjob?jk=f9cec52a87c2914b</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>AI Software Engineer IV</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>The Standard Insurance</t>
+          <t>TaxSlayer</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>North Augusta, SC, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,34 +3846,34 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, MLflow, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3c232645c82fc83</t>
+          <t>https://www.indeed.com/viewjob?jk=1f84a2d5bc189bc0</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Sr. Business Intelligence Engineer</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Crane Worldwide Logistics</t>
+          <t>TaxSlayer</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Augusta, GA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,34 +3881,34 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Snowflake, Data Modeling, dbt, Power BI, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53344a199a269470</t>
+          <t>https://www.indeed.com/viewjob?jk=9540e403cb0fe0bc</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Senior Software Engineer ( Seattle/Provo)</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Press Ganey</t>
+          <t>TaxSlayer</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Provo, UT, US USA</t>
+          <t>Aiken, SC, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,34 +3916,34 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, Data Modeling, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b27efa8ed4a1f97</t>
+          <t>https://www.indeed.com/viewjob?jk=39572bc0cbf1e1ab</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Senior R&amp;D Software Engineer, Fivetran AI</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Fivetran</t>
+          <t>TaxSlayer</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Grovetown, GA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,34 +3951,34 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, BigQuery, Snowflake, ETL, ELT, dbt, Docker</t>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55c8e7c6018043d4</t>
+          <t>https://www.indeed.com/viewjob?jk=f96379913f2a0b13</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Senior R&amp;D Software Engineer, Fivetran AI</t>
+          <t>Sr Devops Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Fivetran</t>
+          <t>_coderio</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, BigQuery, Snowflake, ETL, ELT, dbt, Docker</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30bf0451dbc419d1</t>
+          <t>https://www.indeed.com/viewjob?jk=541df4abc8320b5a</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Senior R&amp;D Software Engineer, Fivetran AI</t>
+          <t>AI Software Engineer IV</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Fivetran</t>
+          <t>The Standard Insurance</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, BigQuery, Snowflake, ETL, ELT, dbt, Docker</t>
+          <t>RDS, Azure, Databricks, Scala, MLflow, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=501671e22555fe5c</t>
+          <t>https://www.indeed.com/viewjob?jk=b3c232645c82fc83</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Senior R&amp;D Software Engineer, Fivetran AI</t>
+          <t>Database Developer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Fivetran</t>
+          <t>Integres, LLC</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,34 +4056,34 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, BigQuery, Snowflake, ETL, ELT, dbt, Docker</t>
+          <t>RDS, Azure, Spark, PySpark, SQL Server, Data Modeling, ETL, Power BI, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8b8baa922f2b05a</t>
+          <t>https://www.indeed.com/viewjob?jk=cc8d97653729dfa4</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Database Developer</t>
+          <t>Senior R&amp;D Software Engineer, Fivetran AI</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Integres, LLC</t>
+          <t>Fivetran</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,34 +4091,34 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>RDS, Azure, Spark, PySpark, SQL Server, Data Modeling, ETL, Power BI, Jenkins, Azure DevOps</t>
+          <t>AWS, RDS, Databricks, GCP, BigQuery, Snowflake, ETL, ELT, dbt, Docker</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc8d97653729dfa4</t>
+          <t>https://www.indeed.com/viewjob?jk=55c8e7c6018043d4</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>AI &amp; Machine Learning Engineer</t>
+          <t>Senior R&amp;D Software Engineer, Fivetran AI</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>OneBlood</t>
+          <t>Fivetran</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Saint Petersburg, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, Azure, Medallion Architecture, ETL, ELT, CI/CD, Git, Python, SQL, R</t>
+          <t>AWS, RDS, Databricks, GCP, BigQuery, Snowflake, ETL, ELT, dbt, Docker</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,7 +4136,77 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9242f2d7ab83418a</t>
+          <t>https://www.indeed.com/viewjob?jk=30bf0451dbc419d1</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Senior R&amp;D Software Engineer, Fivetran AI</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Fivetran</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, GCP, BigQuery, Snowflake, ETL, ELT, dbt, Docker</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=501671e22555fe5c</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Senior R&amp;D Software Engineer, Fivetran AI</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Fivetran</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Oakland, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, GCP, BigQuery, Snowflake, ETL, ELT, dbt, Docker</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f8b8baa922f2b05a</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-07-21.xlsx
+++ b/results/job_matches_2026-07-21.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G108"/>
+  <dimension ref="A1:G104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,60 +468,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Databricks Data Operations Specialist</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>iSynergy IT</t>
+          <t>Scicom Infrastructure Services</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>21.5</v>
+        <v>28.5</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, Synapse Analytics, Databricks, GCP, BigQuery</t>
+          <t>AWS, Glue, Kinesis, S3, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64aa04af21957dc5</t>
+          <t>https://www.indeed.com/viewjob?jk=d63447d1670f0092</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Software Developer II - Meter Data Management Software (Full Stack, Databricks)</t>
+          <t>Databricks Data Engineer / Business Analyst – Data Contracts &amp; OCDS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>National Information Solutions Cooperative (NISC)</t>
+          <t>Scicom Infrastructure Services</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Bismarck, ND, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.8</v>
+        <v>22.9</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, SQS, SNS, RDS, Databricks, Spark, Scala</t>
+          <t>AWS, Glue, S3, RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,7 +531,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09a0c773ba869ab2</t>
+          <t>https://www.indeed.com/viewjob?jk=da10e92c3ddc831a</t>
         </is>
       </c>
     </row>
@@ -548,7 +548,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Cedar Rapids, IA, US USA</t>
+          <t>Bismarck, ND, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -566,7 +566,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33143989f3362efb</t>
+          <t>https://www.indeed.com/viewjob?jk=09a0c773ba869ab2</t>
         </is>
       </c>
     </row>
@@ -583,7 +583,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Lake Saint Louis, MO, US USA</t>
+          <t>Cedar Rapids, IA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b784c8205aa1d58</t>
+          <t>https://www.indeed.com/viewjob?jk=33143989f3362efb</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Software Developer II - Meter Data Management Software (Full Stack, Databricks)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Luxoft</t>
+          <t>National Information Solutions Cooperative (NISC)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Lake Saint Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>18.1</v>
+        <v>18.8</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Hadoop, HDFS, MapReduce, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, EMR, Lambda, S3, SQS, SNS, RDS, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8438fc0eeeabc119</t>
+          <t>https://www.indeed.com/viewjob?jk=0b784c8205aa1d58</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Engineer - Databricks</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Steampunk</t>
+          <t>Luxoft</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,34 +661,34 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, Step Functions, S3, RDS, Azure, Databricks</t>
+          <t>RDS, Azure, Databricks, Hadoop, HDFS, MapReduce, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8b9759a865fb48a</t>
+          <t>https://www.indeed.com/viewjob?jk=8438fc0eeeabc119</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AWS Cloud</t>
+          <t>Data Engineer - Databricks</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Steampunk</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, ECS, IAM, RDS, Scala</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, Step Functions, S3, RDS, Azure, Databricks</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,19 +706,19 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42e3c5912b49c237</t>
+          <t>https://www.indeed.com/viewjob?jk=d8b9759a865fb48a</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Customer Solution Architect — Arango AI Product Suite</t>
+          <t>AWS Cloud</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ARANGO</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Kafka, Snowflake, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,42 +741,42 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=632508141e5e7e23</t>
+          <t>https://www.indeed.com/viewjob?jk=42e3c5912b49c237</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Customer Solution Architect — Arango AI Product Suite</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Sedgwick</t>
+          <t>ARANGO</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, IAM, RDS, Azure, Data Factory, Blob Storage</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Kafka, Snowflake, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c782baa6dabb867</t>
+          <t>https://www.indeed.com/viewjob?jk=632508141e5e7e23</t>
         </is>
       </c>
     </row>
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=377853022880bb36</t>
+          <t>https://www.indeed.com/viewjob?jk=0c782baa6dabb867</t>
         </is>
       </c>
     </row>
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2003e26eeb22b6c</t>
+          <t>https://www.indeed.com/viewjob?jk=377853022880bb36</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Azure Databricks Architect Healthcare Payer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>VeeRteq Solutions Inc.</t>
+          <t>Sedgwick</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,42 +871,42 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Hadoop, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, IAM, RDS, Azure, Data Factory, Blob Storage</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5652d49391bd82a2</t>
+          <t>https://www.indeed.com/viewjob?jk=f2003e26eeb22b6c</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Azure Databricks Architect Healthcare Payer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>VeeRteq Solutions Inc.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Bridgewater, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Hadoop, Hive, Spark, Scala</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Hadoop, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7567cb365890dc6b</t>
+          <t>https://www.indeed.com/viewjob?jk=5652d49391bd82a2</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Digital Pathology (Hybrid)</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Mayo Clinic</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Rochester, MN, US USA</t>
+          <t>Bridgewater, NJ, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, Hive, Spark, Kafka, Snowflake, ELT, Power BI, Tableau, DataOps</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Hadoop, Hive, Spark, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=761b34bda9b68b66</t>
+          <t>https://www.indeed.com/viewjob?jk=7567cb365890dc6b</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Data Engineer - Digital Pathology (Hybrid)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>Mayo Clinic</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Bridgewater, NJ, US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Hadoop, Hive, Spark, Scala</t>
+          <t>Google Cloud Platform, GCP, Hive, Spark, Kafka, Snowflake, ELT, Power BI, Tableau, DataOps</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=177a0dfa7a7c2758</t>
+          <t>https://www.indeed.com/viewjob?jk=761b34bda9b68b66</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Technical Architect</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>REI Systems</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Sterling, VA, US USA</t>
+          <t>Bridgewater, NJ, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, ECS, IAM, RDS, Scala, Oracle, DynamoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Hadoop, Hive, Spark, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,59 +1021,59 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=175f2d223e3312d6</t>
+          <t>https://www.indeed.com/viewjob?jk=177a0dfa7a7c2758</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer (NOAA badge required)</t>
+          <t>Senior Technical Architect</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Element 84</t>
+          <t>REI Systems</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Alexandria, VA, US USA</t>
+          <t>Sterling, VA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, API Gateway, RDS, Azure, Databricks, Scala, Snowflake</t>
+          <t>AWS, Lambda, API Gateway, ECS, IAM, RDS, Scala, Oracle, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=034929104db4d3fc</t>
+          <t>https://www.indeed.com/viewjob?jk=175f2d223e3312d6</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Software Engineer III - Data/Payments Technology</t>
+          <t>Senior DevOps Engineer (NOAA badge required)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Element 84</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Alexandria, VA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,34 +1081,34 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Scala, Kafka, Snowflake, Oracle</t>
+          <t>AWS, Glue, Redshift, Athena, API Gateway, RDS, Azure, Databricks, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8366ecb2495ecb5</t>
+          <t>https://www.indeed.com/viewjob?jk=034929104db4d3fc</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - ITS4</t>
+          <t>Software Engineer III - Data/Payments Technology</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>State of Minnesota - Minnesota IT Services</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,104 +1116,104 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1054e208948fd6fb</t>
+          <t>https://www.indeed.com/viewjob?jk=c8366ecb2495ecb5</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Engineer II - (Remote)</t>
+          <t>Senior Data Engineer - ITS4</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Fanatics Betting &amp; Gaming</t>
+          <t>State of Minnesota - Minnesota IT Services</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Databricks, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
+          <t>AWS, Glue, S3, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54fa68f69cf2083f</t>
+          <t>https://www.indeed.com/viewjob?jk=1054e208948fd6fb</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>.Net Engineer-Data Engineering</t>
+          <t>Data Engineer II - (Remote)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Fanatics Betting &amp; Gaming</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Scala, Snowflake, SQL Server, PostgreSQL, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, S3, RDS, Databricks, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90c0e5d8f944baf1</t>
+          <t>https://www.indeed.com/viewjob?jk=54fa68f69cf2083f</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Reporting Engineer</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Hitachi Rail</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,34 +1221,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MySQL, Star Schema, Fact Tables, Dimension Tables</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7504d94e8707d02b</t>
+          <t>https://www.indeed.com/viewjob?jk=f950c716669dfe8d</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>AI Native Developer- EST</t>
+          <t>.Net Engineer-Data Engineering</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
+          <t>Azure, Data Factory, Scala, Snowflake, SQL Server, PostgreSQL, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37e94025d78d00b3</t>
+          <t>https://www.indeed.com/viewjob?jk=90c0e5d8f944baf1</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Software Engineering LMTS</t>
+          <t>Reporting Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Hitachi Rail</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, NoSQL</t>
+          <t>AWS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MySQL, Star Schema, Fact Tables, Dimension Tables</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=572e8633b0661a80</t>
+          <t>https://www.indeed.com/viewjob?jk=7504d94e8707d02b</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>AI Native Developer- EST</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, SNS, RDS, Azure, Oracle, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1916ff73e89dbf5f</t>
+          <t>https://www.indeed.com/viewjob?jk=37e94025d78d00b3</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Databricks Architect</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Confiz</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Bentonville, AR, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Google Cloud Platform, Cloud Storage, Spark, PySpark</t>
+          <t>AWS, Kinesis, SQS, SNS, RDS, Azure, Oracle, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18be742c481fa20b</t>
+          <t>https://www.indeed.com/viewjob?jk=1916ff73e89dbf5f</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Software Engineer, New College Graduate,</t>
+          <t>Databricks Architect</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Teradyne</t>
+          <t>Confiz</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>North Reading, MA, US USA</t>
+          <t>Bentonville, AR, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,42 +1396,42 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Google Cloud Platform, Cloud Storage, Spark, PySpark</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a9c723d1fa4a196</t>
+          <t>https://www.indeed.com/viewjob?jk=18be742c481fa20b</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Software Engineer III - Risk Decision Technology</t>
+          <t>Software Engineer, New College Graduate,</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Teradyne</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>North Reading, MA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, GCP, BigQuery, Dataflow, Hadoop, Hive, HBase, Kafka</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9cecf643a53b2209</t>
+          <t>https://www.indeed.com/viewjob?jk=4a9c723d1fa4a196</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Associate Cloud Data Engineer II</t>
+          <t>Software Engineer III - Risk Decision Technology</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Amway</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Ada, MI, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,34 +1466,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Hadoop, Spark, Scala</t>
+          <t>AWS, S3, RDS, GCP, BigQuery, Dataflow, Hadoop, Hive, HBase, Kafka</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab4ff42758b01e3c</t>
+          <t>https://www.indeed.com/viewjob?jk=9cecf643a53b2209</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Cloud Solutions Engineer – Azure</t>
+          <t>Associate Cloud Data Engineer II</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Amway</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Ada, MI, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Hadoop, Spark, Scala</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc23fc3c19075d7c</t>
+          <t>https://www.indeed.com/viewjob?jk=ab4ff42758b01e3c</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior AI Security Automation Engineer</t>
+          <t>Cloud Solutions Engineer – Azure</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>State Street</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Quincy, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1acc92079f390921</t>
+          <t>https://www.indeed.com/viewjob?jk=dc23fc3c19075d7c</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior AI Security Automation Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Fairlife, LLC</t>
+          <t>State Street</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Quincy, MA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Medallion Architecture, Spark, PySpark, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, ELT</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34038fa38ced9dcd</t>
+          <t>https://www.indeed.com/viewjob?jk=1acc92079f390921</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Snowflake Platform Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Fairlife, LLC</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Groton, CT, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Snowflake, Time Travel, clustering keys, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Medallion Architecture, Spark, PySpark, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5ad590ea8a95921</t>
+          <t>https://www.indeed.com/viewjob?jk=34038fa38ced9dcd</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior AI Security Automation Engineer</t>
+          <t>Senior Snowflake Platform Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>State Street</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Quincy, MA, US USA</t>
+          <t>Groton, CT, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, ELT</t>
+          <t>AWS, IAM, RDS, Scala, Snowflake, Time Travel, clustering keys, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1063ffb870d53611</t>
+          <t>https://www.indeed.com/viewjob?jk=c5ad590ea8a95921</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior AI Security Automation Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Traackr</t>
+          <t>State Street</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Quincy, MA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,42 +1676,42 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Data Modeling, ETL, ELT, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, ELT</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df567011cf662897</t>
+          <t>https://www.indeed.com/viewjob?jk=1063ffb870d53611</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Platform &amp; Analytics Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Indigenous Pact PBC</t>
+          <t>Traackr</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Data Modeling, ETL, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8deaa38cca423e7</t>
+          <t>https://www.indeed.com/viewjob?jk=df567011cf662897</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1649dc6e6d00bbb</t>
+          <t>https://www.indeed.com/viewjob?jk=d8deaa38cca423e7</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4211cb353fe7a94e</t>
+          <t>https://www.indeed.com/viewjob?jk=d1649dc6e6d00bbb</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24f9b2c310f5bfa3</t>
+          <t>https://www.indeed.com/viewjob?jk=4211cb353fe7a94e</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58f8c703d51d3a40</t>
+          <t>https://www.indeed.com/viewjob?jk=24f9b2c310f5bfa3</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Data Platform &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>Indigenous Pact PBC</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Bridgewater, NJ, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,17 +1886,17 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=786fbdb63698b11b</t>
+          <t>https://www.indeed.com/viewjob?jk=58f8c703d51d3a40</t>
         </is>
       </c>
     </row>
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d193f030168c94d0</t>
+          <t>https://www.indeed.com/viewjob?jk=786fbdb63698b11b</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer (AWS / Java / Node.js / Python) CONTRACT</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Broadridge</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Edgewood, NY, US USA</t>
+          <t>Bridgewater, NJ, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,17 +1956,17 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Scala, PostgreSQL, DynamoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98d7e7ab4a96ab08</t>
+          <t>https://www.indeed.com/viewjob?jk=d193f030168c94d0</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Software Engineer - .NET / APIS</t>
+          <t>Java Product Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Securiport</t>
+          <t>Diaconia, LLC.</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, SQL Server, MySQL, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, Azure, Scala, Kafka, Oracle, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3893b067061f946</t>
+          <t>https://www.indeed.com/viewjob?jk=ed19f7417f9c2e59</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Software Engineer - .NET / SES</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Securiport</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, SQL Server, MySQL, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Azure, Snowflake, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93ea5f1fa5709b99</t>
+          <t>https://www.indeed.com/viewjob?jk=87d9611a04bffadf</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Java Product Engineer</t>
+          <t>Senior Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Diaconia, LLC.</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Hopkins, MN, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, Oracle, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed19f7417f9c2e59</t>
+          <t>https://www.indeed.com/viewjob?jk=caea23a7afe82982</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,17 +2446,17 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Azure, Snowflake, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87d9611a04bffadf</t>
+          <t>https://www.indeed.com/viewjob?jk=2c6c9dc97e7a8c55</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Hopkins, MN, US USA</t>
+          <t>Brookfield, WI, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=caea23a7afe82982</t>
+          <t>https://www.indeed.com/viewjob?jk=97ef6349d26627c1</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Full Stack</t>
+          <t>Specialist - Data Engineering</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB, Cassandra</t>
+          <t>RDS, Hadoop, Spark, Scala, SQL Server, ETL, Tableau, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,32 +2526,32 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c6c9dc97e7a8c55</t>
+          <t>https://www.indeed.com/viewjob?jk=55c8d9fe21fbf89b</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Full Stack</t>
+          <t>Cloud DevOps Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Mastronardi Produce</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Brookfield, WI, US USA</t>
+          <t>Livonia, MI, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB, Cassandra</t>
+          <t>AWS, RDS, Azure, MLOps, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,59 +2561,59 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97ef6349d26627c1</t>
+          <t>https://www.indeed.com/viewjob?jk=7fa1ca8e2ddf6df8</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Specialist - Data Engineering</t>
+          <t>Cloud Systems Engineer III</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>Orange County's Credit Union</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Santa Ana, CA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Spark, Scala, SQL Server, ETL, Tableau, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Scala, ELT, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55c8d9fe21fbf89b</t>
+          <t>https://www.indeed.com/viewjob?jk=37e9b523a42f1787</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Cloud DevOps Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Mastronardi Produce</t>
+          <t>University of Idaho</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Livonia, MI, US USA</t>
+          <t>Moscow, ID, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, MLOps, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Databricks Lakehouse, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fa1ca8e2ddf6df8</t>
+          <t>https://www.indeed.com/viewjob?jk=c2714c15bcc60033</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Cloud Systems Engineer III</t>
+          <t>Application Support Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Orange County's Credit Union</t>
+          <t>Availity, LLC.</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Santa Ana, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, Scala, ELT, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, S3, IAM, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37e9b523a42f1787</t>
+          <t>https://www.indeed.com/viewjob?jk=7b138daabe966037</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Application Support Engineer</t>
+          <t>Software Engineer, MTS, Enterprise Security, Identity &amp; Access Management</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Availity, LLC.</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MongoDB</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b138daabe966037</t>
+          <t>https://www.indeed.com/viewjob?jk=08079db08d267e47</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Software Engineer, MTS, Enterprise Security, Identity &amp; Access Management</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,77 +2726,77 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, PostgreSQL, MySQL, Splunk, Maven</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08079db08d267e47</t>
+          <t>https://www.indeed.com/viewjob?jk=b1d1f01448956ac8</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Junior Data Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>Techfield</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, PostgreSQL, MySQL, Splunk, Maven</t>
+          <t>AWS, S3, Azure, Hadoop, Hive, Spark, Scala, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1d1f01448956ac8</t>
+          <t>https://www.indeed.com/viewjob?jk=95557e0528468ca2</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Analyst (Data Solutions)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI, Tableau, Git</t>
+          <t>AWS, Google Cloud Platform, GCP, Hadoop, Scala, Snowflake, ETL, ELT, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60db44428bef76ed</t>
+          <t>https://www.indeed.com/viewjob?jk=6c875e063114bb1c</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Junior Data Engineer</t>
+          <t>Reporting Solutions Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Techfield</t>
+          <t>Wpromote, LLC</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Hadoop, Hive, Spark, Scala, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, dbt, Tableau</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95557e0528468ca2</t>
+          <t>https://www.indeed.com/viewjob?jk=1cad2ebf6af99a7d</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer (Azure &amp; Snowflake) - Remote</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Mindex</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Google Cloud Platform, GCP, Hadoop, Scala, Snowflake, ETL, ELT, CI/CD, Airflow</t>
+          <t>Azure, Data Factory, Data Lake Storage, Cloud Storage, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c875e063114bb1c</t>
+          <t>https://www.indeed.com/viewjob?jk=329cdc7ca8132e90</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Reporting Solutions Engineer</t>
+          <t>Data Engineer (Azure &amp; Snowflake) - Remote</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Wpromote, LLC</t>
+          <t>Mindex</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, dbt, Tableau</t>
+          <t>Azure, Data Factory, Data Lake Storage, Cloud Storage, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cad2ebf6af99a7d</t>
+          <t>https://www.indeed.com/viewjob?jk=7a4ebf0e5f5c11c0</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=329cdc7ca8132e90</t>
+          <t>https://www.indeed.com/viewjob?jk=7c6a06a8d28780bf</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a4ebf0e5f5c11c0</t>
+          <t>https://www.indeed.com/viewjob?jk=cd6304cc9580794e</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Data Engineer (Azure &amp; Snowflake) - Remote</t>
+          <t>Sr Cloud Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Mindex</t>
+          <t>Lennar</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Data Lake Storage, Cloud Storage, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, IAM, RDS</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c6a06a8d28780bf</t>
+          <t>https://www.indeed.com/viewjob?jk=d0b237d7cb0a351b</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Data Engineer (Azure &amp; Snowflake) - Remote</t>
+          <t>DBHDS - SQL Database Administrator</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Mindex</t>
+          <t>Betis Group, Inc.</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Data Lake Storage, Cloud Storage, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd6304cc9580794e</t>
+          <t>https://www.indeed.com/viewjob?jk=9b671e1c355c84c5</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Sr Cloud Engineer</t>
+          <t>Forward Deployed Data Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Lennar</t>
+          <t>CoorsTek</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Golden, CO, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,34 +3076,34 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, IAM, RDS</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0b237d7cb0a351b</t>
+          <t>https://www.indeed.com/viewjob?jk=01c677c253d655bb</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>DBHDS - SQL Database Administrator</t>
+          <t>Senior Backend Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Betis Group, Inc.</t>
+          <t>Ubiety</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
+          <t>AWS, Kinesis, RDS, GCP, Scala, Kafka, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b671e1c355c84c5</t>
+          <t>https://www.indeed.com/viewjob?jk=8fd4531981abb3e6</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Forward Deployed Data Engineer</t>
+          <t>Solutions Architect - Public Sector (SLED)</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>CoorsTek</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Golden, CO, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, ELT</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01c677c253d655bb</t>
+          <t>https://www.indeed.com/viewjob?jk=9d898f82946c9db3</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr. Solutions Architect - Public Sector (SLED)</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Unity Technologies</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, ELT</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=652b63d35a6266a3</t>
+          <t>https://www.indeed.com/viewjob?jk=deaebb012d17a528</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Ubiety</t>
+          <t>SpyCloud</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, GCP, Scala, Kafka, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Databricks, Spark, Scala, DynamoDB, ETL</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fd4531981abb3e6</t>
+          <t>https://www.indeed.com/viewjob?jk=7a2f212e69e1f862</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Solutions Architect - Public Sector (SLED)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Unity Technologies</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, ELT</t>
+          <t>RDS, Azure, Google Cloud Platform, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d898f82946c9db3</t>
+          <t>https://www.indeed.com/viewjob?jk=652b63d35a6266a3</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Sr. Solutions Architect - Public Sector (SLED)</t>
+          <t>Full-Stack AI Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Micron Technology</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=deaebb012d17a528</t>
+          <t>https://www.indeed.com/viewjob?jk=cb2b319c05d2be3e</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>SR SOFTWARE ENGINEER</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>SpyCloud</t>
+          <t>Dollar General</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Goodlettsville, TN, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Databricks, Spark, Scala, DynamoDB, ETL</t>
+          <t>S3, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, Cassandra, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a2f212e69e1f862</t>
+          <t>https://www.indeed.com/viewjob?jk=fbb1d7ed6fd57469</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Full-Stack AI Engineer</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Micron Technology</t>
+          <t>We Write Code</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, Glue, Redshift, S3, ECS, IAM, Azure, Snowflake, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb2b319c05d2be3e</t>
+          <t>https://www.indeed.com/viewjob?jk=0821497679584e2d</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>SR SOFTWARE ENGINEER</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Dollar General</t>
+          <t>Unum</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Goodlettsville, TN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,112 +3391,112 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>S3, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, Cassandra, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, AWS CloudFormation, Jenkins</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbb1d7ed6fd57469</t>
+          <t>https://www.indeed.com/viewjob?jk=04a647a34b37a72a</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Security Data Analyst - Parsing</t>
+          <t>Sr Datawarehouse Architect for New York City NY</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>SpyCloud</t>
+          <t>Centillion Infotech LLC</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, API Gateway, RDS, Databricks, NoSQL, ETL, CI/CD</t>
+          <t>RDS, Azure, Databricks, Spark, Scala, Data Modeling, ETL, ELT, Python, SQL</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=589dd47eef0f8740</t>
+          <t>https://www.indeed.com/viewjob?jk=a11b6e886c2b743d</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>We Write Code</t>
+          <t>Northwest Federal Credit Union</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, ECS, IAM, Azure, Snowflake, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, MySQL, Azure DevOps, Terraform, Azure Monitor</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0821497679584e2d</t>
+          <t>https://www.indeed.com/viewjob?jk=7291a950f8ec410d</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Advanced Specialist, Data Engineering</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Unum</t>
+          <t>Pearson</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Bloomington, MN, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, AWS CloudFormation, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04a647a34b37a72a</t>
+          <t>https://www.indeed.com/viewjob?jk=7d1ad3be6df1730a</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Sr Datawarehouse Architect for New York City NY</t>
+          <t>Platform Engineer, Data Services</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Centillion Infotech LLC</t>
+          <t>Vytalize Health</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, Scala, Data Modeling, ETL, ELT, Python, SQL</t>
+          <t>AWS, EMR, Athena, RDS, Databricks, GCP, Scala, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a11b6e886c2b743d</t>
+          <t>https://www.indeed.com/viewjob?jk=00036ac2c3d4f673</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Northwest Federal Credit Union</t>
+          <t>College Board</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,34 +3566,34 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, MySQL, Azure DevOps, Terraform, Azure Monitor</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, Scala, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7291a950f8ec410d</t>
+          <t>https://www.indeed.com/viewjob?jk=78ac72ba3ec01f22</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Platform Engineer, Data Services</t>
+          <t>Senior .NET Developer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Vytalize Health</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,34 +3601,34 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, EMR, Athena, RDS, Databricks, GCP, Scala, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Lambda, ECS, Scala, Kafka, SQL Server, PostgreSQL, NoSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00036ac2c3d4f673</t>
+          <t>https://www.indeed.com/viewjob?jk=35a2c65d6f2f7d06</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>College Board</t>
+          <t>Rhodes Financial Services</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Augusta, GA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, Scala, DynamoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78ac72ba3ec01f22</t>
+          <t>https://www.indeed.com/viewjob?jk=291d753a3842da49</t>
         </is>
       </c>
     </row>
@@ -3658,7 +3658,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Rhodes Financial Services</t>
+          <t>TaxSlayer</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=291d753a3842da49</t>
+          <t>https://www.indeed.com/viewjob?jk=e38ede1f1c848056</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior .NET Developer</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>TaxSlayer</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Evans, GA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,34 +3706,34 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, Scala, Kafka, SQL Server, PostgreSQL, NoSQL, Data Modeling, CI/CD</t>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35a2c65d6f2f7d06</t>
+          <t>https://www.indeed.com/viewjob?jk=f9cec52a87c2914b</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Karsun Solutions LLC</t>
+          <t>TaxSlayer</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>North Augusta, SC, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,17 +3741,17 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f81c0ec4956c9db</t>
+          <t>https://www.indeed.com/viewjob?jk=1f84a2d5bc189bc0</t>
         </is>
       </c>
     </row>
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e38ede1f1c848056</t>
+          <t>https://www.indeed.com/viewjob?jk=9540e403cb0fe0bc</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Evans, GA, US USA</t>
+          <t>Aiken, SC, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9cec52a87c2914b</t>
+          <t>https://www.indeed.com/viewjob?jk=39572bc0cbf1e1ab</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>North Augusta, SC, US USA</t>
+          <t>Grovetown, GA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f84a2d5bc189bc0</t>
+          <t>https://www.indeed.com/viewjob?jk=f96379913f2a0b13</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Sr Devops Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>TaxSlayer</t>
+          <t>_coderio</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Augusta, GA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,34 +3881,34 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9540e403cb0fe0bc</t>
+          <t>https://www.indeed.com/viewjob?jk=541df4abc8320b5a</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Database Developer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>TaxSlayer</t>
+          <t>Integres, LLC</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Aiken, SC, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>RDS, Azure, Spark, PySpark, SQL Server, Data Modeling, ETL, Power BI, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39572bc0cbf1e1ab</t>
+          <t>https://www.indeed.com/viewjob?jk=cc8d97653729dfa4</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Senior R&amp;D Software Engineer, Fivetran AI</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>TaxSlayer</t>
+          <t>Fivetran</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Grovetown, GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,34 +3951,34 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Databricks, GCP, BigQuery, Snowflake, ETL, ELT, dbt, Docker</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f96379913f2a0b13</t>
+          <t>https://www.indeed.com/viewjob?jk=55c8e7c6018043d4</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Sr Devops Engineer</t>
+          <t>Senior R&amp;D Software Engineer, Fivetran AI</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>_coderio</t>
+          <t>Fivetran</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Databricks, GCP, BigQuery, Snowflake, ETL, ELT, dbt, Docker</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=541df4abc8320b5a</t>
+          <t>https://www.indeed.com/viewjob?jk=30bf0451dbc419d1</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>AI Software Engineer IV</t>
+          <t>Senior R&amp;D Software Engineer, Fivetran AI</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>The Standard Insurance</t>
+          <t>Fivetran</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, MLflow, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Databricks, GCP, BigQuery, Snowflake, ETL, ELT, dbt, Docker</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3c232645c82fc83</t>
+          <t>https://www.indeed.com/viewjob?jk=501671e22555fe5c</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Database Developer</t>
+          <t>Senior R&amp;D Software Engineer, Fivetran AI</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Integres, LLC</t>
+          <t>Fivetran</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,155 +4056,15 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>RDS, Azure, Spark, PySpark, SQL Server, Data Modeling, ETL, Power BI, Jenkins, Azure DevOps</t>
+          <t>AWS, RDS, Databricks, GCP, BigQuery, Snowflake, ETL, ELT, dbt, Docker</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cc8d97653729dfa4</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>Senior R&amp;D Software Engineer, Fivetran AI</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>Fivetran</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D105" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, GCP, BigQuery, Snowflake, ETL, ELT, dbt, Docker</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=55c8e7c6018043d4</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>Senior R&amp;D Software Engineer, Fivetran AI</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>Fivetran</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D106" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, GCP, BigQuery, Snowflake, ETL, ELT, dbt, Docker</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=30bf0451dbc419d1</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>Senior R&amp;D Software Engineer, Fivetran AI</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>Fivetran</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>Denver, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D107" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, GCP, BigQuery, Snowflake, ETL, ELT, dbt, Docker</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=501671e22555fe5c</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>Senior R&amp;D Software Engineer, Fivetran AI</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>Fivetran</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>Oakland, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D108" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, GCP, BigQuery, Snowflake, ETL, ELT, dbt, Docker</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=f8b8baa922f2b05a</t>
         </is>

--- a/results/job_matches_2026-07-21.xlsx
+++ b/results/job_matches_2026-07-21.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G104"/>
+  <dimension ref="A1:G114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,95 +503,95 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer / Business Analyst – Data Contracts &amp; OCDS</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Scicom Infrastructure Services</t>
+          <t>Deltek</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>22.9</v>
+        <v>25.7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables</t>
+          <t>AWS, Glue, EMR, Kinesis, Redshift, S3, RDS, Azure, Data Factory, Databricks</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da10e92c3ddc831a</t>
+          <t>https://www.indeed.com/viewjob?jk=2bf953a2c9ee5bf5</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Software Developer II - Meter Data Management Software (Full Stack, Databricks)</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>National Information Solutions Cooperative (NISC)</t>
+          <t>Deltek</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Bismarck, ND, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.8</v>
+        <v>25.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, SQS, SNS, RDS, Databricks, Spark, Scala</t>
+          <t>AWS, Glue, EMR, Kinesis, Redshift, S3, RDS, Azure, Data Factory, Databricks</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09a0c773ba869ab2</t>
+          <t>https://www.indeed.com/viewjob?jk=9bc6276c79dcfd60</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Software Developer II - Meter Data Management Software (Full Stack, Databricks)</t>
+          <t>Databricks Data Engineer / Business Analyst – Data Contracts &amp; OCDS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>National Information Solutions Cooperative (NISC)</t>
+          <t>Scicom Infrastructure Services</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Cedar Rapids, IA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.8</v>
+        <v>22.9</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, SQS, SNS, RDS, Databricks, Spark, Scala</t>
+          <t>AWS, Glue, S3, RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33143989f3362efb</t>
+          <t>https://www.indeed.com/viewjob?jk=da10e92c3ddc831a</t>
         </is>
       </c>
     </row>
@@ -618,7 +618,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Lake Saint Louis, MO, US USA</t>
+          <t>Bismarck, ND, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b784c8205aa1d58</t>
+          <t>https://www.indeed.com/viewjob?jk=09a0c773ba869ab2</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Software Developer II - Meter Data Management Software (Full Stack, Databricks)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Luxoft</t>
+          <t>National Information Solutions Cooperative (NISC)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Cedar Rapids, IA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>18.1</v>
+        <v>18.8</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Hadoop, HDFS, MapReduce, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, EMR, Lambda, S3, SQS, SNS, RDS, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,54 +671,54 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8438fc0eeeabc119</t>
+          <t>https://www.indeed.com/viewjob?jk=33143989f3362efb</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer - Databricks</t>
+          <t>Software Developer II - Meter Data Management Software (Full Stack, Databricks)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Steampunk</t>
+          <t>National Information Solutions Cooperative (NISC)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Lake Saint Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>18.1</v>
+        <v>18.8</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, Step Functions, S3, RDS, Azure, Databricks</t>
+          <t>AWS, EMR, Lambda, S3, SQS, SNS, RDS, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8b9759a865fb48a</t>
+          <t>https://www.indeed.com/viewjob?jk=0b784c8205aa1d58</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AWS Cloud</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Luxoft</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -731,34 +731,34 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, ECS, IAM, RDS, Scala</t>
+          <t>RDS, Azure, Databricks, Hadoop, HDFS, MapReduce, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42e3c5912b49c237</t>
+          <t>https://www.indeed.com/viewjob?jk=8438fc0eeeabc119</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Customer Solution Architect — Arango AI Product Suite</t>
+          <t>Data Engineer - Databricks</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ARANGO</t>
+          <t>Steampunk</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Kafka, Snowflake, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, Step Functions, S3, RDS, Azure, Databricks</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,42 +776,42 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=632508141e5e7e23</t>
+          <t>https://www.indeed.com/viewjob?jk=d8b9759a865fb48a</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Customer Solution Architect — Arango AI Product Suite</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Sedgwick</t>
+          <t>ARANGO</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, IAM, RDS, Azure, Data Factory, Blob Storage</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Kafka, Snowflake, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c782baa6dabb867</t>
+          <t>https://www.indeed.com/viewjob?jk=632508141e5e7e23</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=377853022880bb36</t>
+          <t>https://www.indeed.com/viewjob?jk=0c782baa6dabb867</t>
         </is>
       </c>
     </row>
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2003e26eeb22b6c</t>
+          <t>https://www.indeed.com/viewjob?jk=377853022880bb36</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Azure Databricks Architect Healthcare Payer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>VeeRteq Solutions Inc.</t>
+          <t>Sedgwick</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,42 +906,42 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Hadoop, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, IAM, RDS, Azure, Data Factory, Blob Storage</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5652d49391bd82a2</t>
+          <t>https://www.indeed.com/viewjob?jk=f2003e26eeb22b6c</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Azure Databricks Architect Healthcare Payer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>VeeRteq Solutions Inc.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Bridgewater, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Hadoop, Hive, Spark, Scala</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Hadoop, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7567cb365890dc6b</t>
+          <t>https://www.indeed.com/viewjob?jk=5652d49391bd82a2</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Digital Pathology (Hybrid)</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Mayo Clinic</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Rochester, MN, US USA</t>
+          <t>Bridgewater, NJ, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, Hive, Spark, Kafka, Snowflake, ELT, Power BI, Tableau, DataOps</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Hadoop, Hive, Spark, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=761b34bda9b68b66</t>
+          <t>https://www.indeed.com/viewjob?jk=7567cb365890dc6b</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Data Engineer - Digital Pathology (Hybrid)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>Mayo Clinic</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Bridgewater, NJ, US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Hadoop, Hive, Spark, Scala</t>
+          <t>Google Cloud Platform, GCP, Hive, Spark, Kafka, Snowflake, ELT, Power BI, Tableau, DataOps</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=177a0dfa7a7c2758</t>
+          <t>https://www.indeed.com/viewjob?jk=761b34bda9b68b66</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Technical Architect</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>REI Systems</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Sterling, VA, US USA</t>
+          <t>Bridgewater, NJ, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, ECS, IAM, RDS, Scala, Oracle, DynamoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Hadoop, Hive, Spark, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=175f2d223e3312d6</t>
+          <t>https://www.indeed.com/viewjob?jk=177a0dfa7a7c2758</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer (NOAA badge required)</t>
+          <t>Data Engineer (RICHMOND, VA, US, 23219)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Element 84</t>
+          <t>Dominion Energy</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Alexandria, VA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, API Gateway, RDS, Azure, Databricks, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Spark Streaming, Kafka, Kafka Connect, Snowflake</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=034929104db4d3fc</t>
+          <t>https://www.indeed.com/viewjob?jk=78b18ba5356fc564</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Software Engineer III - Data/Payments Technology</t>
+          <t>Senior Technical Architect</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>REI Systems</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Sterling, VA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Scala, Kafka, Snowflake, Oracle</t>
+          <t>AWS, Lambda, API Gateway, ECS, IAM, RDS, Scala, Oracle, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8366ecb2495ecb5</t>
+          <t>https://www.indeed.com/viewjob?jk=175f2d223e3312d6</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - ITS4</t>
+          <t>Senior DevOps Engineer (NOAA badge required)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>State of Minnesota - Minnesota IT Services</t>
+          <t>Element 84</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Alexandria, VA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark</t>
+          <t>AWS, Glue, Redshift, Athena, API Gateway, RDS, Azure, Databricks, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,84 +1161,84 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1054e208948fd6fb</t>
+          <t>https://www.indeed.com/viewjob?jk=034929104db4d3fc</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Engineer II - (Remote)</t>
+          <t>Senior Data Engineer - ITS4</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Fanatics Betting &amp; Gaming</t>
+          <t>State of Minnesota - Minnesota IT Services</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Databricks, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
+          <t>AWS, Glue, S3, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54fa68f69cf2083f</t>
+          <t>https://www.indeed.com/viewjob?jk=1054e208948fd6fb</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Data Engineer II - (Remote)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Fanatics Betting &amp; Gaming</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, S3, RDS, Databricks, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f950c716669dfe8d</t>
+          <t>https://www.indeed.com/viewjob?jk=54fa68f69cf2083f</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>.Net Engineer-Data Engineering</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Scala, Snowflake, SQL Server, PostgreSQL, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90c0e5d8f944baf1</t>
+          <t>https://www.indeed.com/viewjob?jk=f950c716669dfe8d</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Reporting Engineer</t>
+          <t>Research Engineer II - ML Ops</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Hitachi Rail</t>
+          <t>GE HealthCare</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MySQL, Star Schema, Fact Tables, Dimension Tables</t>
+          <t>AWS, Lambda, S3, ECS, Spark, Scala, DynamoDB, MLOps, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7504d94e8707d02b</t>
+          <t>https://www.indeed.com/viewjob?jk=03cffd0794f9ae1f</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>AI Native Developer- EST</t>
+          <t>.Net Engineer-Data Engineering</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
+          <t>Azure, Data Factory, Scala, Snowflake, SQL Server, PostgreSQL, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37e94025d78d00b3</t>
+          <t>https://www.indeed.com/viewjob?jk=90c0e5d8f944baf1</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Reporting Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Hitachi Rail</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, SNS, RDS, Azure, Oracle, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MySQL, Star Schema, Fact Tables, Dimension Tables</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1916ff73e89dbf5f</t>
+          <t>https://www.indeed.com/viewjob?jk=7504d94e8707d02b</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Databricks Architect</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Confiz</t>
+          <t>Texas Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Bentonville, AR, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,34 +1396,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Google Cloud Platform, Cloud Storage, Spark, PySpark</t>
+          <t>AWS, ECS, IAM, Azure, Scala, Splunk, CI/CD, Jenkins, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18be742c481fa20b</t>
+          <t>https://www.indeed.com/viewjob?jk=c6430dfa06f6062e</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Software Engineer, New College Graduate,</t>
+          <t>AI Native Developer- EST</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Teradyne</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>North Reading, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a9c723d1fa4a196</t>
+          <t>https://www.indeed.com/viewjob?jk=37e94025d78d00b3</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Software Engineer III - Risk Decision Technology</t>
+          <t>Senior Data Science Engineer (With TS/SCI Clearance and a current Full Scope Poly)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>J&amp;T Business Consulting</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Annapolis Junction, MD, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, GCP, BigQuery, Dataflow, Hadoop, Hive, HBase, Kafka</t>
+          <t>AWS, RDS, Azure, Vertex AI, Hadoop, Spark, Scala, Kafka, NoSQL, MLOps</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,67 +1476,67 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9cecf643a53b2209</t>
+          <t>https://www.indeed.com/viewjob?jk=439377efddb3496b</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Associate Cloud Data Engineer II</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Amway</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Ada, MI, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Hadoop, Spark, Scala</t>
+          <t>AWS, Kinesis, SQS, SNS, RDS, Azure, Oracle, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab4ff42758b01e3c</t>
+          <t>https://www.indeed.com/viewjob?jk=1916ff73e89dbf5f</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Cloud Solutions Engineer – Azure</t>
+          <t>Databricks Architect</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Confiz</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bentonville, AR, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Google Cloud Platform, Cloud Storage, Spark, PySpark</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc23fc3c19075d7c</t>
+          <t>https://www.indeed.com/viewjob?jk=18be742c481fa20b</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior AI Security Automation Engineer</t>
+          <t>Software Engineer, New College Graduate,</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>State Street</t>
+          <t>Teradyne</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Quincy, MA, US USA</t>
+          <t>North Reading, MA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, ELT</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1acc92079f390921</t>
+          <t>https://www.indeed.com/viewjob?jk=4a9c723d1fa4a196</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer III - Risk Decision Technology</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Fairlife, LLC</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Medallion Architecture, Spark, PySpark, Dimensional Modeling</t>
+          <t>AWS, S3, RDS, GCP, BigQuery, Dataflow, Hadoop, Hive, HBase, Kafka</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34038fa38ced9dcd</t>
+          <t>https://www.indeed.com/viewjob?jk=9cecf643a53b2209</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Snowflake Platform Engineer</t>
+          <t>Associate Cloud Data Engineer II</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Amway</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Groton, CT, US USA</t>
+          <t>Ada, MI, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,17 +1641,17 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Snowflake, Time Travel, clustering keys, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Hadoop, Spark, Scala</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5ad590ea8a95921</t>
+          <t>https://www.indeed.com/viewjob?jk=ab4ff42758b01e3c</t>
         </is>
       </c>
     </row>
@@ -1681,29 +1681,29 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1063ffb870d53611</t>
+          <t>https://www.indeed.com/viewjob?jk=1acc92079f390921</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Snowflake Platform Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Traackr</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Groton, CT, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Data Modeling, ETL, ELT, MLOps, MLflow</t>
+          <t>AWS, IAM, RDS, Scala, Snowflake, Time Travel, clustering keys, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,67 +1721,67 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df567011cf662897</t>
+          <t>https://www.indeed.com/viewjob?jk=c5ad590ea8a95921</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Platform &amp; Analytics Engineer</t>
+          <t>Senior AI Security Automation Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Indigenous Pact PBC</t>
+          <t>State Street</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Quincy, MA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, ELT</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8deaa38cca423e7</t>
+          <t>https://www.indeed.com/viewjob?jk=1063ffb870d53611</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Platform &amp; Analytics Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Indigenous Pact PBC</t>
+          <t>Fairlife, LLC</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Medallion Architecture, Spark, PySpark, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1649dc6e6d00bbb</t>
+          <t>https://www.indeed.com/viewjob?jk=34038fa38ced9dcd</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Platform &amp; Analytics Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Indigenous Pact PBC</t>
+          <t>Traackr</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Data Modeling, ETL, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4211cb353fe7a94e</t>
+          <t>https://www.indeed.com/viewjob?jk=df567011cf662897</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Platform &amp; Analytics Engineer</t>
+          <t>Senior DevOps Engineer (EKS/Kubernetes)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Indigenous Pact PBC</t>
+          <t>Caris Life Sciences</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, S3, IAM, RDS, Scala, PostgreSQL, MySQL, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24f9b2c310f5bfa3</t>
+          <t>https://www.indeed.com/viewjob?jk=0028549706f10f55</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58f8c703d51d3a40</t>
+          <t>https://www.indeed.com/viewjob?jk=d8deaa38cca423e7</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Data Platform &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>Indigenous Pact PBC</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Bridgewater, NJ, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=786fbdb63698b11b</t>
+          <t>https://www.indeed.com/viewjob?jk=d1649dc6e6d00bbb</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Data Platform &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>Indigenous Pact PBC</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Bridgewater, NJ, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d193f030168c94d0</t>
+          <t>https://www.indeed.com/viewjob?jk=4211cb353fe7a94e</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Cybersecurity Engineer</t>
+          <t>Data Platform &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Leidos</t>
+          <t>Indigenous Pact PBC</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ELT, CI/CD, Azure DevOps, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=baa14defff29cc46</t>
+          <t>https://www.indeed.com/viewjob?jk=24f9b2c310f5bfa3</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior AI Solutions Architect</t>
+          <t>Data Platform &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Neo4j</t>
+          <t>Indigenous Pact PBC</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Hadoop, Hive, Spark, Scala, NoSQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0dbb073f20120e13</t>
+          <t>https://www.indeed.com/viewjob?jk=58f8c703d51d3a40</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Solution Architect - Java/J2EE</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>PNC Financial Services Group</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Farmers Branch, TX, US USA</t>
+          <t>Bridgewater, NJ, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MongoDB, Cassandra</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a23b5c57a47b265</t>
+          <t>https://www.indeed.com/viewjob?jk=786fbdb63698b11b</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Software Architect - Java/Spring Boot/Kafka</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>PNC Financial Services Group</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Bridgewater, NJ, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MongoDB, Cassandra</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f929c4ac83ec17b7</t>
+          <t>https://www.indeed.com/viewjob?jk=d193f030168c94d0</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Software Engineering SMTS</t>
+          <t>Cybersecurity Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Leidos</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ELT, CI/CD, Azure DevOps, Kubernetes</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98a642ee513df5f7</t>
+          <t>https://www.indeed.com/viewjob?jk=baa14defff29cc46</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Powertrain Applications Engineer</t>
+          <t>Senior AI Solutions Architect</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Neo4j</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,77 +2166,77 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, SQL Server, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Hadoop, Hive, Spark, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af00d281c82c2777</t>
+          <t>https://www.indeed.com/viewjob?jk=0dbb073f20120e13</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Solution Architect - Java/J2EE</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>datAvail</t>
+          <t>PNC Financial Services Group</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Farmers Branch, TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b02e7a9293c05e9</t>
+          <t>https://www.indeed.com/viewjob?jk=3a23b5c57a47b265</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>AI &amp; Data Engineer, Data Discovery Services</t>
+          <t>Software Architect - Java/Spring Boot/Kafka</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Bristol Myers Squibb</t>
+          <t>PNC Financial Services Group</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, ECS, RDS, Azure, Databricks, Vertex AI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,102 +2246,102 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9331d42b3835041a</t>
+          <t>https://www.indeed.com/viewjob?jk=f929c4ac83ec17b7</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Databricks Platform Engineer</t>
+          <t>Data Science Analyst - Agentic AI Developer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Confiz</t>
+          <t>NRG Energy</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Bentonville, AR, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Google Cloud Platform, Spark, Scala, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Vertex AI, Spark, Scala, Power BI, Tableau, MLOps</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b713352ad723441</t>
+          <t>https://www.indeed.com/viewjob?jk=e70aff22bb7641b9</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>AWS Devops Cloud Engineer</t>
+          <t>Software Engineering SMTS</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Onebridge</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, ECS, IAM, RDS, Databricks, Spark, Scala</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b690190bc20de39</t>
+          <t>https://www.indeed.com/viewjob?jk=98a642ee513df5f7</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Java Product Engineer</t>
+          <t>Powertrain Applications Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Diaconia, LLC.</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, Oracle, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
+          <t>AWS, S3, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, SQL Server, ELT</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed19f7417f9c2e59</t>
+          <t>https://www.indeed.com/viewjob?jk=af00d281c82c2777</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>iSynergy Information Technologies</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Azure, Snowflake, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87d9611a04bffadf</t>
+          <t>https://www.indeed.com/viewjob?jk=21910689207bf63d</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Full Stack</t>
+          <t>Senior Cloud Engineer - Azure</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>CCC Intelligent Solutions</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Hopkins, MN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB, Cassandra</t>
+          <t>RDS, Azure, Scala, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=caea23a7afe82982</t>
+          <t>https://www.indeed.com/viewjob?jk=4665edec79f4e66b</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Full Stack</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>datAvail</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB, Cassandra</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c6c9dc97e7a8c55</t>
+          <t>https://www.indeed.com/viewjob?jk=0b02e7a9293c05e9</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Full Stack</t>
+          <t>AI &amp; Data Engineer, Data Discovery Services</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Bristol Myers Squibb</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Brookfield, WI, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB, Cassandra</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, ECS, RDS, Azure, Databricks, Vertex AI</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97ef6349d26627c1</t>
+          <t>https://www.indeed.com/viewjob?jk=9331d42b3835041a</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Specialist - Data Engineering</t>
+          <t>Databricks Platform Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>Confiz</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Bentonville, AR, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,147 +2516,147 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Spark, Scala, SQL Server, ETL, Tableau, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Google Cloud Platform, Spark, Scala, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55c8d9fe21fbf89b</t>
+          <t>https://www.indeed.com/viewjob?jk=5b713352ad723441</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Cloud DevOps Engineer</t>
+          <t>AWS Devops Cloud Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Mastronardi Produce</t>
+          <t>Onebridge</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Livonia, MI, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, MLOps, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, Redshift, S3, ECS, IAM, RDS, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fa1ca8e2ddf6df8</t>
+          <t>https://www.indeed.com/viewjob?jk=9b690190bc20de39</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Cloud Systems Engineer III</t>
+          <t>AI Architect</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Orange County's Credit Union</t>
+          <t>VeeRteq Solutions Inc.</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Santa Ana, CA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, Scala, ELT, CI/CD, Terraform, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, NoSQL, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37e9b523a42f1787</t>
+          <t>https://www.indeed.com/viewjob?jk=8574e7ed96b2d014</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>University of Idaho</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Moscow, ID, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Databricks Lakehouse, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Azure, Snowflake, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2714c15bcc60033</t>
+          <t>https://www.indeed.com/viewjob?jk=87d9611a04bffadf</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Application Support Engineer</t>
+          <t>Senior Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Availity, LLC.</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Hopkins, MN, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MongoDB</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,32 +2666,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b138daabe966037</t>
+          <t>https://www.indeed.com/viewjob?jk=caea23a7afe82982</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Software Engineer, MTS, Enterprise Security, Identity &amp; Access Management</t>
+          <t>Senior Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,137 +2701,137 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08079db08d267e47</t>
+          <t>https://www.indeed.com/viewjob?jk=2c6c9dc97e7a8c55</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Brookfield, WI, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, PostgreSQL, MySQL, Splunk, Maven</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1d1f01448956ac8</t>
+          <t>https://www.indeed.com/viewjob?jk=97ef6349d26627c1</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Junior Data Engineer</t>
+          <t>Java Product Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Techfield</t>
+          <t>Diaconia, LLC.</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Hadoop, Hive, Spark, Scala, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, Azure, Scala, Kafka, Oracle, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95557e0528468ca2</t>
+          <t>https://www.indeed.com/viewjob?jk=ed19f7417f9c2e59</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Specialist - Data Engineering</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Google Cloud Platform, GCP, Hadoop, Scala, Snowflake, ETL, ELT, CI/CD, Airflow</t>
+          <t>RDS, Hadoop, Spark, Scala, SQL Server, ETL, Tableau, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c875e063114bb1c</t>
+          <t>https://www.indeed.com/viewjob?jk=55c8d9fe21fbf89b</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Reporting Solutions Engineer</t>
+          <t>Senior Software Engineer – AI Applications</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Wpromote, LLC</t>
+          <t>Mears Group Inc</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Englewood, CO, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, dbt, Tableau</t>
+          <t>AWS, RDS, Azure, Spark, Scala, NoSQL, ETL, Power BI, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cad2ebf6af99a7d</t>
+          <t>https://www.indeed.com/viewjob?jk=c131dea7fda0b9ad</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Engineer (Azure &amp; Snowflake) - Remote</t>
+          <t>Cloud DevOps Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Mindex</t>
+          <t>Mastronardi Produce</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>Livonia, MI, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Data Lake Storage, Cloud Storage, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, MLOps, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,102 +2876,102 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=329cdc7ca8132e90</t>
+          <t>https://www.indeed.com/viewjob?jk=7fa1ca8e2ddf6df8</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Data Engineer (Azure &amp; Snowflake) - Remote</t>
+          <t>Cloud Systems Engineer III</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Mindex</t>
+          <t>Orange County's Credit Union</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>Santa Ana, CA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Data Lake Storage, Cloud Storage, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Scala, ELT, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a4ebf0e5f5c11c0</t>
+          <t>https://www.indeed.com/viewjob?jk=37e9b523a42f1787</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Data Engineer (Azure &amp; Snowflake) - Remote</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Mindex</t>
+          <t>University of Idaho</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>Moscow, ID, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Data Lake Storage, Cloud Storage, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Databricks Lakehouse, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c6a06a8d28780bf</t>
+          <t>https://www.indeed.com/viewjob?jk=c2714c15bcc60033</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data Engineer (Azure &amp; Snowflake) - Remote</t>
+          <t>Application Support Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Mindex</t>
+          <t>Availity, LLC.</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Data Lake Storage, Cloud Storage, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, S3, IAM, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd6304cc9580794e</t>
+          <t>https://www.indeed.com/viewjob?jk=7b138daabe966037</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Sr Cloud Engineer</t>
+          <t>Software Engineer, MTS, Enterprise Security, Identity &amp; Access Management</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Lennar</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, IAM, RDS</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0b237d7cb0a351b</t>
+          <t>https://www.indeed.com/viewjob?jk=08079db08d267e47</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>DBHDS - SQL Database Administrator</t>
+          <t>Junior Data Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Betis Group, Inc.</t>
+          <t>Techfield</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
+          <t>AWS, S3, Azure, Hadoop, Hive, Spark, Scala, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b671e1c355c84c5</t>
+          <t>https://www.indeed.com/viewjob?jk=95557e0528468ca2</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Forward Deployed Data Engineer</t>
+          <t>Reporting Solutions Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>CoorsTek</t>
+          <t>Wpromote, LLC</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Golden, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,34 +3076,34 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, dbt, Tableau</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01c677c253d655bb</t>
+          <t>https://www.indeed.com/viewjob?jk=1cad2ebf6af99a7d</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer</t>
+          <t>Data Engineer (Azure &amp; Snowflake) - Remote</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Ubiety</t>
+          <t>Mindex</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, GCP, Scala, Kafka, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>Azure, Data Factory, Data Lake Storage, Cloud Storage, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fd4531981abb3e6</t>
+          <t>https://www.indeed.com/viewjob?jk=329cdc7ca8132e90</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Solutions Architect - Public Sector (SLED)</t>
+          <t>Data Engineer (Azure &amp; Snowflake) - Remote</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Mindex</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, ELT</t>
+          <t>Azure, Data Factory, Data Lake Storage, Cloud Storage, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d898f82946c9db3</t>
+          <t>https://www.indeed.com/viewjob?jk=7a4ebf0e5f5c11c0</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Sr. Solutions Architect - Public Sector (SLED)</t>
+          <t>Data Engineer (Azure &amp; Snowflake) - Remote</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Mindex</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, ELT</t>
+          <t>Azure, Data Factory, Data Lake Storage, Cloud Storage, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=deaebb012d17a528</t>
+          <t>https://www.indeed.com/viewjob?jk=7c6a06a8d28780bf</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer (Azure &amp; Snowflake) - Remote</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>SpyCloud</t>
+          <t>Mindex</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Databricks, Spark, Scala, DynamoDB, ETL</t>
+          <t>Azure, Data Factory, Data Lake Storage, Cloud Storage, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a2f212e69e1f862</t>
+          <t>https://www.indeed.com/viewjob?jk=cd6304cc9580794e</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr Cloud Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Unity Technologies</t>
+          <t>Lennar</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, IAM, RDS</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=652b63d35a6266a3</t>
+          <t>https://www.indeed.com/viewjob?jk=d0b237d7cb0a351b</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Full-Stack AI Engineer</t>
+          <t>DBHDS - SQL Database Administrator</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Micron Technology</t>
+          <t>Betis Group, Inc.</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb2b319c05d2be3e</t>
+          <t>https://www.indeed.com/viewjob?jk=9b671e1c355c84c5</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>SR SOFTWARE ENGINEER</t>
+          <t>Forward Deployed Data Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Dollar General</t>
+          <t>CoorsTek</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Goodlettsville, TN, US USA</t>
+          <t>Golden, CO, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>S3, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, Cassandra, CI/CD, Docker</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbb1d7ed6fd57469</t>
+          <t>https://www.indeed.com/viewjob?jk=01c677c253d655bb</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Solutions Architect - Public Sector (SLED)</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>We Write Code</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, ECS, IAM, Azure, Snowflake, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, ELT</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0821497679584e2d</t>
+          <t>https://www.indeed.com/viewjob?jk=9d898f82946c9db3</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Sr. Solutions Architect - Public Sector (SLED)</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Unum</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, AWS CloudFormation, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, ELT</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,54 +3401,54 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04a647a34b37a72a</t>
+          <t>https://www.indeed.com/viewjob?jk=deaebb012d17a528</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Sr Datawarehouse Architect for New York City NY</t>
+          <t>Senior Backend Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Centillion Infotech LLC</t>
+          <t>Ubiety</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, Scala, Data Modeling, ETL, ELT, Python, SQL</t>
+          <t>AWS, Kinesis, RDS, GCP, Scala, Kafka, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a11b6e886c2b743d</t>
+          <t>https://www.indeed.com/viewjob?jk=8fd4531981abb3e6</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Northwest Federal Credit Union</t>
+          <t>Deltek</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3457,81 +3457,81 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, MySQL, Azure DevOps, Terraform, Azure Monitor</t>
+          <t>AWS, ECS, RDS, Azure, GCP, PostgreSQL, ELT, CI/CD, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7291a950f8ec410d</t>
+          <t>https://www.indeed.com/viewjob?jk=3118e1ec3a525992</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Advanced Specialist, Data Engineering</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Pearson</t>
+          <t>SpyCloud</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Bloomington, MN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Databricks, Spark, Scala, DynamoDB, ETL</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d1ad3be6df1730a</t>
+          <t>https://www.indeed.com/viewjob?jk=7a2f212e69e1f862</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Platform Engineer, Data Services</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Vytalize Health</t>
+          <t>Unity Technologies</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, EMR, Athena, RDS, Databricks, GCP, Scala, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Google Cloud Platform, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,67 +3541,67 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00036ac2c3d4f673</t>
+          <t>https://www.indeed.com/viewjob?jk=652b63d35a6266a3</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Full-Stack AI Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>College Board</t>
+          <t>Micron Technology</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, Scala, DynamoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78ac72ba3ec01f22</t>
+          <t>https://www.indeed.com/viewjob?jk=cb2b319c05d2be3e</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior .NET Developer</t>
+          <t>SR SOFTWARE ENGINEER</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Dollar General</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Goodlettsville, TN, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, Scala, Kafka, SQL Server, PostgreSQL, NoSQL, Data Modeling, CI/CD</t>
+          <t>S3, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, Cassandra, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,67 +3611,67 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35a2c65d6f2f7d06</t>
+          <t>https://www.indeed.com/viewjob?jk=fbb1d7ed6fd57469</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Rhodes Financial Services</t>
+          <t>We Write Code</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Augusta, GA, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Glue, Redshift, S3, ECS, IAM, Azure, Snowflake, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=291d753a3842da49</t>
+          <t>https://www.indeed.com/viewjob?jk=0821497679584e2d</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>TaxSlayer</t>
+          <t>Unum</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Augusta, GA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, AWS CloudFormation, Jenkins</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e38ede1f1c848056</t>
+          <t>https://www.indeed.com/viewjob?jk=04a647a34b37a72a</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Sr Datawarehouse Architect for New York City NY</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>TaxSlayer</t>
+          <t>Centillion Infotech LLC</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Evans, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Spark, Scala, Data Modeling, ETL, ELT, Python, SQL</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9cec52a87c2914b</t>
+          <t>https://www.indeed.com/viewjob?jk=a11b6e886c2b743d</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Generative AI Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>TaxSlayer</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>North Augusta, SC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,34 +3741,34 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Vertex AI, Hadoop, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f84a2d5bc189bc0</t>
+          <t>https://www.indeed.com/viewjob?jk=4413ec7a4b00d4ae</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Generative AI Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>TaxSlayer</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Augusta, GA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,34 +3776,34 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Vertex AI, Hadoop, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9540e403cb0fe0bc</t>
+          <t>https://www.indeed.com/viewjob?jk=3e48a5b4af545b7e</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>TaxSlayer</t>
+          <t>Northwest Federal Credit Union</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Aiken, SC, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,34 +3811,34 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, MySQL, Azure DevOps, Terraform, Azure Monitor</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39572bc0cbf1e1ab</t>
+          <t>https://www.indeed.com/viewjob?jk=7291a950f8ec410d</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Advanced Specialist, Data Engineering</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>TaxSlayer</t>
+          <t>Pearson</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Grovetown, GA, US USA</t>
+          <t>Bloomington, MN, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f96379913f2a0b13</t>
+          <t>https://www.indeed.com/viewjob?jk=7d1ad3be6df1730a</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Sr Devops Engineer</t>
+          <t>Platform Engineer, Data Services</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>_coderio</t>
+          <t>Vytalize Health</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,34 +3881,34 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, EMR, Athena, RDS, Databricks, GCP, Scala, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=541df4abc8320b5a</t>
+          <t>https://www.indeed.com/viewjob?jk=00036ac2c3d4f673</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Database Developer</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Integres, LLC</t>
+          <t>College Board</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>RDS, Azure, Spark, PySpark, SQL Server, Data Modeling, ETL, Power BI, Jenkins, Azure DevOps</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, Scala, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc8d97653729dfa4</t>
+          <t>https://www.indeed.com/viewjob?jk=78ac72ba3ec01f22</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Senior R&amp;D Software Engineer, Fivetran AI</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Fivetran</t>
+          <t>Rhodes Financial Services</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Augusta, GA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,34 +3951,34 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, BigQuery, Snowflake, ETL, ELT, dbt, Docker</t>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55c8e7c6018043d4</t>
+          <t>https://www.indeed.com/viewjob?jk=291d753a3842da49</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Senior R&amp;D Software Engineer, Fivetran AI</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Fivetran</t>
+          <t>TaxSlayer</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Augusta, GA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,34 +3986,34 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, BigQuery, Snowflake, ETL, ELT, dbt, Docker</t>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30bf0451dbc419d1</t>
+          <t>https://www.indeed.com/viewjob?jk=e38ede1f1c848056</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Senior R&amp;D Software Engineer, Fivetran AI</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Fivetran</t>
+          <t>TaxSlayer</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Evans, GA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,34 +4021,34 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, BigQuery, Snowflake, ETL, ELT, dbt, Docker</t>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=501671e22555fe5c</t>
+          <t>https://www.indeed.com/viewjob?jk=f9cec52a87c2914b</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Senior R&amp;D Software Engineer, Fivetran AI</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Fivetran</t>
+          <t>TaxSlayer</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>North Augusta, SC, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,15 +4056,365 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1f84a2d5bc189bc0</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Software Developer</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>TaxSlayer</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Augusta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9540e403cb0fe0bc</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Software Developer</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>TaxSlayer</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Aiken, SC, US USA</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=39572bc0cbf1e1ab</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Software Developer</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>TaxSlayer</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Grovetown, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f96379913f2a0b13</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Sr Devops Engineer</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>_coderio</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Miami, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=541df4abc8320b5a</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Database Developer</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Integres, LLC</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Saint Paul, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Spark, PySpark, SQL Server, Data Modeling, ETL, Power BI, Jenkins, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cc8d97653729dfa4</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Contract Associate Development Engineer</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Sinclair Broadcast Group</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Hunt Valley, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>AWS, Databricks, Scala, MySQL, MongoDB, CI/CD, Terraform, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c7da459b7e5a5519</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Senior R&amp;D Software Engineer, Fivetran AI</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Fivetran</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
           <t>AWS, RDS, Databricks, GCP, BigQuery, Snowflake, ETL, ELT, dbt, Docker</t>
         </is>
       </c>
-      <c r="F104" t="inlineStr">
+      <c r="F111" t="inlineStr">
         <is>
           <t>2026-07-20</t>
         </is>
       </c>
-      <c r="G104" t="inlineStr">
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=55c8e7c6018043d4</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Senior R&amp;D Software Engineer, Fivetran AI</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Fivetran</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, GCP, BigQuery, Snowflake, ETL, ELT, dbt, Docker</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=30bf0451dbc419d1</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Senior R&amp;D Software Engineer, Fivetran AI</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Fivetran</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, GCP, BigQuery, Snowflake, ETL, ELT, dbt, Docker</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=501671e22555fe5c</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Senior R&amp;D Software Engineer, Fivetran AI</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Fivetran</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Oakland, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, GCP, BigQuery, Snowflake, ETL, ELT, dbt, Docker</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=f8b8baa922f2b05a</t>
         </is>
